--- a/Products/Morfology Lab Product List Moby.xlsx
+++ b/Products/Morfology Lab Product List Moby.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="X:\Kullanıcılar\Rovshen\Masaüstü\PROJELER\Şirketler\GREEN MED\Web Page\Products\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{584685F3-68C8-41CD-82AC-D360AF47D638}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B5547150-F56E-4704-8FAB-32FEF3B0DE5E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="19396" windowHeight="11475" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1268" uniqueCount="717">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1365" uniqueCount="725">
   <si>
     <t>LABORATUVAR SARF MALZEMELERİ — ÜRÜN GİRİŞ ŞABLONU</t>
   </si>
@@ -278,9 +278,6 @@
     <t>3500 analizörü için POP-4 polimer, 384 test</t>
   </si>
   <si>
-    <t>POP-4 Polymer for 3500 analyzer, 384 tests</t>
-  </si>
-  <si>
     <t>4393715</t>
   </si>
   <si>
@@ -293,9 +290,6 @@
     <t>24 упак/ pack</t>
   </si>
   <si>
-    <t>Pouch</t>
-  </si>
-  <si>
     <t>384 samples</t>
   </si>
   <si>
@@ -308,9 +302,6 @@
     <t>3500 analizörü için anot tampon kabı, 4 adet/paket</t>
   </si>
   <si>
-    <t>Anode Buffer Container for 3500 analyzer, 4 pcs/pack</t>
-  </si>
-  <si>
     <t>Life Technologies Corporation</t>
   </si>
   <si>
@@ -332,9 +323,6 @@
     <t>3500 analizörü için katot tampon kabı, 4 adet/paket</t>
   </si>
   <si>
-    <t>Cathode Buffer Container for 3500 analyzer, 4 pcs/pack</t>
-  </si>
-  <si>
     <t>4408256</t>
   </si>
   <si>
@@ -374,9 +362,6 @@
     <t>3500 Genetik Analizör için koşullandırma reaktifi</t>
   </si>
   <si>
-    <t>Conditioning Reagent for 3500 Genetic Analyzer</t>
-  </si>
-  <si>
     <t>4393718</t>
   </si>
   <si>
@@ -398,9 +383,6 @@
     <t>3500 için GeneScan - 600 LIZ laboratuvar reaktifi</t>
   </si>
   <si>
-    <t>GeneScan - 600 LIZ laboratory reagent for 3500</t>
-  </si>
-  <si>
     <t>4408399</t>
   </si>
   <si>
@@ -422,9 +404,6 @@
     <t>Quantifiler™ Trio DNA Kantifikasyon Kiti, 400 test</t>
   </si>
   <si>
-    <t>Quantifiler™ Trio DNA Quantification Kit, 400 tests</t>
-  </si>
-  <si>
     <t>4482910</t>
   </si>
   <si>
@@ -452,9 +431,6 @@
     <t>GlobalFiler™ Express PCR Amplifikasyon Kiti, 200 test</t>
   </si>
   <si>
-    <t>GlobalFiler™ Express PCR Amplification Kit, 200 tests</t>
-  </si>
-  <si>
     <t>STR PCR amplification kit</t>
   </si>
   <si>
@@ -476,9 +452,6 @@
     <t>GlobalFiler™ PCR Amplifikasyon Kiti, 200 test</t>
   </si>
   <si>
-    <t>GlobalFiler™ PCR Amplification Kit, 200 tests</t>
-  </si>
-  <si>
     <t>4476135</t>
   </si>
   <si>
@@ -491,9 +464,6 @@
     <t>Prep-n-Go™ tamponu (bukkal sürüntüler için), 200 reaksiyon</t>
   </si>
   <si>
-    <t>Prep-n-Go™ Buffer (for buccal swabs), 200 rxn</t>
-  </si>
-  <si>
     <t>4471406</t>
   </si>
   <si>
@@ -515,9 +485,6 @@
     <t>Adli DNA Ekstraksiyon Kiti, PrepFiler Express™, 52 test</t>
   </si>
   <si>
-    <t>Forensic DNA Extraction Kit, PrepFiler Express™, 52 tests</t>
-  </si>
-  <si>
     <t>4441352</t>
   </si>
   <si>
@@ -542,9 +509,6 @@
     <t>Adli DNA Ekstraksiyon Kiti, PrepFiler Express BTA™, 52 test</t>
   </si>
   <si>
-    <t>Forensic DNA Extraction Kit, PrepFiler Express BTA™, 52 tests</t>
-  </si>
-  <si>
     <t>4441351</t>
   </si>
   <si>
@@ -578,9 +542,6 @@
     <t>İnsan serum proteinlerine karşı antiserum, Hematolog, 324HV</t>
   </si>
   <si>
-    <t>Antiserum against human serum proteins, Hematolog, 324HV</t>
-  </si>
-  <si>
     <t>Gematolog, Russia</t>
   </si>
   <si>
@@ -596,9 +557,6 @@
     <t>Domuz serum proteinlerine karşı antiserum, Hematolog, 226SV</t>
   </si>
   <si>
-    <t>Antiserum against porcine serum proteins, Hematolog, 226SV</t>
-  </si>
-  <si>
     <t>10 ml / мл</t>
   </si>
   <si>
@@ -608,9 +566,6 @@
     <t>Sığır serum proteinlerine karşı antiserum, Hematolog, 162RS</t>
   </si>
   <si>
-    <t>Antiserum against bovine serum proteins, Hematolog, 162RS</t>
-  </si>
-  <si>
     <t>20 ml / мл</t>
   </si>
   <si>
@@ -620,15 +575,9 @@
     <t>At serum proteinlerine karşı antiserum, Hematolog, 160-1LSH</t>
   </si>
   <si>
-    <t>Antiserum against equine serum proteins, Hematolog, 160-1LSH</t>
-  </si>
-  <si>
     <t>Kuş serum proteinlerine karşı antiserum, Hematolog, 215-1PT</t>
   </si>
   <si>
-    <t>Antiserum against avian serum proteins, Hematolog, 215-1PT</t>
-  </si>
-  <si>
     <t>15 ml / мл</t>
   </si>
   <si>
@@ -638,18 +587,12 @@
     <t>Köpek serum proteinlerine karşı antiserum, Hematolog, 163SB</t>
   </si>
   <si>
-    <t>Antiserum against dog serum proteins, Hematolog, 163SB</t>
-  </si>
-  <si>
     <t>5 ml / мл</t>
   </si>
   <si>
     <t>Kedi serum proteinlerine karşı antiserum, Hematolog, 145-1KSH</t>
   </si>
   <si>
-    <t>Antiserum against cat serum proteins, Hematolog, 145-1KSH</t>
-  </si>
-  <si>
     <t>Tavşan serum proteinlerine karşı antiserum</t>
   </si>
   <si>
@@ -659,9 +602,6 @@
     <t>Anti-M hemaglütinasyon serumu (solyclon Anti-M)</t>
   </si>
   <si>
-    <t>Anti-M hemagglutinating serum (solyclon Anti-M)</t>
-  </si>
-  <si>
     <t>Hemagglutinating serum</t>
   </si>
   <si>
@@ -674,15 +614,9 @@
     <t>Anti-N hemaglütinasyon serumu (solyclon Anti-N)</t>
   </si>
   <si>
-    <t>Anti-N hemagglutinating serum (solyclon Anti-N</t>
-  </si>
-  <si>
     <t>Anti-P hemaglütinasyon serumu (solyclon Anti-P)</t>
   </si>
   <si>
-    <t>Anti-P hemagglutinating serum (solyclon Anti-P)</t>
-  </si>
-  <si>
     <t>Kell hemaglütinasyon serumu</t>
   </si>
   <si>
@@ -692,9 +626,6 @@
     <t>Kan gruplaması için Anti-A monoklonal antikorlar, 797F</t>
   </si>
   <si>
-    <t>Anti-A Monoclonal Antibodies for Blood Typing, 797F</t>
-  </si>
-  <si>
     <t>№ФСР 2008/04007 — регистрационное удостоверение на медицинское изделие «Цоликлоны Анти-А, Анти-В и Анти-АВ» (антитела моноклональные анти-А, анти-В, анти-АВ) по ТУ 9398-001-27575295-2004</t>
   </si>
   <si>
@@ -710,15 +641,9 @@
     <t>Kan gruplaması için Anti-B monoklonal antikorlar, 798F</t>
   </si>
   <si>
-    <t>Anti-B Monoclonal Antibodies for Blood Typing, 798F</t>
-  </si>
-  <si>
     <t>Kan gruplaması için Anti-H monoklonal antikorlar, 31-7</t>
   </si>
   <si>
-    <t>Anti-H Monoclonal Antibodies for Blood Typing, 31-7</t>
-  </si>
-  <si>
     <t>100 ml / мл</t>
   </si>
   <si>
@@ -728,15 +653,9 @@
     <t>Anti-D monoklonal kan gruplama reaktifi, 918</t>
   </si>
   <si>
-    <t>Anti-D monoclonal blood grouping reagent, 918</t>
-  </si>
-  <si>
     <t>Mikrotom bıçakları</t>
   </si>
   <si>
-    <t>Microtome blades</t>
-  </si>
-  <si>
     <t>Plasma Blade LPH</t>
   </si>
   <si>
@@ -752,9 +671,6 @@
     <t>Mayer Hematoksilin 1 L, BioWitrum</t>
   </si>
   <si>
-    <t>Mayer's Hematoxylin 1 L., BioWitrum</t>
-  </si>
-  <si>
     <t>HК-G0-DL01</t>
   </si>
   <si>
@@ -773,9 +689,6 @@
     <t>Eozin su-alkollü konsantre 0,5 L, BioWitrum</t>
   </si>
   <si>
-    <t>Eosin water-alcoholic concentrated 0,5 L, BioWitrum</t>
-  </si>
-  <si>
     <t>HК-EK-A500</t>
   </si>
   <si>
@@ -785,9 +698,6 @@
     <t>PURELAB Option-R 7/15 ters ozmoz filtre kartuşu</t>
   </si>
   <si>
-    <t>PURELAB Option-R 7/15   Cartridge for reverse osmosis filters</t>
-  </si>
-  <si>
     <t>LC143 Purelab Option 7/15 Reverse Osmosis</t>
   </si>
   <si>
@@ -815,9 +725,6 @@
     <t>Purelab Option-R için UV lamba</t>
   </si>
   <si>
-    <t>UV lamp for Purelab Option-R</t>
-  </si>
-  <si>
     <t>LC105 Purelab Option 7/15</t>
   </si>
   <si>
@@ -833,9 +740,6 @@
     <t>Purelab Option-R için saflaştırma paketi</t>
   </si>
   <si>
-    <t>Purification pack for Purelab Option-R</t>
-  </si>
-  <si>
     <t>LC214 Purelab flex 3&amp;4 Purification pack</t>
   </si>
   <si>
@@ -854,9 +758,6 @@
     <t>UV lamba 185/254 nm</t>
   </si>
   <si>
-    <t>UV lamp 185/254nm</t>
-  </si>
-  <si>
     <t>LC210-02 Purelab flex 3&amp;4 UV lamp</t>
   </si>
   <si>
@@ -896,9 +797,6 @@
     <t>Emit® II Plus Etil Alkol reaktifi, 115 ml</t>
   </si>
   <si>
-    <t>Emit® II Plus EthylAlcohol reagent, 115 ml</t>
-  </si>
-  <si>
     <t>Art 10445452 REF 9K309</t>
   </si>
   <si>
@@ -923,9 +821,6 @@
     <t>EMIT® Alkol Yüksek Kontrol 300 mg/dL, 1x3 ml</t>
   </si>
   <si>
-    <t>EMIT® Alcohol High Control 300 MG/DL, 1x3 ml</t>
-  </si>
-  <si>
     <t>Art 10445449 REF 9K079</t>
   </si>
   <si>
@@ -950,9 +845,6 @@
     <t>EMIT® Etil Alkol Düşük Kontrol 40 mg/dL, 1x3 ml</t>
   </si>
   <si>
-    <t>EMIT® Ethyl Alcohol Low Control 40 MG/DL, 1x3 ml</t>
-  </si>
-  <si>
     <t>ART 10445447  REF 9K049</t>
   </si>
   <si>
@@ -968,9 +860,6 @@
     <t>EMIT® Alkol Negatif Kalibratör, 1x3 ml</t>
   </si>
   <si>
-    <t>EMIT® Alcohol Negative Calibrator, 1x3 ml</t>
-  </si>
-  <si>
     <t>ART 10445445  REF 9K029</t>
   </si>
   <si>
@@ -989,9 +878,6 @@
     <t>EMIT® Alkol Kalibratörü 100 mg/dL, 1x3 ml</t>
   </si>
   <si>
-    <t>EMIT® Alcohol Calibrator 100 MG/DL, 1x3 ml</t>
-  </si>
-  <si>
     <t>ART 10445448 REF 9K059</t>
   </si>
   <si>
@@ -1010,9 +896,6 @@
     <t>EPSON Şerit Kartuşu ERC-09</t>
   </si>
   <si>
-    <t>EPSON Ribbon Cartridge ERC-09</t>
-  </si>
-  <si>
     <t>EPSON Ribbon Cartridge ERC-09 CHINA PAT.P.</t>
   </si>
   <si>
@@ -1031,9 +914,6 @@
     <t>"ClipTip" filtreli pipet uçları, 1000 µl, 8×96 adet</t>
   </si>
   <si>
-    <t>"ClipTip" pipette tips, filtered, 1000 µl, 8*96 pcs</t>
-  </si>
-  <si>
     <t>REF 94420713</t>
   </si>
   <si>
@@ -1058,9 +938,6 @@
     <t>ClipTip™ filtreli pipet uçları</t>
   </si>
   <si>
-    <t>ClipTip&amp;trade; Filtered Pipette Tips</t>
-  </si>
-  <si>
     <t>REF 94410713</t>
   </si>
   <si>
@@ -1074,9 +951,6 @@
   </si>
   <si>
     <t>Agilent GC için helyum gazı, %99,999, 50 L</t>
-  </si>
-  <si>
-    <t>Helium gas for Agilent GC, 99.999%, 50 L</t>
   </si>
   <si>
     <t>99,9999%, 50 Litr
@@ -1102,9 +976,6 @@
     <t>Agilent GC için argon gazı, %99,99, 50 L</t>
   </si>
   <si>
-    <t>Argon gas for Agilent GC, 99.99%, 50 L</t>
-  </si>
-  <si>
     <t>99,999%, 50 Litr
 CAS №: 7440-37-1
 EC №: 231-147-0</t>
@@ -1119,9 +990,6 @@
     <t>Carl Roth Sodyum klorür, ≥%99,5, 1 kg</t>
   </si>
   <si>
-    <t>Carl Roth Sodium chloride, ≥99.5 %, 1 kg</t>
-  </si>
-  <si>
     <t>art № 3957.1</t>
   </si>
   <si>
@@ -1146,9 +1014,6 @@
     <t>Amonyum format, 100 g</t>
   </si>
   <si>
-    <t>Ammonium formate, 100g</t>
-  </si>
-  <si>
     <t>17843-50mg</t>
   </si>
   <si>
@@ -1167,9 +1032,6 @@
     <t>Formik asit Rotipuran, %99, 50 ml</t>
   </si>
   <si>
-    <t>Formic acid Rotipuran, 99%, 50 ml</t>
-  </si>
-  <si>
     <t>85049-051</t>
   </si>
   <si>
@@ -1185,9 +1047,6 @@
     <t>ROTI tampon çözeltisi, pH 4,00 ±0,02, 500 ml</t>
   </si>
   <si>
-    <t>ROTI buffer solution, pH 4.00 ±0.02, 500 ml</t>
-  </si>
-  <si>
     <t>Артикул: P712.3     VWR 32095.184</t>
   </si>
   <si>
@@ -1200,9 +1059,6 @@
     <t>ROTI tampon çözeltisi, pH 10,00 ±0,02, 500 ml</t>
   </si>
   <si>
-    <t>ROTI buffer solution, pH 10.00 ±0.02, 500 ml</t>
-  </si>
-  <si>
     <t>Артикул: P716.2 VWR 32040.185</t>
   </si>
   <si>
@@ -1210,9 +1066,6 @@
   </si>
   <si>
     <t>Hidrojen iz jeneratörü için elektrolitik hücre bloğu</t>
-  </si>
-  <si>
-    <t>Electrolytic cell block for Hydrogen Trace generator</t>
   </si>
   <si>
     <t>08-9412
@@ -1240,9 +1093,6 @@
     <t>Precision Hydrogen Trace için elektrolitik hücre bloğu</t>
   </si>
   <si>
-    <t>Electrolytic cell block for Precision Hydrogen Trace</t>
-  </si>
-  <si>
     <t>05-1007</t>
   </si>
   <si>
@@ -1252,9 +1102,6 @@
     <t>Peak Precision Hydrogen Trace için servis kiti, 1 yıl</t>
   </si>
   <si>
-    <t>Service kit for Peak Precision Hydrogen Trace, 1-year</t>
-  </si>
-  <si>
     <t>08-3609</t>
   </si>
   <si>
@@ -1273,9 +1120,6 @@
     <t>Precision Hydrogen Trace için Peak servis kiti, 1 yıl</t>
   </si>
   <si>
-    <t>Peak service kit, Precision Hydrogen Trace, 1 year</t>
-  </si>
-  <si>
     <t>art № 08-9412   Комплект для ежегодного ремонта Precision Hydrogen Trace (08-9412)  В комплект входит: Клапан (арт. №02-6051)- 2 шт., Двойной цилиндр в сборе (арт. №05-1047)-2 шт.</t>
   </si>
   <si>
@@ -1288,9 +1132,6 @@
     <t>Standart numune, kan alkolü ve florür kantifikasyonu, 10 ml</t>
   </si>
   <si>
-    <t>Standard sample, Blood alcohol and fluoride quantification, 10 ml</t>
-  </si>
-  <si>
     <t>LGC Limited, USA</t>
   </si>
   <si>
@@ -1303,9 +1144,6 @@
     <t>Kalibrasyon çözeltisi Cerilliant, etanol kalibrasyon kiti, 10 × 1,2 ml</t>
   </si>
   <si>
-    <t>Calibration solution Cerilliant, Ethanol calibration kit, 10 x 1.2 ml</t>
-  </si>
-  <si>
     <t>CERE-034</t>
   </si>
   <si>
@@ -1321,9 +1159,6 @@
     <t>Cerilliant etanol kalibrasyon kiti, 10 × 1,2 ml</t>
   </si>
   <si>
-    <t>Cerilliant Ethanol calibration kit, 10 x 1.2 ml</t>
-  </si>
-  <si>
     <t>E-034-1KIT,  CAS Number 64-17-5</t>
   </si>
   <si>
@@ -1333,9 +1168,6 @@
     <t>Vidalı kapaklı idrar kapları, 100 ml, 500 adet/paket</t>
   </si>
   <si>
-    <t>Urine containers with screw cap, 100 ml, 500 pcs/pack</t>
-  </si>
-  <si>
     <t>Order number 75.1354.001</t>
   </si>
   <si>
@@ -1363,9 +1195,6 @@
     <t>VACUSERA vakum tüpleri, NaF+K3 EDTA, 4 ml, 1200 adet</t>
   </si>
   <si>
-    <t>VACUSERA vacuum tubes, NaF+K3 Edta, 4 ml, 1200 pcs</t>
-  </si>
-  <si>
     <t>234704</t>
   </si>
   <si>
@@ -1381,9 +1210,6 @@
     <t>Agilent LC servis kiti, 1 yıl (Jet Clean dahil)</t>
   </si>
   <si>
-    <t>Agilent LC service kit, 1 year (with jet clean)</t>
-  </si>
-  <si>
     <t>G2571-67001  G1964-20402</t>
   </si>
   <si>
@@ -1405,9 +1231,6 @@
     <t>Agilent LC için servis kiti, 1 yıl (Jet Clean dahil)</t>
   </si>
   <si>
-    <t>Service kit for Agilent LC, 1-year (incl. Jet Clean)</t>
-  </si>
-  <si>
     <t>G2571-67001 Canted Coil Spring, 8.9mm OD | ChromTech    .</t>
   </si>
   <si>
@@ -1417,9 +1240,6 @@
     <t>Agilent GC cihazı için servis kiti, 1 yıl</t>
   </si>
   <si>
-    <t>Service kit for Agilent GC instrument, 1-year</t>
-  </si>
-  <si>
     <t>Part Number: 5188-6496</t>
   </si>
   <si>
@@ -1435,9 +1255,6 @@
     <t>GC 7890 için filament montajı (G7005-60061)</t>
   </si>
   <si>
-    <t>Filament Assembly for GC 7890 (G7005-60061)</t>
-  </si>
-  <si>
     <t>Part № G7005-60061</t>
   </si>
   <si>
@@ -1456,9 +1273,6 @@
     <t>Agilent için polimer ayaklı vial insertleri, 100 adet</t>
   </si>
   <si>
-    <t>Vial inserts with polymer feet for Agilent, 100 pcs</t>
-  </si>
-  <si>
     <t>5181-1270</t>
   </si>
   <si>
@@ -1474,9 +1288,6 @@
     <t>Agilent 7890 AP kartı (analog ve güç devresi) (yenilenmiş)</t>
   </si>
   <si>
-    <t>Agilent 7890 AP Board (Analog &amp; power printed circuit) (G3430-61850/G3430-60151/G3430-60150) (Refurbished)</t>
-  </si>
-  <si>
     <t>G3430-60151</t>
   </si>
   <si>
@@ -1489,9 +1300,6 @@
     <t>Agilent GC 7890 sistemi için ana kart</t>
   </si>
   <si>
-    <t>Mainboard for Agilent GC 7890 system</t>
-  </si>
-  <si>
     <t>OEM Reference Number: G1099-65010</t>
   </si>
   <si>
@@ -1507,9 +1315,6 @@
     <t>1290 Infinity II otomatik örnekleyici için servis kiti</t>
   </si>
   <si>
-    <t>Service kit for 1290 Infinity II autosampler</t>
-  </si>
-  <si>
     <t>G7161-68740</t>
   </si>
   <si>
@@ -1522,9 +1327,6 @@
     <t>1260 Infinity II otomatik örnekleyici için servis kiti</t>
   </si>
   <si>
-    <t>Service kit for 1260 Infinity II autosampler</t>
-  </si>
-  <si>
     <t>G1329B</t>
   </si>
   <si>
@@ -1534,9 +1336,6 @@
     <t>1290 Infinity II pompa için servis kiti</t>
   </si>
   <si>
-    <t>Service kit for 1290 Infinity II pump</t>
-  </si>
-  <si>
     <t>G1310-68741</t>
   </si>
   <si>
@@ -1552,9 +1351,6 @@
     <t>1290 Infinity II otomatik örnekleyici için PM kiti</t>
   </si>
   <si>
-    <t>PM kit for 1290 Infinity II autosampler</t>
-  </si>
-  <si>
     <t>G1313-68719</t>
   </si>
   <si>
@@ -1570,9 +1366,6 @@
     <t>Cary 60 için sertifikalı nötr yoğunluk cam filtreler</t>
   </si>
   <si>
-    <t>Certified neutral density glass filters for Cary 60</t>
-  </si>
-  <si>
     <t>Артикул: 218006500</t>
   </si>
   <si>
@@ -1585,9 +1378,6 @@
     <t>GC Headspace için deaktivasyonlu FS kolon, 0,53 mm</t>
   </si>
   <si>
-    <t>Deactivated FS column for GC Headspace, 0.53mm</t>
-  </si>
-  <si>
     <t>Part Number:160-2535-5</t>
   </si>
   <si>
@@ -1603,9 +1393,6 @@
     <t>Agilent Headspace örnekleyici için ferrüller, 0,53 mm</t>
   </si>
   <si>
-    <t>Ferrules for Agilent Headspace sampler, 0.53 mm</t>
-  </si>
-  <si>
     <t>0100-2595</t>
   </si>
   <si>
@@ -1618,9 +1405,6 @@
     <t>Headspace örnekleyici için ferrüller, 0,53 mm</t>
   </si>
   <si>
-    <t>Ferrules for Headspace sampler, 0.53 mm</t>
-  </si>
-  <si>
     <t>Part № 8002-0217</t>
   </si>
   <si>
@@ -1639,9 +1423,6 @@
     <t>Elga deiyonizatör için kartuş (LC-140)</t>
   </si>
   <si>
-    <t>Cartridge (LC-140) for Elga Deionizer</t>
-  </si>
-  <si>
     <t>TR-LC140 Preteatment purelab    Medica &amp;Option7/15</t>
   </si>
   <si>
@@ -1657,9 +1438,6 @@
     <t>Purelab deiyonizatör için kartuş (LC-214)</t>
   </si>
   <si>
-    <t>Cartridge (LC-214) for Purelab Deionizer</t>
-  </si>
-  <si>
     <t>LC-214 ELGA 2-06620</t>
   </si>
   <si>
@@ -1672,9 +1450,6 @@
     <t>Purelab için UV lamba 185/254 nm (LC-210-02)</t>
   </si>
   <si>
-    <t>UV lamp 185/254nm (LC-210-02) for Purelab</t>
-  </si>
-  <si>
     <t>UV lamp 185/254nm LC-210-02</t>
   </si>
   <si>
@@ -1687,9 +1462,6 @@
     <t>Purelab için kompozit hava filtresi (LC 136 M2)</t>
   </si>
   <si>
-    <t>Composite air filter (LC 136 M2) for Purelab</t>
-  </si>
-  <si>
     <t>LC 136 M2  REF: INST36651</t>
   </si>
   <si>
@@ -1708,9 +1480,6 @@
     <t>Purelab için DI kartuş paketi (LC-141)</t>
   </si>
   <si>
-    <t>DI Cartridge pack (LC-141) for Purelab</t>
-  </si>
-  <si>
     <t>TR-LC141 PURELAB &amp; Medica DI Pack</t>
   </si>
   <si>
@@ -1735,9 +1504,6 @@
     <t>İmmünokromatografik test şeritleri (COC, mAMP, BZO)</t>
   </si>
   <si>
-    <t>Immunochromatographic test strips (COC, mAMP, BZO)</t>
-  </si>
-  <si>
     <t>Артикул: 00065752</t>
   </si>
   <si>
@@ -1753,9 +1519,6 @@
     <t>İmmünokromatografik test şeritleri (BAR, MDMA, MTD)</t>
   </si>
   <si>
-    <t>Immunochromatographic test strips (BAR, MDMA, MTD)</t>
-  </si>
-  <si>
     <t>Артикул: 96694</t>
   </si>
   <si>
@@ -1765,22 +1528,13 @@
     <t>İmmünokromatografik test şeritleri (sentetik kannabinoidler)</t>
   </si>
   <si>
-    <t>Immunochromatographic test strips (Synthetic cannabinoids)</t>
-  </si>
-  <si>
     <t>Артикул: 100299</t>
   </si>
   <si>
     <t>İmmünokromatografik test şeritleri (etanol / ETG)</t>
   </si>
   <si>
-    <t>Immunochromatographic test strips (Ethanol / ETG)</t>
-  </si>
-  <si>
     <t>R1-IK-200609-19 raporu için termal kağıt rulosu (57 mm × 10 m, iç çap 12 mm)</t>
-  </si>
-  <si>
-    <t>Roll thermal paper for R1-IK-200609-19 report (57 mm х 10m, вт.12мм.)</t>
   </si>
   <si>
     <t>Thermal paper roll</t>
@@ -2100,9 +1854,6 @@
 For Research, Forensic, or Paternity Use Only. Not intended for any animal or human therapeutic or diagnostic use.</t>
   </si>
   <si>
-    <t>Test for blood stain identification, 30 tests</t>
-  </si>
-  <si>
     <t xml:space="preserve">Test detects the presence of human hemoglobin and D-dimer (a degradation protein found in menstrual blood). This monoclonal antibody test is robust and easy to use in both the laboratory and the field. </t>
   </si>
   <si>
@@ -2470,9 +2221,6 @@
 height: 120,00 mm (+/- 0,2 mm)</t>
   </si>
   <si>
-    <t>Paraffin Plus</t>
-  </si>
-  <si>
     <t>X881</t>
   </si>
   <si>
@@ -2498,9 +2246,6 @@
   </si>
   <si>
     <t>Formalin ≥37% (non-acidic, for histology)</t>
-  </si>
-  <si>
-    <t>Formalin ≥37% (non-acidic, for histology</t>
   </si>
   <si>
     <t>P733</t>
@@ -2605,6 +2350,285 @@
 Power supply: Input: 100–240 V 50–60 Hz Output 24 V DC 7.5 A
 Battery: 33 Wh, up to 40 minutes operational, 2 h standby mode
 Power consumption: Average 40 W</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> POP-4 Polymer for 3500 analyzer</t>
+  </si>
+  <si>
+    <t>Anode Buffer Container for 3500 analyzer</t>
+  </si>
+  <si>
+    <t>Cathode Buffer Container for 3500 analyzer</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Conditioning Reagent for 3500 Genetic Analyzer</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> GeneScan - 600 LIZ laboratory reagent for 3500 analyzer</t>
+  </si>
+  <si>
+    <t>Quantifiler™ Trio DNA Quantification Kit</t>
+  </si>
+  <si>
+    <t>GlobalFiler™ Express PCR Amplification Kit</t>
+  </si>
+  <si>
+    <t>GlobalFiler™ PCR Amplification Kit</t>
+  </si>
+  <si>
+    <t>Prep-n-Go™ Buffer (for buccal swabs)</t>
+  </si>
+  <si>
+    <t>Forensic DNA Extraction Kit, PrepFiler Express™</t>
+  </si>
+  <si>
+    <t>Forensic DNA Extraction Kit, PrepFiler Express BTA™</t>
+  </si>
+  <si>
+    <t>PMB test for blood stain identification</t>
+  </si>
+  <si>
+    <t>Antiserum against human serum proteins</t>
+  </si>
+  <si>
+    <t>Antiserum against porcine serum proteins</t>
+  </si>
+  <si>
+    <t>Antiserum against cattle serum proteins</t>
+  </si>
+  <si>
+    <t>Antiserum against equine serum proteins</t>
+  </si>
+  <si>
+    <t>Antiserum against avian serum proteins</t>
+  </si>
+  <si>
+    <t>Antiserum against dog serum proteins</t>
+  </si>
+  <si>
+    <t>Antiserum against cat serum proteins</t>
+  </si>
+  <si>
+    <t>Anti-M hemagglutinating serum</t>
+  </si>
+  <si>
+    <t>Anti-N hemagglutinating serum</t>
+  </si>
+  <si>
+    <t>Anti-P hemagglutinating serum</t>
+  </si>
+  <si>
+    <t>Anti-A Monoclonal Antibodies for Blood Typing</t>
+  </si>
+  <si>
+    <t>Anti-B Monoclonal Antibodies for Blood Typing</t>
+  </si>
+  <si>
+    <t>Anti-H Monoclonal Antibodies for Blood Typing</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Anti-D monoclonal blood grouping reagent</t>
+  </si>
+  <si>
+    <t>Microtome blades (50pcs/pack)</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Mayer's Hematoxylin 1 L.</t>
+  </si>
+  <si>
+    <t>Eosin water-alcoholic concentrated</t>
+  </si>
+  <si>
+    <t>Reverse Osmosis cartridge for PURELAB Option-R 7/15</t>
+  </si>
+  <si>
+    <t>UV Lamp for PURELAB Option-R</t>
+  </si>
+  <si>
+    <t>Purification Pack for PURELAB Option-R</t>
+  </si>
+  <si>
+    <t>UV Lamp, 185/254 nm</t>
+  </si>
+  <si>
+    <t>Ethyl Alcohol Reagent</t>
+  </si>
+  <si>
+    <t>Alcohol High Control</t>
+  </si>
+  <si>
+    <t>Ethyl Alcohol Low Control</t>
+  </si>
+  <si>
+    <t>Alcohol Negative Calibrator</t>
+  </si>
+  <si>
+    <t>Alcohol Calibrator</t>
+  </si>
+  <si>
+    <t>Ribbon Cartridge (for EPSON ERC-09)</t>
+  </si>
+  <si>
+    <t>Pipette Tips, Filtered, 1000 µL</t>
+  </si>
+  <si>
+    <t>Pipette Tips, Non-Filtered, 1000 µL</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Helium Gas, 50 L  (for Gas Chromatography) </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Argon Gas, 50 L  (for Gas Chromatography) </t>
+  </si>
+  <si>
+    <t>Sodium Chloride, ≥99.5%, 1 kg</t>
+  </si>
+  <si>
+    <t>Ammonium Formate, 100g</t>
+  </si>
+  <si>
+    <t>Formic acid, 99%, 50 ml</t>
+  </si>
+  <si>
+    <t>Buffer Solution, pH 4, 500 mL</t>
+  </si>
+  <si>
+    <t>Buffer solution, pH 10, 500 ml</t>
+  </si>
+  <si>
+    <t>Electrolytic Cell Block (for Hydrogen Trace Generator)</t>
+  </si>
+  <si>
+    <t>Electrolytic Cell Block (for Precision Hydrogen Trace Generator)</t>
+  </si>
+  <si>
+    <t>Service Kit (for Precision Hydrogen Trace)</t>
+  </si>
+  <si>
+    <t>Service Kit II (for Precision Hydrogen Trace)</t>
+  </si>
+  <si>
+    <t>Blood Alcohol Standard sample, 10 ml</t>
+  </si>
+  <si>
+    <t>Ethanol calibration Solution, 10 x 1.2 mL</t>
+  </si>
+  <si>
+    <t>Ethanol calibration Solution</t>
+  </si>
+  <si>
+    <t>Urine Containers, 100 mL, 500 pcs/pack</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Vacuum tubes, 4 ml, 1200 pcs</t>
+  </si>
+  <si>
+    <t>Service Kit for LC System</t>
+  </si>
+  <si>
+    <t>Service kit (including Jet Clean)</t>
+  </si>
+  <si>
+    <t>Service Kit (for Agilent GC)</t>
+  </si>
+  <si>
+    <t>Filament Assembly (for GC/MS 7890)</t>
+  </si>
+  <si>
+    <t>Vial Inserts with Polymer Feet, 100 pcs</t>
+  </si>
+  <si>
+    <t>AP Board (for Agilent GC 7890 )</t>
+  </si>
+  <si>
+    <t>Mainboard (for Agilent GC 7890)</t>
+  </si>
+  <si>
+    <t>Service Kit (for 1290 Infinity II autosampler)</t>
+  </si>
+  <si>
+    <t>Service Kit (for 1260 Infinity II autosampler)</t>
+  </si>
+  <si>
+    <t>Service Kit (for Agilent 1290 Infinity II Pump)</t>
+  </si>
+  <si>
+    <t>PM Kit (for 1290 Infinity II Autosampler)</t>
+  </si>
+  <si>
+    <t>Neutral Density Glass Filter Set (for Cary 60)</t>
+  </si>
+  <si>
+    <t>Deactivated FS column, 0.53mm (for GC Headspace)</t>
+  </si>
+  <si>
+    <t>Ferrules, 0.53mm (for Agilent Headspace Sampler)</t>
+  </si>
+  <si>
+    <t>Ferrules, 0.53 mm (for Headspace)</t>
+  </si>
+  <si>
+    <t>Cartridge LC-140 (for Elga Deionizer)</t>
+  </si>
+  <si>
+    <t>Cartridge LC-214 (for Purelab Deionizer)</t>
+  </si>
+  <si>
+    <t>UV Lamp, 185/254nm LC-210-02 (for Purelab)</t>
+  </si>
+  <si>
+    <t>Composite Air Filter LC 136 M2 (for Purelab)</t>
+  </si>
+  <si>
+    <t>DI Cartridge Pack LC-141 (for Purelab)</t>
+  </si>
+  <si>
+    <t>Centrifuge tubes, 15 ml, 500 pcs</t>
+  </si>
+  <si>
+    <t>Immunochromatographic Test Strips (COC, mAMP, BZO)</t>
+  </si>
+  <si>
+    <t>Immunochromatographic Test Strips  (BAR, MDMA, MTD)</t>
+  </si>
+  <si>
+    <t>Immunochromatographic Test Strips (Synthetic cannabinoids)</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Immunochromatographic Test Strips (Ethanol / ETG)</t>
+  </si>
+  <si>
+    <t>Roll thermal paper</t>
+  </si>
+  <si>
+    <t>Immunochromatographic Test Strips (BAR, MDMA, MTD)</t>
+  </si>
+  <si>
+    <t>Paraffin (for histology)</t>
+  </si>
+  <si>
+    <t>Yeni Ambalaj Birimi</t>
+  </si>
+  <si>
+    <t>pack</t>
+  </si>
+  <si>
+    <t>kit</t>
+  </si>
+  <si>
+    <t>mL</t>
+  </si>
+  <si>
+    <t>liter</t>
+  </si>
+  <si>
+    <t>pcs</t>
+  </si>
+  <si>
+    <t>kg</t>
+  </si>
+  <si>
+    <t>set</t>
   </si>
 </sst>
 </file>
@@ -2993,7 +3017,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="74">
+  <cellXfs count="75">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -3181,6 +3205,9 @@
     </xf>
     <xf numFmtId="0" fontId="5" fillId="24" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -3474,7 +3501,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:P102"/>
+  <dimension ref="A1:Q102"/>
   <sheetFormatPr defaultColWidth="8.6640625" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="1" width="5" customWidth="1"/>
@@ -3486,64 +3513,66 @@
     <col min="8" max="8" width="16" customWidth="1"/>
     <col min="9" max="10" width="34" customWidth="1"/>
     <col min="11" max="11" width="16" customWidth="1"/>
-    <col min="12" max="12" width="14" customWidth="1"/>
-    <col min="13" max="13" width="22" customWidth="1"/>
-    <col min="14" max="14" width="34" customWidth="1"/>
-    <col min="15" max="15" width="30" customWidth="1"/>
-    <col min="16" max="16" width="8.6640625" customWidth="1"/>
+    <col min="12" max="13" width="14" customWidth="1"/>
+    <col min="14" max="14" width="22" customWidth="1"/>
+    <col min="15" max="15" width="34" customWidth="1"/>
+    <col min="16" max="16" width="30" customWidth="1"/>
+    <col min="17" max="17" width="8.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:16" ht="13.5" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="2" spans="1:16" ht="37.5" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A2" s="67" t="s">
+    <row r="1" spans="1:17" ht="13.5" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="2" spans="1:17" ht="37.5" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A2" s="68" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="67"/>
-      <c r="C2" s="67"/>
-      <c r="D2" s="67"/>
-      <c r="E2" s="67"/>
-      <c r="F2" s="67"/>
-      <c r="G2" s="67"/>
-      <c r="H2" s="67"/>
-      <c r="I2" s="67"/>
-      <c r="J2" s="67"/>
-      <c r="K2" s="67"/>
-      <c r="L2" s="67"/>
-      <c r="M2" s="67"/>
-      <c r="N2" s="67"/>
-      <c r="O2" s="67"/>
-    </row>
-    <row r="3" spans="1:16" ht="13.5" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="4" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="B2" s="68"/>
+      <c r="C2" s="68"/>
+      <c r="D2" s="68"/>
+      <c r="E2" s="68"/>
+      <c r="F2" s="68"/>
+      <c r="G2" s="68"/>
+      <c r="H2" s="68"/>
+      <c r="I2" s="68"/>
+      <c r="J2" s="68"/>
+      <c r="K2" s="68"/>
+      <c r="L2" s="68"/>
+      <c r="M2" s="68"/>
+      <c r="N2" s="68"/>
+      <c r="O2" s="68"/>
+      <c r="P2" s="68"/>
+    </row>
+    <row r="3" spans="1:17" ht="13.5" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="4" spans="1:17" ht="18" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A4" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="B4" s="68" t="s">
+      <c r="B4" s="69" t="s">
         <v>2</v>
       </c>
-      <c r="C4" s="68"/>
-      <c r="D4" s="68"/>
-      <c r="E4" s="68"/>
-      <c r="F4" s="69" t="s">
+      <c r="C4" s="69"/>
+      <c r="D4" s="69"/>
+      <c r="E4" s="69"/>
+      <c r="F4" s="70" t="s">
         <v>3</v>
       </c>
-      <c r="G4" s="69"/>
-      <c r="H4" s="69"/>
-      <c r="I4" s="69"/>
+      <c r="G4" s="70"/>
+      <c r="H4" s="70"/>
+      <c r="I4" s="70"/>
       <c r="J4" s="61"/>
-      <c r="K4" s="70" t="s">
+      <c r="K4" s="71" t="s">
         <v>4</v>
       </c>
-      <c r="L4" s="70"/>
-      <c r="M4" s="2" t="s">
+      <c r="L4" s="71"/>
+      <c r="M4" s="66"/>
+      <c r="N4" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="N4" s="71" t="s">
+      <c r="O4" s="72" t="s">
         <v>6</v>
       </c>
-      <c r="O4" s="71"/>
-    </row>
-    <row r="5" spans="1:16" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="P4" s="72"/>
+    </row>
+    <row r="5" spans="1:17" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A5" s="3" t="s">
         <v>7</v>
       </c>
@@ -3578,20 +3607,23 @@
       <c r="L5" s="8" t="s">
         <v>17</v>
       </c>
-      <c r="M5" s="9" t="s">
+      <c r="M5" s="8" t="s">
+        <v>717</v>
+      </c>
+      <c r="N5" s="9" t="s">
         <v>18</v>
       </c>
-      <c r="N5" s="10" t="s">
+      <c r="O5" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="O5" s="10" t="s">
+      <c r="P5" s="10" t="s">
         <v>20</v>
       </c>
-      <c r="P5" s="10" t="s">
-        <v>612</v>
-      </c>
-    </row>
-    <row r="6" spans="1:16" ht="24" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="Q5" s="10" t="s">
+        <v>530</v>
+      </c>
+    </row>
+    <row r="6" spans="1:17" ht="24" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A6" s="11" t="s">
         <v>21</v>
       </c>
@@ -3626,17 +3658,18 @@
       <c r="L6" s="11" t="s">
         <v>31</v>
       </c>
-      <c r="M6" s="11" t="s">
+      <c r="M6" s="11"/>
+      <c r="N6" s="11" t="s">
         <v>32</v>
       </c>
-      <c r="N6" s="11" t="s">
+      <c r="O6" s="11" t="s">
         <v>33</v>
       </c>
-      <c r="O6" s="11" t="s">
+      <c r="P6" s="11" t="s">
         <v>34</v>
       </c>
     </row>
-    <row r="7" spans="1:16" ht="52.9" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="7" spans="1:17" ht="52.9" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A7" s="12">
         <v>1</v>
       </c>
@@ -3644,4137 +3677,4424 @@
         <v>79</v>
       </c>
       <c r="C7" s="13" t="s">
+        <v>632</v>
+      </c>
+      <c r="D7" s="14" t="s">
         <v>80</v>
       </c>
-      <c r="D7" s="14" t="s">
+      <c r="E7" s="14" t="s">
         <v>81</v>
-      </c>
-      <c r="E7" s="14" t="s">
-        <v>82</v>
       </c>
       <c r="F7" s="15" t="s">
         <v>76</v>
       </c>
       <c r="G7" s="16" t="s">
+        <v>82</v>
+      </c>
+      <c r="H7" s="16" t="s">
         <v>83</v>
       </c>
-      <c r="H7" s="16" t="s">
+      <c r="I7" s="17" t="s">
+        <v>555</v>
+      </c>
+      <c r="J7" s="17" t="s">
+        <v>556</v>
+      </c>
+      <c r="K7" s="23" t="s">
+        <v>91</v>
+      </c>
+      <c r="L7" s="18" t="s">
         <v>84</v>
       </c>
-      <c r="I7" s="17" t="s">
-        <v>637</v>
-      </c>
-      <c r="J7" s="17" t="s">
-        <v>638</v>
-      </c>
-      <c r="K7" s="18" t="s">
+      <c r="M7" s="18" t="s">
+        <v>718</v>
+      </c>
+      <c r="N7" s="19" t="s">
+        <v>52</v>
+      </c>
+      <c r="O7" s="62" t="s">
         <v>85</v>
       </c>
-      <c r="L7" s="18" t="s">
+      <c r="P7" s="21" t="s">
         <v>86</v>
       </c>
-      <c r="M7" s="19" t="s">
-        <v>52</v>
-      </c>
-      <c r="N7" s="62" t="s">
-        <v>87</v>
-      </c>
-      <c r="O7" s="21" t="s">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="8" spans="1:16" ht="51" customHeight="1" x14ac:dyDescent="0.45">
+    </row>
+    <row r="8" spans="1:17" ht="51" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A8" s="22">
         <v>2</v>
       </c>
       <c r="B8" s="13" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="C8" s="13" t="s">
-        <v>90</v>
+        <v>633</v>
       </c>
       <c r="D8" s="14" t="s">
         <v>50</v>
       </c>
       <c r="E8" s="14" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="F8" s="15" t="s">
         <v>76</v>
       </c>
       <c r="G8" s="16" t="s">
+        <v>89</v>
+      </c>
+      <c r="H8" s="16" t="s">
+        <v>90</v>
+      </c>
+      <c r="I8" s="17" t="s">
+        <v>557</v>
+      </c>
+      <c r="J8" s="17" t="s">
+        <v>560</v>
+      </c>
+      <c r="K8" s="23" t="s">
+        <v>91</v>
+      </c>
+      <c r="L8" s="23" t="s">
         <v>92</v>
       </c>
-      <c r="H8" s="16" t="s">
+      <c r="M8" s="23" t="s">
+        <v>718</v>
+      </c>
+      <c r="N8" s="24" t="s">
+        <v>52</v>
+      </c>
+      <c r="O8" s="63" t="s">
         <v>93</v>
       </c>
-      <c r="I8" s="17" t="s">
-        <v>639</v>
-      </c>
-      <c r="J8" s="17" t="s">
-        <v>642</v>
-      </c>
-      <c r="K8" s="23" t="s">
-        <v>94</v>
-      </c>
-      <c r="L8" s="23" t="s">
-        <v>95</v>
-      </c>
-      <c r="M8" s="24" t="s">
-        <v>52</v>
-      </c>
-      <c r="N8" s="63" t="s">
-        <v>96</v>
-      </c>
-      <c r="O8" s="26" t="s">
-        <v>611</v>
-      </c>
-    </row>
-    <row r="9" spans="1:16" ht="19.5" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="P8" s="26" t="s">
+        <v>529</v>
+      </c>
+    </row>
+    <row r="9" spans="1:17" ht="19.5" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A9" s="12">
         <v>3</v>
       </c>
       <c r="B9" s="13" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="C9" s="13" t="s">
-        <v>98</v>
+        <v>634</v>
       </c>
       <c r="D9" s="14" t="s">
-        <v>99</v>
+        <v>95</v>
       </c>
       <c r="E9" s="14" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="F9" s="15" t="s">
         <v>76</v>
       </c>
       <c r="G9" s="16" t="s">
+        <v>89</v>
+      </c>
+      <c r="H9" s="16" t="s">
+        <v>90</v>
+      </c>
+      <c r="I9" s="17" t="s">
+        <v>558</v>
+      </c>
+      <c r="J9" s="17" t="s">
+        <v>559</v>
+      </c>
+      <c r="K9" s="18" t="s">
+        <v>91</v>
+      </c>
+      <c r="L9" s="18" t="s">
         <v>92</v>
       </c>
-      <c r="H9" s="16" t="s">
-        <v>93</v>
-      </c>
-      <c r="I9" s="17" t="s">
-        <v>640</v>
-      </c>
-      <c r="J9" s="17" t="s">
-        <v>641</v>
-      </c>
-      <c r="K9" s="18" t="s">
-        <v>94</v>
-      </c>
-      <c r="L9" s="18" t="s">
-        <v>95</v>
-      </c>
-      <c r="M9" s="19" t="s">
+      <c r="M9" s="18" t="s">
+        <v>718</v>
+      </c>
+      <c r="N9" s="19" t="s">
         <v>52</v>
       </c>
-      <c r="N9" s="62" t="s">
-        <v>100</v>
-      </c>
-      <c r="O9" s="21" t="s">
-        <v>611</v>
-      </c>
-    </row>
-    <row r="10" spans="1:16" ht="19.5" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="O9" s="62" t="s">
+        <v>96</v>
+      </c>
+      <c r="P9" s="21" t="s">
+        <v>529</v>
+      </c>
+    </row>
+    <row r="10" spans="1:17" ht="19.5" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A10" s="22">
         <v>4</v>
       </c>
       <c r="B10" s="13" t="s">
-        <v>101</v>
+        <v>97</v>
       </c>
       <c r="C10" s="13" t="s">
-        <v>102</v>
+        <v>98</v>
       </c>
       <c r="D10" s="14" t="s">
-        <v>103</v>
+        <v>99</v>
       </c>
       <c r="E10" s="14" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="F10" s="15" t="s">
         <v>76</v>
       </c>
       <c r="G10" s="16" t="s">
+        <v>100</v>
+      </c>
+      <c r="H10" s="16" t="s">
+        <v>101</v>
+      </c>
+      <c r="I10" s="17" t="s">
+        <v>102</v>
+      </c>
+      <c r="J10" s="17" t="s">
+        <v>561</v>
+      </c>
+      <c r="K10" s="23" t="s">
+        <v>103</v>
+      </c>
+      <c r="L10" s="23" t="s">
         <v>104</v>
       </c>
-      <c r="H10" s="16" t="s">
+      <c r="M10" s="23" t="s">
+        <v>718</v>
+      </c>
+      <c r="N10" s="24" t="s">
+        <v>52</v>
+      </c>
+      <c r="O10" s="63" t="s">
         <v>105</v>
       </c>
-      <c r="I10" s="17" t="s">
+      <c r="P10" s="26" t="s">
         <v>106</v>
       </c>
-      <c r="J10" s="17" t="s">
-        <v>643</v>
-      </c>
-      <c r="K10" s="23" t="s">
-        <v>107</v>
-      </c>
-      <c r="L10" s="23" t="s">
-        <v>108</v>
-      </c>
-      <c r="M10" s="24" t="s">
-        <v>52</v>
-      </c>
-      <c r="N10" s="63" t="s">
-        <v>109</v>
-      </c>
-      <c r="O10" s="26" t="s">
-        <v>110</v>
-      </c>
-    </row>
-    <row r="11" spans="1:16" ht="52.15" customHeight="1" x14ac:dyDescent="0.45">
+    </row>
+    <row r="11" spans="1:17" ht="52.15" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A11" s="12">
         <v>5</v>
       </c>
       <c r="B11" s="13" t="s">
-        <v>111</v>
+        <v>107</v>
       </c>
       <c r="C11" s="13" t="s">
-        <v>112</v>
+        <v>635</v>
       </c>
       <c r="D11" s="14" t="s">
-        <v>113</v>
+        <v>108</v>
       </c>
       <c r="E11" s="14" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="F11" s="15" t="s">
         <v>76</v>
       </c>
       <c r="G11" s="16" t="s">
-        <v>114</v>
+        <v>109</v>
       </c>
       <c r="H11" s="16" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="I11" s="17" t="s">
-        <v>115</v>
+        <v>110</v>
       </c>
       <c r="J11" s="17" t="s">
-        <v>644</v>
+        <v>562</v>
       </c>
       <c r="K11" s="18" t="s">
-        <v>94</v>
+        <v>91</v>
       </c>
       <c r="L11" s="18" t="s">
-        <v>116</v>
-      </c>
-      <c r="M11" s="19" t="s">
+        <v>111</v>
+      </c>
+      <c r="M11" s="18" t="s">
+        <v>718</v>
+      </c>
+      <c r="N11" s="19" t="s">
         <v>52</v>
       </c>
-      <c r="N11" s="62" t="s">
-        <v>117</v>
-      </c>
-      <c r="O11" s="21" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="12" spans="1:16" ht="19.5" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="O11" s="62" t="s">
+        <v>112</v>
+      </c>
+      <c r="P11" s="21" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="12" spans="1:17" ht="19.5" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A12" s="22">
         <v>6</v>
       </c>
       <c r="B12" s="13" t="s">
-        <v>119</v>
+        <v>114</v>
       </c>
       <c r="C12" s="13" t="s">
-        <v>120</v>
+        <v>636</v>
       </c>
       <c r="D12" s="14" t="s">
-        <v>121</v>
+        <v>115</v>
       </c>
       <c r="E12" s="14" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="F12" s="15" t="s">
         <v>76</v>
       </c>
       <c r="G12" s="16" t="s">
-        <v>122</v>
+        <v>116</v>
       </c>
       <c r="H12" s="16" t="s">
-        <v>123</v>
+        <v>117</v>
       </c>
       <c r="I12" s="17" t="s">
-        <v>124</v>
+        <v>118</v>
       </c>
       <c r="J12" s="17" t="s">
-        <v>645</v>
+        <v>563</v>
       </c>
       <c r="K12" s="23" t="s">
-        <v>94</v>
+        <v>91</v>
       </c>
       <c r="L12" s="23" t="s">
-        <v>125</v>
-      </c>
-      <c r="M12" s="24" t="s">
+        <v>119</v>
+      </c>
+      <c r="M12" s="23" t="s">
+        <v>718</v>
+      </c>
+      <c r="N12" s="24" t="s">
         <v>52</v>
       </c>
-      <c r="N12" s="63" t="s">
-        <v>126</v>
-      </c>
-      <c r="O12" s="26" t="s">
-        <v>110</v>
-      </c>
-    </row>
-    <row r="13" spans="1:16" ht="19.5" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="O12" s="63" t="s">
+        <v>120</v>
+      </c>
+      <c r="P12" s="26" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="13" spans="1:17" ht="19.5" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A13" s="12">
         <v>7</v>
       </c>
       <c r="B13" s="13" t="s">
-        <v>127</v>
+        <v>121</v>
       </c>
       <c r="C13" s="13" t="s">
-        <v>128</v>
+        <v>637</v>
       </c>
       <c r="D13" s="14" t="s">
-        <v>129</v>
+        <v>122</v>
       </c>
       <c r="E13" s="14" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="F13" s="15" t="s">
         <v>76</v>
       </c>
       <c r="G13" s="16" t="s">
-        <v>130</v>
+        <v>123</v>
       </c>
       <c r="H13" s="16" t="s">
-        <v>131</v>
+        <v>124</v>
       </c>
       <c r="I13" s="17" t="s">
-        <v>132</v>
+        <v>125</v>
       </c>
       <c r="J13" s="17" t="s">
-        <v>646</v>
+        <v>564</v>
       </c>
       <c r="K13" s="18" t="s">
-        <v>133</v>
+        <v>126</v>
       </c>
       <c r="L13" s="18" t="s">
-        <v>134</v>
-      </c>
-      <c r="M13" s="19" t="s">
+        <v>127</v>
+      </c>
+      <c r="M13" s="18" t="s">
+        <v>719</v>
+      </c>
+      <c r="N13" s="19" t="s">
         <v>52</v>
       </c>
-      <c r="N13" s="62" t="s">
-        <v>135</v>
-      </c>
-      <c r="O13" s="21" t="s">
-        <v>136</v>
-      </c>
-    </row>
-    <row r="14" spans="1:16" s="49" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="O13" s="62" t="s">
+        <v>128</v>
+      </c>
+      <c r="P13" s="21" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="14" spans="1:17" s="49" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A14" s="50">
         <v>8</v>
       </c>
       <c r="B14" s="40" t="s">
-        <v>137</v>
+        <v>130</v>
       </c>
       <c r="C14" s="40" t="s">
-        <v>138</v>
+        <v>638</v>
       </c>
       <c r="D14" s="65">
         <v>4476609</v>
       </c>
       <c r="E14" s="41" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="F14" s="42" t="s">
         <v>76</v>
       </c>
       <c r="G14" s="43" t="s">
-        <v>139</v>
+        <v>131</v>
       </c>
       <c r="H14" s="43" t="s">
-        <v>140</v>
+        <v>132</v>
       </c>
       <c r="I14" s="44" t="s">
-        <v>141</v>
+        <v>133</v>
       </c>
       <c r="J14" s="44" t="s">
-        <v>647</v>
+        <v>565</v>
       </c>
       <c r="K14" s="51" t="s">
-        <v>133</v>
+        <v>126</v>
       </c>
       <c r="L14" s="51" t="s">
-        <v>142</v>
-      </c>
-      <c r="M14" s="52" t="s">
+        <v>134</v>
+      </c>
+      <c r="M14" s="51" t="s">
+        <v>719</v>
+      </c>
+      <c r="N14" s="52" t="s">
         <v>52</v>
       </c>
-      <c r="N14" s="64" t="s">
-        <v>143</v>
-      </c>
-      <c r="O14" s="54" t="s">
-        <v>144</v>
-      </c>
-      <c r="P14" s="49" t="s">
-        <v>613</v>
-      </c>
-    </row>
-    <row r="15" spans="1:16" ht="19.5" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="O14" s="64" t="s">
+        <v>135</v>
+      </c>
+      <c r="P14" s="54" t="s">
+        <v>136</v>
+      </c>
+      <c r="Q14" s="49" t="s">
+        <v>531</v>
+      </c>
+    </row>
+    <row r="15" spans="1:17" ht="19.5" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A15" s="12">
         <v>9</v>
       </c>
       <c r="B15" s="13" t="s">
-        <v>145</v>
+        <v>137</v>
       </c>
       <c r="C15" s="13" t="s">
-        <v>146</v>
+        <v>639</v>
       </c>
       <c r="D15" s="14" t="s">
-        <v>147</v>
+        <v>138</v>
       </c>
       <c r="E15" s="14" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="F15" s="15" t="s">
         <v>76</v>
       </c>
       <c r="G15" s="16" t="s">
+        <v>131</v>
+      </c>
+      <c r="H15" s="16" t="s">
+        <v>132</v>
+      </c>
+      <c r="I15" s="17" t="s">
         <v>139</v>
       </c>
-      <c r="H15" s="16" t="s">
+      <c r="J15" s="17" t="s">
+        <v>566</v>
+      </c>
+      <c r="K15" s="18" t="s">
+        <v>126</v>
+      </c>
+      <c r="L15" s="18" t="s">
+        <v>134</v>
+      </c>
+      <c r="M15" s="18" t="s">
+        <v>719</v>
+      </c>
+      <c r="N15" s="19" t="s">
+        <v>52</v>
+      </c>
+      <c r="O15" s="62" t="s">
         <v>140</v>
       </c>
-      <c r="I15" s="17" t="s">
-        <v>148</v>
-      </c>
-      <c r="J15" s="17" t="s">
-        <v>648</v>
-      </c>
-      <c r="K15" s="18" t="s">
-        <v>133</v>
-      </c>
-      <c r="L15" s="18" t="s">
-        <v>142</v>
-      </c>
-      <c r="M15" s="19" t="s">
-        <v>52</v>
-      </c>
-      <c r="N15" s="62" t="s">
-        <v>149</v>
-      </c>
-      <c r="O15" s="21" t="s">
-        <v>144</v>
-      </c>
-    </row>
-    <row r="16" spans="1:16" ht="19.5" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="P15" s="21" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="16" spans="1:17" ht="19.5" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A16" s="22">
         <v>10</v>
       </c>
       <c r="B16" s="13" t="s">
-        <v>150</v>
+        <v>141</v>
       </c>
       <c r="C16" s="13" t="s">
-        <v>151</v>
+        <v>640</v>
       </c>
       <c r="D16" s="14" t="s">
-        <v>152</v>
+        <v>142</v>
       </c>
       <c r="E16" s="14" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="F16" s="15" t="s">
         <v>76</v>
       </c>
       <c r="G16" s="16" t="s">
-        <v>153</v>
+        <v>143</v>
       </c>
       <c r="H16" s="16" t="s">
-        <v>154</v>
+        <v>144</v>
       </c>
       <c r="I16" s="17" t="s">
-        <v>155</v>
+        <v>145</v>
       </c>
       <c r="J16" s="17" t="s">
-        <v>649</v>
+        <v>567</v>
       </c>
       <c r="K16" s="23" t="s">
-        <v>94</v>
+        <v>91</v>
       </c>
       <c r="L16" s="23" t="s">
-        <v>142</v>
-      </c>
-      <c r="M16" s="24" t="s">
+        <v>134</v>
+      </c>
+      <c r="M16" s="23" t="s">
+        <v>718</v>
+      </c>
+      <c r="N16" s="24" t="s">
         <v>52</v>
       </c>
-      <c r="N16" s="63" t="s">
-        <v>156</v>
-      </c>
-      <c r="O16" s="26" t="s">
-        <v>157</v>
-      </c>
-    </row>
-    <row r="17" spans="1:15" ht="19.5" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="O16" s="63" t="s">
+        <v>146</v>
+      </c>
+      <c r="P16" s="26" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="17" spans="1:16" ht="19.5" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A17" s="12">
         <v>11</v>
       </c>
       <c r="B17" s="13" t="s">
-        <v>158</v>
+        <v>148</v>
       </c>
       <c r="C17" s="13" t="s">
-        <v>159</v>
+        <v>641</v>
       </c>
       <c r="D17" s="14" t="s">
-        <v>160</v>
+        <v>149</v>
       </c>
       <c r="E17" s="14" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="F17" s="15" t="s">
         <v>76</v>
       </c>
       <c r="G17" s="16" t="s">
-        <v>161</v>
+        <v>150</v>
       </c>
       <c r="H17" s="16" t="s">
-        <v>162</v>
+        <v>151</v>
       </c>
       <c r="I17" s="17" t="s">
-        <v>163</v>
+        <v>152</v>
       </c>
       <c r="J17" s="17" t="s">
-        <v>650</v>
+        <v>568</v>
       </c>
       <c r="K17" s="18" t="s">
-        <v>133</v>
+        <v>126</v>
       </c>
       <c r="L17" s="18" t="s">
-        <v>164</v>
-      </c>
-      <c r="M17" s="19" t="s">
+        <v>153</v>
+      </c>
+      <c r="M17" s="18" t="s">
+        <v>719</v>
+      </c>
+      <c r="N17" s="19" t="s">
         <v>52</v>
       </c>
-      <c r="N17" s="62" t="s">
-        <v>165</v>
-      </c>
-      <c r="O17" s="21" t="s">
-        <v>166</v>
-      </c>
-    </row>
-    <row r="18" spans="1:15" ht="19.5" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="O17" s="62" t="s">
+        <v>154</v>
+      </c>
+      <c r="P17" s="21" t="s">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="18" spans="1:16" ht="19.5" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A18" s="22">
         <v>12</v>
       </c>
       <c r="B18" s="13" t="s">
-        <v>167</v>
+        <v>156</v>
       </c>
       <c r="C18" s="13" t="s">
-        <v>168</v>
+        <v>642</v>
       </c>
       <c r="D18" s="14" t="s">
-        <v>169</v>
+        <v>157</v>
       </c>
       <c r="E18" s="14" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="F18" s="15" t="s">
         <v>76</v>
       </c>
       <c r="G18" s="16" t="s">
-        <v>161</v>
+        <v>150</v>
       </c>
       <c r="H18" s="16" t="s">
-        <v>162</v>
+        <v>151</v>
       </c>
       <c r="I18" s="17" t="s">
-        <v>170</v>
+        <v>158</v>
       </c>
       <c r="J18" s="17" t="s">
-        <v>651</v>
+        <v>569</v>
       </c>
       <c r="K18" s="23" t="s">
-        <v>133</v>
+        <v>126</v>
       </c>
       <c r="L18" s="23" t="s">
-        <v>164</v>
-      </c>
-      <c r="M18" s="24" t="s">
+        <v>153</v>
+      </c>
+      <c r="M18" s="23" t="s">
+        <v>719</v>
+      </c>
+      <c r="N18" s="24" t="s">
         <v>52</v>
       </c>
-      <c r="N18" s="63" t="s">
-        <v>171</v>
-      </c>
-      <c r="O18" s="26" t="s">
-        <v>166</v>
-      </c>
-    </row>
-    <row r="19" spans="1:15" ht="19.5" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="O18" s="63" t="s">
+        <v>159</v>
+      </c>
+      <c r="P18" s="26" t="s">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="19" spans="1:16" ht="19.5" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A19" s="12">
         <v>13</v>
       </c>
       <c r="B19" s="13" t="s">
-        <v>172</v>
+        <v>160</v>
       </c>
       <c r="C19" s="13" t="s">
-        <v>652</v>
+        <v>643</v>
       </c>
       <c r="D19" s="14" t="s">
-        <v>173</v>
+        <v>161</v>
       </c>
       <c r="E19" s="14" t="s">
-        <v>174</v>
+        <v>162</v>
       </c>
       <c r="F19" s="15" t="s">
         <v>77</v>
       </c>
       <c r="G19" s="16" t="s">
-        <v>175</v>
+        <v>163</v>
       </c>
       <c r="H19" s="16" t="s">
-        <v>176</v>
+        <v>164</v>
       </c>
       <c r="I19" s="17" t="s">
-        <v>653</v>
+        <v>570</v>
       </c>
       <c r="J19" s="17" t="s">
-        <v>654</v>
+        <v>571</v>
       </c>
       <c r="K19" s="18" t="s">
-        <v>94</v>
+        <v>91</v>
       </c>
       <c r="L19" s="18" t="s">
-        <v>177</v>
-      </c>
-      <c r="M19" s="19" t="s">
-        <v>178</v>
-      </c>
-      <c r="N19" s="38"/>
-      <c r="O19" s="21"/>
-    </row>
-    <row r="20" spans="1:15" ht="19.5" customHeight="1" x14ac:dyDescent="0.45">
+        <v>165</v>
+      </c>
+      <c r="M19" s="18" t="s">
+        <v>718</v>
+      </c>
+      <c r="N19" s="19" t="s">
+        <v>166</v>
+      </c>
+      <c r="O19" s="38"/>
+      <c r="P19" s="21"/>
+    </row>
+    <row r="20" spans="1:16" ht="19.5" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A20" s="22">
         <v>14</v>
       </c>
       <c r="B20" s="13" t="s">
-        <v>179</v>
+        <v>167</v>
       </c>
       <c r="C20" s="13" t="s">
-        <v>180</v>
+        <v>644</v>
       </c>
       <c r="D20" s="13" t="s">
-        <v>656</v>
+        <v>573</v>
       </c>
       <c r="E20" s="14" t="s">
-        <v>181</v>
+        <v>168</v>
       </c>
       <c r="F20" s="15" t="s">
         <v>77</v>
       </c>
       <c r="G20" s="16" t="s">
-        <v>182</v>
+        <v>169</v>
       </c>
       <c r="H20" s="16" t="s">
-        <v>183</v>
+        <v>170</v>
       </c>
       <c r="I20" s="17"/>
       <c r="J20" s="17" t="s">
-        <v>655</v>
+        <v>572</v>
       </c>
       <c r="K20" s="23" t="s">
-        <v>107</v>
+        <v>103</v>
       </c>
       <c r="L20" s="23" t="s">
-        <v>184</v>
-      </c>
-      <c r="M20" s="24" t="s">
-        <v>181</v>
-      </c>
-      <c r="N20" s="37"/>
-      <c r="O20" s="26"/>
-    </row>
-    <row r="21" spans="1:15" ht="19.5" customHeight="1" x14ac:dyDescent="0.45">
+        <v>171</v>
+      </c>
+      <c r="M20" s="23" t="s">
+        <v>720</v>
+      </c>
+      <c r="N20" s="24" t="s">
+        <v>168</v>
+      </c>
+      <c r="O20" s="37"/>
+      <c r="P20" s="26"/>
+    </row>
+    <row r="21" spans="1:16" ht="19.5" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A21" s="12">
         <v>15</v>
       </c>
       <c r="B21" s="13" t="s">
-        <v>185</v>
+        <v>172</v>
       </c>
       <c r="C21" s="13" t="s">
-        <v>186</v>
+        <v>645</v>
       </c>
       <c r="D21" s="13" t="s">
-        <v>656</v>
+        <v>573</v>
       </c>
       <c r="E21" s="14" t="s">
-        <v>181</v>
+        <v>168</v>
       </c>
       <c r="F21" s="15" t="s">
         <v>77</v>
       </c>
       <c r="G21" s="16" t="s">
-        <v>182</v>
+        <v>169</v>
       </c>
       <c r="H21" s="16" t="s">
-        <v>187</v>
+        <v>173</v>
       </c>
       <c r="I21" s="17"/>
       <c r="J21" s="17" t="s">
-        <v>657</v>
+        <v>574</v>
       </c>
       <c r="K21" s="18" t="s">
-        <v>107</v>
+        <v>103</v>
       </c>
       <c r="L21" s="18" t="s">
-        <v>188</v>
-      </c>
-      <c r="M21" s="19" t="s">
-        <v>181</v>
-      </c>
-      <c r="N21" s="38"/>
-      <c r="O21" s="21"/>
-    </row>
-    <row r="22" spans="1:15" ht="19.5" customHeight="1" x14ac:dyDescent="0.45">
+        <v>174</v>
+      </c>
+      <c r="M21" s="18" t="s">
+        <v>720</v>
+      </c>
+      <c r="N21" s="19" t="s">
+        <v>168</v>
+      </c>
+      <c r="O21" s="38"/>
+      <c r="P21" s="21"/>
+    </row>
+    <row r="22" spans="1:16" ht="19.5" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A22" s="22">
         <v>16</v>
       </c>
       <c r="B22" s="13" t="s">
-        <v>189</v>
+        <v>175</v>
       </c>
       <c r="C22" s="13" t="s">
-        <v>190</v>
+        <v>646</v>
       </c>
       <c r="D22" s="13" t="s">
-        <v>656</v>
+        <v>573</v>
       </c>
       <c r="E22" s="14" t="s">
-        <v>181</v>
+        <v>168</v>
       </c>
       <c r="F22" s="15" t="s">
         <v>77</v>
       </c>
       <c r="G22" s="16" t="s">
-        <v>182</v>
+        <v>169</v>
       </c>
       <c r="H22" s="16" t="s">
-        <v>191</v>
+        <v>176</v>
       </c>
       <c r="I22" s="17"/>
       <c r="J22" s="17" t="s">
-        <v>658</v>
+        <v>575</v>
       </c>
       <c r="K22" s="23" t="s">
-        <v>107</v>
+        <v>103</v>
       </c>
       <c r="L22" s="23" t="s">
-        <v>192</v>
-      </c>
-      <c r="M22" s="24" t="s">
-        <v>181</v>
-      </c>
-      <c r="N22" s="37"/>
-      <c r="O22" s="26"/>
-    </row>
-    <row r="23" spans="1:15" ht="19.5" customHeight="1" x14ac:dyDescent="0.45">
+        <v>177</v>
+      </c>
+      <c r="M22" s="23" t="s">
+        <v>720</v>
+      </c>
+      <c r="N22" s="24" t="s">
+        <v>168</v>
+      </c>
+      <c r="O22" s="37"/>
+      <c r="P22" s="26"/>
+    </row>
+    <row r="23" spans="1:16" ht="19.5" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A23" s="12">
         <v>17</v>
       </c>
       <c r="B23" s="13" t="s">
-        <v>193</v>
+        <v>178</v>
       </c>
       <c r="C23" s="13" t="s">
-        <v>194</v>
+        <v>647</v>
       </c>
       <c r="D23" s="13" t="s">
-        <v>656</v>
+        <v>573</v>
       </c>
       <c r="E23" s="14" t="s">
-        <v>181</v>
+        <v>168</v>
       </c>
       <c r="F23" s="15" t="s">
         <v>77</v>
       </c>
       <c r="G23" s="16" t="s">
-        <v>182</v>
+        <v>169</v>
       </c>
       <c r="H23" s="16" t="s">
-        <v>187</v>
+        <v>173</v>
       </c>
       <c r="I23" s="17"/>
       <c r="J23" s="17" t="s">
-        <v>659</v>
+        <v>576</v>
       </c>
       <c r="K23" s="18" t="s">
-        <v>107</v>
+        <v>103</v>
       </c>
       <c r="L23" s="18" t="s">
-        <v>188</v>
-      </c>
-      <c r="M23" s="19" t="s">
-        <v>181</v>
-      </c>
-      <c r="N23" s="38"/>
-      <c r="O23" s="21"/>
-    </row>
-    <row r="24" spans="1:15" ht="19.5" customHeight="1" x14ac:dyDescent="0.45">
+        <v>174</v>
+      </c>
+      <c r="M23" s="18" t="s">
+        <v>720</v>
+      </c>
+      <c r="N23" s="19" t="s">
+        <v>168</v>
+      </c>
+      <c r="O23" s="38"/>
+      <c r="P23" s="21"/>
+    </row>
+    <row r="24" spans="1:16" ht="19.5" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A24" s="22">
         <v>18</v>
       </c>
       <c r="B24" s="13" t="s">
-        <v>195</v>
+        <v>179</v>
       </c>
       <c r="C24" s="13" t="s">
-        <v>196</v>
+        <v>648</v>
       </c>
       <c r="D24" s="13" t="s">
-        <v>656</v>
+        <v>573</v>
       </c>
       <c r="E24" s="14" t="s">
-        <v>181</v>
+        <v>168</v>
       </c>
       <c r="F24" s="15" t="s">
         <v>77</v>
       </c>
       <c r="G24" s="16" t="s">
-        <v>182</v>
+        <v>169</v>
       </c>
       <c r="H24" s="16" t="s">
-        <v>197</v>
+        <v>180</v>
       </c>
       <c r="I24" s="17"/>
       <c r="J24" s="17" t="s">
-        <v>660</v>
+        <v>577</v>
       </c>
       <c r="K24" s="23" t="s">
-        <v>107</v>
+        <v>103</v>
       </c>
       <c r="L24" s="23" t="s">
-        <v>198</v>
-      </c>
-      <c r="M24" s="24" t="s">
         <v>181</v>
       </c>
-      <c r="N24" s="37"/>
-      <c r="O24" s="26"/>
-    </row>
-    <row r="25" spans="1:15" ht="19.5" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="M24" s="23" t="s">
+        <v>720</v>
+      </c>
+      <c r="N24" s="24" t="s">
+        <v>168</v>
+      </c>
+      <c r="O24" s="37"/>
+      <c r="P24" s="26"/>
+    </row>
+    <row r="25" spans="1:16" ht="19.5" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A25" s="12">
         <v>19</v>
       </c>
       <c r="B25" s="13" t="s">
-        <v>199</v>
+        <v>182</v>
       </c>
       <c r="C25" s="13" t="s">
-        <v>200</v>
+        <v>649</v>
       </c>
       <c r="D25" s="13" t="s">
-        <v>656</v>
+        <v>573</v>
       </c>
       <c r="E25" s="14" t="s">
-        <v>181</v>
+        <v>168</v>
       </c>
       <c r="F25" s="15" t="s">
         <v>77</v>
       </c>
       <c r="G25" s="16" t="s">
-        <v>182</v>
+        <v>169</v>
       </c>
       <c r="H25" s="16" t="s">
-        <v>201</v>
+        <v>183</v>
       </c>
       <c r="I25" s="17"/>
       <c r="J25" s="17" t="s">
-        <v>661</v>
+        <v>578</v>
       </c>
       <c r="K25" s="18" t="s">
-        <v>107</v>
+        <v>103</v>
       </c>
       <c r="L25" s="18" t="s">
-        <v>108</v>
-      </c>
-      <c r="M25" s="19" t="s">
-        <v>181</v>
-      </c>
-      <c r="N25" s="38"/>
-      <c r="O25" s="21"/>
-    </row>
-    <row r="26" spans="1:15" ht="19.5" customHeight="1" x14ac:dyDescent="0.45">
+        <v>104</v>
+      </c>
+      <c r="M25" s="18" t="s">
+        <v>720</v>
+      </c>
+      <c r="N25" s="19" t="s">
+        <v>168</v>
+      </c>
+      <c r="O25" s="38"/>
+      <c r="P25" s="21"/>
+    </row>
+    <row r="26" spans="1:16" ht="19.5" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A26" s="22">
         <v>20</v>
       </c>
       <c r="B26" s="13" t="s">
-        <v>202</v>
+        <v>184</v>
       </c>
       <c r="C26" s="13" t="s">
-        <v>203</v>
+        <v>650</v>
       </c>
       <c r="D26" s="13" t="s">
-        <v>656</v>
+        <v>573</v>
       </c>
       <c r="E26" s="14" t="s">
-        <v>181</v>
+        <v>168</v>
       </c>
       <c r="F26" s="15" t="s">
         <v>77</v>
       </c>
       <c r="G26" s="16" t="s">
-        <v>182</v>
+        <v>169</v>
       </c>
       <c r="H26" s="16" t="s">
-        <v>201</v>
+        <v>183</v>
       </c>
       <c r="I26" s="17"/>
       <c r="J26" s="17" t="s">
-        <v>662</v>
+        <v>579</v>
       </c>
       <c r="K26" s="23" t="s">
-        <v>107</v>
+        <v>103</v>
       </c>
       <c r="L26" s="23" t="s">
-        <v>108</v>
-      </c>
-      <c r="M26" s="24" t="s">
-        <v>181</v>
-      </c>
-      <c r="N26" s="37"/>
-      <c r="O26" s="26"/>
-    </row>
-    <row r="27" spans="1:15" ht="19.5" customHeight="1" x14ac:dyDescent="0.45">
+        <v>104</v>
+      </c>
+      <c r="M26" s="23" t="s">
+        <v>720</v>
+      </c>
+      <c r="N26" s="24" t="s">
+        <v>168</v>
+      </c>
+      <c r="O26" s="37"/>
+      <c r="P26" s="26"/>
+    </row>
+    <row r="27" spans="1:16" ht="19.5" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A27" s="12">
         <v>21</v>
       </c>
       <c r="B27" s="13" t="s">
-        <v>204</v>
+        <v>185</v>
       </c>
       <c r="C27" s="13" t="s">
-        <v>205</v>
+        <v>186</v>
       </c>
       <c r="D27" s="14"/>
       <c r="E27" s="14" t="s">
-        <v>181</v>
+        <v>168</v>
       </c>
       <c r="F27" s="15" t="s">
         <v>77</v>
       </c>
       <c r="G27" s="16" t="s">
-        <v>182</v>
+        <v>169</v>
       </c>
       <c r="H27" s="16" t="s">
-        <v>201</v>
+        <v>183</v>
       </c>
       <c r="I27" s="17"/>
       <c r="J27" s="17"/>
       <c r="K27" s="18" t="s">
-        <v>107</v>
+        <v>103</v>
       </c>
       <c r="L27" s="18" t="s">
-        <v>108</v>
-      </c>
-      <c r="M27" s="19" t="s">
-        <v>181</v>
-      </c>
-      <c r="N27" s="38"/>
-      <c r="O27" s="21"/>
-    </row>
-    <row r="28" spans="1:15" ht="19.5" customHeight="1" x14ac:dyDescent="0.45">
+        <v>104</v>
+      </c>
+      <c r="M27" s="18" t="s">
+        <v>720</v>
+      </c>
+      <c r="N27" s="19" t="s">
+        <v>168</v>
+      </c>
+      <c r="O27" s="38"/>
+      <c r="P27" s="21"/>
+    </row>
+    <row r="28" spans="1:16" ht="19.5" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A28" s="22">
         <v>22</v>
       </c>
       <c r="B28" s="13" t="s">
-        <v>206</v>
+        <v>187</v>
       </c>
       <c r="C28" s="13" t="s">
-        <v>207</v>
+        <v>651</v>
       </c>
       <c r="D28" s="14"/>
       <c r="E28" s="14" t="s">
-        <v>181</v>
+        <v>168</v>
       </c>
       <c r="F28" s="15" t="s">
         <v>77</v>
       </c>
       <c r="G28" s="16" t="s">
-        <v>208</v>
+        <v>188</v>
       </c>
       <c r="H28" s="16" t="s">
-        <v>209</v>
+        <v>189</v>
       </c>
       <c r="I28" s="17"/>
       <c r="J28" s="17"/>
       <c r="K28" s="23" t="s">
-        <v>107</v>
+        <v>103</v>
       </c>
       <c r="L28" s="23" t="s">
-        <v>210</v>
-      </c>
-      <c r="M28" s="24" t="s">
-        <v>181</v>
-      </c>
-      <c r="N28" s="37"/>
-      <c r="O28" s="26"/>
-    </row>
-    <row r="29" spans="1:15" ht="19.5" customHeight="1" x14ac:dyDescent="0.45">
+        <v>190</v>
+      </c>
+      <c r="M28" s="23" t="s">
+        <v>720</v>
+      </c>
+      <c r="N28" s="24" t="s">
+        <v>168</v>
+      </c>
+      <c r="O28" s="37"/>
+      <c r="P28" s="26"/>
+    </row>
+    <row r="29" spans="1:16" ht="19.5" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A29" s="12">
         <v>23</v>
       </c>
       <c r="B29" s="13" t="s">
-        <v>211</v>
+        <v>191</v>
       </c>
       <c r="C29" s="13" t="s">
-        <v>212</v>
+        <v>652</v>
       </c>
       <c r="D29" s="14"/>
       <c r="E29" s="14" t="s">
-        <v>181</v>
+        <v>168</v>
       </c>
       <c r="F29" s="15" t="s">
         <v>77</v>
       </c>
       <c r="G29" s="16" t="s">
-        <v>208</v>
+        <v>188</v>
       </c>
       <c r="H29" s="16" t="s">
-        <v>209</v>
+        <v>189</v>
       </c>
       <c r="I29" s="17"/>
       <c r="J29" s="17"/>
       <c r="K29" s="18" t="s">
-        <v>107</v>
+        <v>103</v>
       </c>
       <c r="L29" s="18" t="s">
-        <v>210</v>
-      </c>
-      <c r="M29" s="19" t="s">
-        <v>181</v>
-      </c>
-      <c r="N29" s="38"/>
-      <c r="O29" s="21"/>
-    </row>
-    <row r="30" spans="1:15" ht="19.5" customHeight="1" x14ac:dyDescent="0.45">
+        <v>190</v>
+      </c>
+      <c r="M29" s="18" t="s">
+        <v>720</v>
+      </c>
+      <c r="N29" s="19" t="s">
+        <v>168</v>
+      </c>
+      <c r="O29" s="38"/>
+      <c r="P29" s="21"/>
+    </row>
+    <row r="30" spans="1:16" ht="19.5" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A30" s="22">
         <v>24</v>
       </c>
       <c r="B30" s="13" t="s">
-        <v>213</v>
+        <v>192</v>
       </c>
       <c r="C30" s="13" t="s">
-        <v>214</v>
+        <v>653</v>
       </c>
       <c r="D30" s="14"/>
       <c r="E30" s="14" t="s">
-        <v>181</v>
+        <v>168</v>
       </c>
       <c r="F30" s="15" t="s">
         <v>77</v>
       </c>
       <c r="G30" s="16" t="s">
-        <v>208</v>
+        <v>188</v>
       </c>
       <c r="H30" s="16" t="s">
-        <v>209</v>
+        <v>189</v>
       </c>
       <c r="I30" s="17"/>
       <c r="J30" s="17"/>
       <c r="K30" s="23" t="s">
-        <v>107</v>
+        <v>103</v>
       </c>
       <c r="L30" s="23" t="s">
-        <v>210</v>
-      </c>
-      <c r="M30" s="24" t="s">
-        <v>181</v>
-      </c>
-      <c r="N30" s="37"/>
-      <c r="O30" s="26"/>
-    </row>
-    <row r="31" spans="1:15" ht="19.5" customHeight="1" x14ac:dyDescent="0.45">
+        <v>190</v>
+      </c>
+      <c r="M30" s="23" t="s">
+        <v>720</v>
+      </c>
+      <c r="N30" s="24" t="s">
+        <v>168</v>
+      </c>
+      <c r="O30" s="37"/>
+      <c r="P30" s="26"/>
+    </row>
+    <row r="31" spans="1:16" ht="19.5" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A31" s="12">
         <v>25</v>
       </c>
       <c r="B31" s="13" t="s">
-        <v>215</v>
+        <v>193</v>
       </c>
       <c r="C31" s="13" t="s">
-        <v>216</v>
+        <v>194</v>
       </c>
       <c r="D31" s="14"/>
       <c r="E31" s="14" t="s">
-        <v>181</v>
+        <v>168</v>
       </c>
       <c r="F31" s="15" t="s">
         <v>77</v>
       </c>
       <c r="G31" s="16" t="s">
-        <v>208</v>
+        <v>188</v>
       </c>
       <c r="H31" s="16" t="s">
-        <v>209</v>
+        <v>189</v>
       </c>
       <c r="I31" s="17"/>
       <c r="J31" s="17"/>
       <c r="K31" s="18" t="s">
-        <v>107</v>
+        <v>103</v>
       </c>
       <c r="L31" s="18" t="s">
-        <v>210</v>
-      </c>
-      <c r="M31" s="19" t="s">
-        <v>181</v>
-      </c>
-      <c r="N31" s="38"/>
-      <c r="O31" s="21"/>
-    </row>
-    <row r="32" spans="1:15" ht="19.5" customHeight="1" x14ac:dyDescent="0.45">
+        <v>190</v>
+      </c>
+      <c r="M31" s="18" t="s">
+        <v>720</v>
+      </c>
+      <c r="N31" s="19" t="s">
+        <v>168</v>
+      </c>
+      <c r="O31" s="38"/>
+      <c r="P31" s="21"/>
+    </row>
+    <row r="32" spans="1:16" ht="19.5" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A32" s="22">
         <v>26</v>
       </c>
       <c r="B32" s="13" t="s">
-        <v>217</v>
+        <v>195</v>
       </c>
       <c r="C32" s="13" t="s">
-        <v>218</v>
+        <v>654</v>
       </c>
       <c r="D32" s="14" t="s">
-        <v>219</v>
+        <v>196</v>
       </c>
       <c r="E32" s="14" t="s">
-        <v>181</v>
+        <v>168</v>
       </c>
       <c r="F32" s="15" t="s">
         <v>77</v>
       </c>
       <c r="G32" s="16" t="s">
-        <v>220</v>
+        <v>197</v>
       </c>
       <c r="H32" s="16" t="s">
-        <v>221</v>
+        <v>198</v>
       </c>
       <c r="I32" s="17"/>
       <c r="J32" s="17"/>
       <c r="K32" s="23" t="s">
-        <v>107</v>
+        <v>103</v>
       </c>
       <c r="L32" s="23" t="s">
-        <v>222</v>
-      </c>
-      <c r="M32" s="24" t="s">
-        <v>181</v>
-      </c>
-      <c r="N32" s="37"/>
-      <c r="O32" s="26"/>
-    </row>
-    <row r="33" spans="1:15" ht="19.5" customHeight="1" x14ac:dyDescent="0.45">
+        <v>199</v>
+      </c>
+      <c r="M32" s="23" t="s">
+        <v>720</v>
+      </c>
+      <c r="N32" s="24" t="s">
+        <v>168</v>
+      </c>
+      <c r="O32" s="37"/>
+      <c r="P32" s="26"/>
+    </row>
+    <row r="33" spans="1:16" ht="19.5" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A33" s="12">
         <v>27</v>
       </c>
       <c r="B33" s="13" t="s">
-        <v>223</v>
+        <v>200</v>
       </c>
       <c r="C33" s="13" t="s">
-        <v>224</v>
+        <v>655</v>
       </c>
       <c r="D33" s="14" t="s">
-        <v>219</v>
+        <v>196</v>
       </c>
       <c r="E33" s="14" t="s">
-        <v>181</v>
+        <v>168</v>
       </c>
       <c r="F33" s="15" t="s">
         <v>77</v>
       </c>
       <c r="G33" s="16" t="s">
-        <v>220</v>
+        <v>197</v>
       </c>
       <c r="H33" s="16" t="s">
-        <v>221</v>
+        <v>198</v>
       </c>
       <c r="I33" s="17"/>
       <c r="J33" s="17"/>
       <c r="K33" s="18" t="s">
-        <v>107</v>
+        <v>103</v>
       </c>
       <c r="L33" s="18" t="s">
-        <v>222</v>
-      </c>
-      <c r="M33" s="19" t="s">
-        <v>181</v>
-      </c>
-      <c r="N33" s="38"/>
-      <c r="O33" s="21"/>
-    </row>
-    <row r="34" spans="1:15" ht="19.5" customHeight="1" x14ac:dyDescent="0.45">
+        <v>199</v>
+      </c>
+      <c r="M33" s="18" t="s">
+        <v>720</v>
+      </c>
+      <c r="N33" s="19" t="s">
+        <v>168</v>
+      </c>
+      <c r="O33" s="38"/>
+      <c r="P33" s="21"/>
+    </row>
+    <row r="34" spans="1:16" ht="19.5" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A34" s="22">
         <v>28</v>
       </c>
       <c r="B34" s="13" t="s">
-        <v>225</v>
+        <v>201</v>
       </c>
       <c r="C34" s="13" t="s">
-        <v>226</v>
+        <v>656</v>
       </c>
       <c r="D34" s="14"/>
       <c r="E34" s="14" t="s">
-        <v>181</v>
+        <v>168</v>
       </c>
       <c r="F34" s="15" t="s">
         <v>77</v>
       </c>
       <c r="G34" s="16" t="s">
-        <v>220</v>
+        <v>197</v>
       </c>
       <c r="H34" s="16" t="s">
-        <v>227</v>
+        <v>202</v>
       </c>
       <c r="I34" s="17"/>
       <c r="J34" s="17"/>
       <c r="K34" s="23" t="s">
-        <v>107</v>
+        <v>103</v>
       </c>
       <c r="L34" s="23" t="s">
-        <v>228</v>
-      </c>
-      <c r="M34" s="24" t="s">
-        <v>181</v>
-      </c>
-      <c r="N34" s="37"/>
-      <c r="O34" s="26"/>
-    </row>
-    <row r="35" spans="1:15" ht="19.5" customHeight="1" x14ac:dyDescent="0.45">
+        <v>203</v>
+      </c>
+      <c r="M34" s="23" t="s">
+        <v>720</v>
+      </c>
+      <c r="N34" s="24" t="s">
+        <v>168</v>
+      </c>
+      <c r="O34" s="37"/>
+      <c r="P34" s="26"/>
+    </row>
+    <row r="35" spans="1:16" ht="19.5" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A35" s="12">
         <v>29</v>
       </c>
       <c r="B35" s="13" t="s">
-        <v>229</v>
+        <v>204</v>
       </c>
       <c r="C35" s="13" t="s">
-        <v>230</v>
+        <v>657</v>
       </c>
       <c r="D35" s="14"/>
       <c r="E35" s="14" t="s">
-        <v>181</v>
+        <v>168</v>
       </c>
       <c r="F35" s="15" t="s">
         <v>77</v>
       </c>
       <c r="G35" s="16" t="s">
-        <v>220</v>
+        <v>197</v>
       </c>
       <c r="H35" s="16" t="s">
-        <v>209</v>
+        <v>189</v>
       </c>
       <c r="I35" s="17"/>
       <c r="J35" s="17"/>
       <c r="K35" s="18" t="s">
-        <v>107</v>
+        <v>103</v>
       </c>
       <c r="L35" s="18" t="s">
-        <v>210</v>
-      </c>
-      <c r="M35" s="19" t="s">
-        <v>181</v>
-      </c>
-      <c r="N35" s="38"/>
-      <c r="O35" s="21"/>
-    </row>
-    <row r="36" spans="1:15" ht="19.5" customHeight="1" x14ac:dyDescent="0.45">
+        <v>190</v>
+      </c>
+      <c r="M35" s="18" t="s">
+        <v>720</v>
+      </c>
+      <c r="N35" s="19" t="s">
+        <v>168</v>
+      </c>
+      <c r="O35" s="38"/>
+      <c r="P35" s="21"/>
+    </row>
+    <row r="36" spans="1:16" ht="19.5" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A36" s="22">
         <v>30</v>
       </c>
       <c r="B36" s="13" t="s">
-        <v>231</v>
+        <v>205</v>
       </c>
       <c r="C36" s="13" t="s">
-        <v>232</v>
+        <v>658</v>
       </c>
       <c r="D36" s="14">
         <v>28407004</v>
       </c>
       <c r="E36" s="14" t="s">
-        <v>233</v>
+        <v>206</v>
       </c>
       <c r="F36" s="15" t="s">
         <v>78</v>
       </c>
       <c r="G36" s="16" t="s">
-        <v>234</v>
+        <v>207</v>
       </c>
       <c r="H36" s="16" t="s">
-        <v>235</v>
+        <v>208</v>
       </c>
       <c r="I36" s="17"/>
       <c r="J36" s="17" t="s">
-        <v>663</v>
+        <v>580</v>
       </c>
       <c r="K36" s="23" t="s">
-        <v>94</v>
+        <v>91</v>
       </c>
       <c r="L36" s="23" t="s">
-        <v>236</v>
-      </c>
-      <c r="M36" s="24" t="s">
-        <v>233</v>
-      </c>
-      <c r="N36" s="37"/>
-      <c r="O36" s="26"/>
-    </row>
-    <row r="37" spans="1:15" ht="19.5" customHeight="1" x14ac:dyDescent="0.45">
+        <v>209</v>
+      </c>
+      <c r="M36" s="23" t="s">
+        <v>718</v>
+      </c>
+      <c r="N36" s="24" t="s">
+        <v>206</v>
+      </c>
+      <c r="O36" s="37"/>
+      <c r="P36" s="26"/>
+    </row>
+    <row r="37" spans="1:16" ht="19.5" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A37" s="12">
         <v>31</v>
       </c>
       <c r="B37" s="13" t="s">
-        <v>237</v>
+        <v>210</v>
       </c>
       <c r="C37" s="13" t="s">
-        <v>238</v>
+        <v>659</v>
       </c>
       <c r="D37" s="14" t="s">
-        <v>239</v>
+        <v>211</v>
       </c>
       <c r="E37" s="14" t="s">
-        <v>240</v>
+        <v>212</v>
       </c>
       <c r="F37" s="15" t="s">
         <v>77</v>
       </c>
       <c r="G37" s="16" t="s">
-        <v>241</v>
+        <v>213</v>
       </c>
       <c r="H37" s="16" t="s">
-        <v>242</v>
+        <v>214</v>
       </c>
       <c r="I37" s="17"/>
       <c r="J37" s="17"/>
       <c r="K37" s="18" t="s">
-        <v>107</v>
+        <v>103</v>
       </c>
       <c r="L37" s="18" t="s">
-        <v>243</v>
-      </c>
-      <c r="M37" s="19" t="s">
-        <v>240</v>
-      </c>
-      <c r="N37" s="38"/>
-      <c r="O37" s="21"/>
-    </row>
-    <row r="38" spans="1:15" ht="19.5" customHeight="1" x14ac:dyDescent="0.45">
+        <v>215</v>
+      </c>
+      <c r="M37" s="18" t="s">
+        <v>721</v>
+      </c>
+      <c r="N37" s="19" t="s">
+        <v>212</v>
+      </c>
+      <c r="O37" s="38"/>
+      <c r="P37" s="21"/>
+    </row>
+    <row r="38" spans="1:16" ht="19.5" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A38" s="22">
         <v>32</v>
       </c>
       <c r="B38" s="13" t="s">
-        <v>244</v>
+        <v>216</v>
       </c>
       <c r="C38" s="13" t="s">
-        <v>245</v>
+        <v>660</v>
       </c>
       <c r="D38" s="14" t="s">
-        <v>246</v>
+        <v>217</v>
       </c>
       <c r="E38" s="14" t="s">
-        <v>240</v>
+        <v>212</v>
       </c>
       <c r="F38" s="15" t="s">
         <v>77</v>
       </c>
       <c r="G38" s="16" t="s">
-        <v>241</v>
+        <v>213</v>
       </c>
       <c r="H38" s="16" t="s">
-        <v>247</v>
+        <v>218</v>
       </c>
       <c r="I38" s="17"/>
       <c r="J38" s="17"/>
       <c r="K38" s="23" t="s">
-        <v>107</v>
+        <v>103</v>
       </c>
       <c r="L38" s="23" t="s">
-        <v>222</v>
-      </c>
-      <c r="M38" s="24" t="s">
-        <v>240</v>
-      </c>
-      <c r="N38" s="37"/>
-      <c r="O38" s="26"/>
-    </row>
-    <row r="39" spans="1:15" ht="52.9" customHeight="1" x14ac:dyDescent="0.45">
+        <v>199</v>
+      </c>
+      <c r="M38" s="23" t="s">
+        <v>721</v>
+      </c>
+      <c r="N38" s="24" t="s">
+        <v>212</v>
+      </c>
+      <c r="O38" s="37"/>
+      <c r="P38" s="26"/>
+    </row>
+    <row r="39" spans="1:16" ht="52.9" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A39" s="12">
         <v>33</v>
       </c>
       <c r="B39" s="13" t="s">
-        <v>248</v>
+        <v>219</v>
       </c>
       <c r="C39" s="13" t="s">
-        <v>249</v>
+        <v>661</v>
       </c>
       <c r="D39" s="14" t="s">
-        <v>250</v>
+        <v>220</v>
       </c>
       <c r="E39" s="14" t="s">
-        <v>251</v>
+        <v>221</v>
       </c>
       <c r="F39" s="15" t="s">
         <v>75</v>
       </c>
       <c r="G39" s="16" t="s">
-        <v>252</v>
+        <v>222</v>
       </c>
       <c r="H39" s="16" t="s">
-        <v>253</v>
+        <v>223</v>
       </c>
       <c r="I39" s="17" t="s">
-        <v>254</v>
+        <v>224</v>
       </c>
       <c r="J39" s="17"/>
       <c r="K39" s="18" t="s">
-        <v>255</v>
+        <v>225</v>
       </c>
       <c r="L39" s="18" t="s">
-        <v>116</v>
-      </c>
-      <c r="M39" s="19" t="s">
-        <v>256</v>
-      </c>
-      <c r="N39" s="20" t="s">
-        <v>615</v>
-      </c>
-      <c r="O39" s="21" t="s">
-        <v>257</v>
-      </c>
-    </row>
-    <row r="40" spans="1:15" ht="19.5" customHeight="1" x14ac:dyDescent="0.45">
+        <v>111</v>
+      </c>
+      <c r="M39" s="18" t="s">
+        <v>722</v>
+      </c>
+      <c r="N39" s="19" t="s">
+        <v>226</v>
+      </c>
+      <c r="O39" s="20" t="s">
+        <v>533</v>
+      </c>
+      <c r="P39" s="21" t="s">
+        <v>227</v>
+      </c>
+    </row>
+    <row r="40" spans="1:16" ht="19.5" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A40" s="22">
         <v>34</v>
       </c>
       <c r="B40" s="13" t="s">
-        <v>258</v>
+        <v>228</v>
       </c>
       <c r="C40" s="13" t="s">
-        <v>259</v>
+        <v>662</v>
       </c>
       <c r="D40" s="14" t="s">
-        <v>260</v>
+        <v>229</v>
       </c>
       <c r="E40" s="14" t="s">
-        <v>251</v>
+        <v>221</v>
       </c>
       <c r="F40" s="15" t="s">
         <v>75</v>
       </c>
       <c r="G40" s="16" t="s">
-        <v>261</v>
+        <v>230</v>
       </c>
       <c r="H40" s="16" t="s">
-        <v>253</v>
+        <v>223</v>
       </c>
       <c r="I40" s="17" t="s">
-        <v>262</v>
+        <v>231</v>
       </c>
       <c r="J40" s="17"/>
       <c r="K40" s="23" t="s">
-        <v>263</v>
+        <v>232</v>
       </c>
       <c r="L40" s="23" t="s">
-        <v>116</v>
-      </c>
-      <c r="M40" s="24" t="s">
-        <v>256</v>
-      </c>
-      <c r="N40" s="25" t="s">
-        <v>615</v>
-      </c>
-      <c r="O40" s="26" t="s">
-        <v>552</v>
-      </c>
-    </row>
-    <row r="41" spans="1:15" ht="19.5" customHeight="1" x14ac:dyDescent="0.45">
+        <v>111</v>
+      </c>
+      <c r="M40" s="23" t="s">
+        <v>722</v>
+      </c>
+      <c r="N40" s="24" t="s">
+        <v>226</v>
+      </c>
+      <c r="O40" s="25" t="s">
+        <v>533</v>
+      </c>
+      <c r="P40" s="26" t="s">
+        <v>476</v>
+      </c>
+    </row>
+    <row r="41" spans="1:16" ht="19.5" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A41" s="12">
         <v>35</v>
       </c>
       <c r="B41" s="13" t="s">
-        <v>264</v>
+        <v>233</v>
       </c>
       <c r="C41" s="13" t="s">
-        <v>265</v>
+        <v>663</v>
       </c>
       <c r="D41" s="14" t="s">
-        <v>266</v>
+        <v>234</v>
       </c>
       <c r="E41" s="14" t="s">
-        <v>251</v>
+        <v>221</v>
       </c>
       <c r="F41" s="15" t="s">
         <v>75</v>
       </c>
       <c r="G41" s="16" t="s">
-        <v>267</v>
+        <v>235</v>
       </c>
       <c r="H41" s="16" t="s">
-        <v>268</v>
+        <v>236</v>
       </c>
       <c r="I41" s="17" t="s">
-        <v>269</v>
+        <v>237</v>
       </c>
       <c r="J41" s="17"/>
       <c r="K41" s="18" t="s">
-        <v>94</v>
+        <v>91</v>
       </c>
       <c r="L41" s="18" t="s">
-        <v>116</v>
-      </c>
-      <c r="M41" s="19" t="s">
-        <v>256</v>
-      </c>
-      <c r="N41" s="20" t="s">
-        <v>614</v>
-      </c>
-      <c r="O41" s="21" t="s">
-        <v>270</v>
-      </c>
-    </row>
-    <row r="42" spans="1:15" ht="19.5" customHeight="1" x14ac:dyDescent="0.45">
+        <v>111</v>
+      </c>
+      <c r="M41" s="18" t="s">
+        <v>722</v>
+      </c>
+      <c r="N41" s="19" t="s">
+        <v>226</v>
+      </c>
+      <c r="O41" s="20" t="s">
+        <v>532</v>
+      </c>
+      <c r="P41" s="21" t="s">
+        <v>238</v>
+      </c>
+    </row>
+    <row r="42" spans="1:16" ht="19.5" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A42" s="22">
         <v>36</v>
       </c>
       <c r="B42" s="13" t="s">
-        <v>271</v>
+        <v>239</v>
       </c>
       <c r="C42" s="13" t="s">
-        <v>272</v>
+        <v>664</v>
       </c>
       <c r="D42" s="14" t="s">
-        <v>273</v>
+        <v>240</v>
       </c>
       <c r="E42" s="14" t="s">
-        <v>251</v>
+        <v>221</v>
       </c>
       <c r="F42" s="15" t="s">
         <v>75</v>
       </c>
       <c r="G42" s="16" t="s">
-        <v>261</v>
+        <v>230</v>
       </c>
       <c r="H42" s="16" t="s">
-        <v>268</v>
+        <v>236</v>
       </c>
       <c r="I42" s="17" t="s">
-        <v>274</v>
+        <v>241</v>
       </c>
       <c r="J42" s="17"/>
       <c r="K42" s="23" t="s">
-        <v>263</v>
+        <v>232</v>
       </c>
       <c r="L42" s="23" t="s">
-        <v>116</v>
-      </c>
-      <c r="M42" s="24" t="s">
-        <v>256</v>
-      </c>
-      <c r="N42" s="25" t="s">
-        <v>614</v>
-      </c>
-      <c r="O42" s="26" t="s">
-        <v>616</v>
-      </c>
-    </row>
-    <row r="43" spans="1:15" s="49" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.45">
+        <v>111</v>
+      </c>
+      <c r="M42" s="23" t="s">
+        <v>722</v>
+      </c>
+      <c r="N42" s="24" t="s">
+        <v>226</v>
+      </c>
+      <c r="O42" s="25" t="s">
+        <v>532</v>
+      </c>
+      <c r="P42" s="26" t="s">
+        <v>534</v>
+      </c>
+    </row>
+    <row r="43" spans="1:16" s="49" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A43" s="39">
         <v>37</v>
       </c>
       <c r="B43" s="40" t="s">
-        <v>275</v>
+        <v>242</v>
       </c>
       <c r="C43" s="40" t="s">
-        <v>276</v>
+        <v>243</v>
       </c>
       <c r="D43" s="41" t="s">
-        <v>277</v>
+        <v>244</v>
       </c>
       <c r="E43" s="41" t="s">
-        <v>278</v>
+        <v>245</v>
       </c>
       <c r="F43" s="42" t="s">
         <v>78</v>
       </c>
       <c r="G43" s="43" t="s">
-        <v>279</v>
+        <v>246</v>
       </c>
       <c r="H43" s="43" t="s">
-        <v>280</v>
+        <v>247</v>
       </c>
       <c r="I43" s="44" t="s">
-        <v>281</v>
+        <v>248</v>
       </c>
       <c r="J43" s="44"/>
       <c r="K43" s="45" t="s">
-        <v>107</v>
+        <v>103</v>
       </c>
       <c r="L43" s="45" t="s">
-        <v>116</v>
-      </c>
-      <c r="M43" s="46" t="s">
-        <v>282</v>
-      </c>
-      <c r="N43" s="47" t="s">
-        <v>283</v>
-      </c>
-      <c r="O43" s="48" t="s">
-        <v>284</v>
-      </c>
-    </row>
-    <row r="44" spans="1:15" ht="147.75" customHeight="1" x14ac:dyDescent="0.45">
+        <v>111</v>
+      </c>
+      <c r="M43" s="45" t="s">
+        <v>722</v>
+      </c>
+      <c r="N43" s="46" t="s">
+        <v>249</v>
+      </c>
+      <c r="O43" s="47" t="s">
+        <v>250</v>
+      </c>
+      <c r="P43" s="48" t="s">
+        <v>251</v>
+      </c>
+    </row>
+    <row r="44" spans="1:16" ht="147.75" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A44" s="22">
         <v>38</v>
       </c>
       <c r="B44" s="13" t="s">
-        <v>285</v>
+        <v>252</v>
       </c>
       <c r="C44" s="13" t="s">
-        <v>286</v>
+        <v>665</v>
       </c>
       <c r="D44" s="14" t="s">
-        <v>287</v>
+        <v>253</v>
       </c>
       <c r="E44" s="14" t="s">
-        <v>278</v>
+        <v>245</v>
       </c>
       <c r="F44" s="15" t="s">
         <v>77</v>
       </c>
       <c r="G44" s="16" t="s">
-        <v>288</v>
+        <v>254</v>
       </c>
       <c r="H44" s="16" t="s">
-        <v>289</v>
+        <v>255</v>
       </c>
       <c r="I44" s="17" t="s">
-        <v>290</v>
+        <v>256</v>
       </c>
       <c r="J44" s="17" t="s">
-        <v>664</v>
+        <v>581</v>
       </c>
       <c r="K44" s="23" t="s">
-        <v>107</v>
+        <v>103</v>
       </c>
       <c r="L44" s="23" t="s">
-        <v>291</v>
-      </c>
-      <c r="M44" s="24" t="s">
-        <v>282</v>
-      </c>
-      <c r="N44" s="63" t="s">
-        <v>292</v>
-      </c>
-      <c r="O44" s="26" t="s">
-        <v>293</v>
-      </c>
-    </row>
-    <row r="45" spans="1:15" ht="184.5" customHeight="1" x14ac:dyDescent="0.45">
+        <v>257</v>
+      </c>
+      <c r="M44" s="23" t="s">
+        <v>718</v>
+      </c>
+      <c r="N44" s="24" t="s">
+        <v>249</v>
+      </c>
+      <c r="O44" s="63" t="s">
+        <v>258</v>
+      </c>
+      <c r="P44" s="26" t="s">
+        <v>259</v>
+      </c>
+    </row>
+    <row r="45" spans="1:16" ht="184.5" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A45" s="12">
         <v>39</v>
       </c>
       <c r="B45" s="13" t="s">
-        <v>294</v>
+        <v>260</v>
       </c>
       <c r="C45" s="13" t="s">
-        <v>295</v>
+        <v>666</v>
       </c>
       <c r="D45" s="14" t="s">
-        <v>296</v>
+        <v>261</v>
       </c>
       <c r="E45" s="14" t="s">
-        <v>278</v>
+        <v>245</v>
       </c>
       <c r="F45" s="15" t="s">
         <v>77</v>
       </c>
       <c r="G45" s="16" t="s">
-        <v>297</v>
+        <v>262</v>
       </c>
       <c r="H45" s="16" t="s">
-        <v>154</v>
+        <v>144</v>
       </c>
       <c r="I45" s="17" t="s">
-        <v>298</v>
+        <v>263</v>
       </c>
       <c r="J45" s="17" t="s">
-        <v>665</v>
+        <v>582</v>
       </c>
       <c r="K45" s="18" t="s">
-        <v>299</v>
+        <v>264</v>
       </c>
       <c r="L45" s="18" t="s">
-        <v>300</v>
-      </c>
-      <c r="M45" s="19" t="s">
-        <v>282</v>
-      </c>
-      <c r="N45" s="62" t="s">
-        <v>301</v>
-      </c>
-      <c r="O45" s="21" t="s">
-        <v>302</v>
-      </c>
-    </row>
-    <row r="46" spans="1:15" ht="134.75" customHeight="1" x14ac:dyDescent="0.45">
+        <v>265</v>
+      </c>
+      <c r="M45" s="18" t="s">
+        <v>718</v>
+      </c>
+      <c r="N45" s="19" t="s">
+        <v>249</v>
+      </c>
+      <c r="O45" s="62" t="s">
+        <v>266</v>
+      </c>
+      <c r="P45" s="21" t="s">
+        <v>267</v>
+      </c>
+    </row>
+    <row r="46" spans="1:16" ht="134.75" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A46" s="22">
         <v>40</v>
       </c>
       <c r="B46" s="13" t="s">
-        <v>303</v>
+        <v>268</v>
       </c>
       <c r="C46" s="13" t="s">
-        <v>304</v>
+        <v>667</v>
       </c>
       <c r="D46" s="14" t="s">
-        <v>305</v>
+        <v>269</v>
       </c>
       <c r="E46" s="14" t="s">
-        <v>278</v>
+        <v>245</v>
       </c>
       <c r="F46" s="15" t="s">
         <v>77</v>
       </c>
       <c r="G46" s="16" t="s">
-        <v>297</v>
+        <v>262</v>
       </c>
       <c r="H46" s="16" t="s">
-        <v>154</v>
+        <v>144</v>
       </c>
       <c r="I46" s="17" t="s">
-        <v>306</v>
+        <v>270</v>
       </c>
       <c r="J46" s="17" t="s">
-        <v>666</v>
+        <v>583</v>
       </c>
       <c r="K46" s="23" t="s">
-        <v>299</v>
+        <v>264</v>
       </c>
       <c r="L46" s="23" t="s">
-        <v>300</v>
-      </c>
-      <c r="M46" s="24" t="s">
-        <v>282</v>
-      </c>
-      <c r="N46" s="63" t="s">
-        <v>307</v>
-      </c>
-      <c r="O46" s="26" t="s">
-        <v>308</v>
-      </c>
-    </row>
-    <row r="47" spans="1:15" ht="173.65" customHeight="1" x14ac:dyDescent="0.45">
+        <v>265</v>
+      </c>
+      <c r="M46" s="23" t="s">
+        <v>718</v>
+      </c>
+      <c r="N46" s="24" t="s">
+        <v>249</v>
+      </c>
+      <c r="O46" s="63" t="s">
+        <v>271</v>
+      </c>
+      <c r="P46" s="26" t="s">
+        <v>272</v>
+      </c>
+    </row>
+    <row r="47" spans="1:16" ht="173.65" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A47" s="12">
         <v>41</v>
       </c>
       <c r="B47" s="13" t="s">
-        <v>309</v>
+        <v>273</v>
       </c>
       <c r="C47" s="13" t="s">
-        <v>310</v>
+        <v>668</v>
       </c>
       <c r="D47" s="14" t="s">
-        <v>311</v>
+        <v>274</v>
       </c>
       <c r="E47" s="14" t="s">
-        <v>278</v>
+        <v>245</v>
       </c>
       <c r="F47" s="15" t="s">
         <v>77</v>
       </c>
       <c r="G47" s="16" t="s">
-        <v>312</v>
+        <v>275</v>
       </c>
       <c r="H47" s="16" t="s">
-        <v>154</v>
+        <v>144</v>
       </c>
       <c r="I47" s="17" t="s">
-        <v>313</v>
+        <v>276</v>
       </c>
       <c r="J47" s="17" t="s">
-        <v>667</v>
+        <v>584</v>
       </c>
       <c r="K47" s="18" t="s">
-        <v>299</v>
+        <v>264</v>
       </c>
       <c r="L47" s="18" t="s">
-        <v>300</v>
-      </c>
-      <c r="M47" s="19" t="s">
-        <v>282</v>
-      </c>
-      <c r="N47" s="20" t="s">
-        <v>314</v>
-      </c>
-      <c r="O47" s="21" t="s">
-        <v>315</v>
-      </c>
-    </row>
-    <row r="48" spans="1:15" s="49" customFormat="1" ht="153.4" customHeight="1" x14ac:dyDescent="0.45">
+        <v>265</v>
+      </c>
+      <c r="M47" s="18" t="s">
+        <v>718</v>
+      </c>
+      <c r="N47" s="19" t="s">
+        <v>249</v>
+      </c>
+      <c r="O47" s="20" t="s">
+        <v>277</v>
+      </c>
+      <c r="P47" s="21" t="s">
+        <v>278</v>
+      </c>
+    </row>
+    <row r="48" spans="1:16" s="49" customFormat="1" ht="153.4" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A48" s="50">
         <v>42</v>
       </c>
       <c r="B48" s="40" t="s">
-        <v>316</v>
+        <v>279</v>
       </c>
       <c r="C48" s="40" t="s">
-        <v>317</v>
+        <v>669</v>
       </c>
       <c r="D48" s="41" t="s">
-        <v>318</v>
+        <v>280</v>
       </c>
       <c r="E48" s="41" t="s">
-        <v>319</v>
+        <v>281</v>
       </c>
       <c r="F48" s="42" t="s">
         <v>77</v>
       </c>
       <c r="G48" s="43" t="s">
-        <v>312</v>
+        <v>275</v>
       </c>
       <c r="H48" s="43" t="s">
-        <v>154</v>
+        <v>144</v>
       </c>
       <c r="I48" s="44" t="s">
-        <v>320</v>
+        <v>282</v>
       </c>
       <c r="J48" s="44" t="s">
-        <v>668</v>
+        <v>585</v>
       </c>
       <c r="K48" s="51" t="s">
-        <v>299</v>
+        <v>264</v>
       </c>
       <c r="L48" s="51" t="s">
-        <v>300</v>
-      </c>
-      <c r="M48" s="52" t="s">
-        <v>319</v>
-      </c>
-      <c r="N48" s="53" t="s">
-        <v>321</v>
-      </c>
-      <c r="O48" s="54" t="s">
-        <v>322</v>
-      </c>
-    </row>
-    <row r="49" spans="1:15" ht="19.5" customHeight="1" x14ac:dyDescent="0.45">
+        <v>265</v>
+      </c>
+      <c r="M48" s="51" t="s">
+        <v>718</v>
+      </c>
+      <c r="N48" s="52" t="s">
+        <v>281</v>
+      </c>
+      <c r="O48" s="53" t="s">
+        <v>283</v>
+      </c>
+      <c r="P48" s="54" t="s">
+        <v>284</v>
+      </c>
+    </row>
+    <row r="49" spans="1:16" ht="19.5" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A49" s="12">
         <v>43</v>
       </c>
       <c r="B49" s="13" t="s">
-        <v>323</v>
+        <v>285</v>
       </c>
       <c r="C49" s="13" t="s">
-        <v>324</v>
+        <v>670</v>
       </c>
       <c r="D49" s="14" t="s">
-        <v>325</v>
+        <v>286</v>
       </c>
       <c r="E49" s="14" t="s">
-        <v>326</v>
+        <v>287</v>
       </c>
       <c r="F49" s="15" t="s">
         <v>78</v>
       </c>
       <c r="G49" s="16" t="s">
-        <v>327</v>
+        <v>288</v>
       </c>
       <c r="H49" s="16" t="s">
-        <v>328</v>
+        <v>289</v>
       </c>
       <c r="I49" s="17"/>
       <c r="J49" s="17" t="s">
-        <v>669</v>
+        <v>586</v>
       </c>
       <c r="K49" s="18" t="s">
-        <v>255</v>
+        <v>225</v>
       </c>
       <c r="L49" s="18" t="s">
-        <v>116</v>
-      </c>
-      <c r="M49" s="19" t="s">
-        <v>329</v>
-      </c>
-      <c r="N49" s="38"/>
-      <c r="O49" s="21"/>
-    </row>
-    <row r="50" spans="1:15" ht="19.5" customHeight="1" x14ac:dyDescent="0.45">
+        <v>111</v>
+      </c>
+      <c r="M49" s="18" t="s">
+        <v>718</v>
+      </c>
+      <c r="N49" s="19" t="s">
+        <v>290</v>
+      </c>
+      <c r="O49" s="38"/>
+      <c r="P49" s="21"/>
+    </row>
+    <row r="50" spans="1:16" ht="19.5" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A50" s="22">
         <v>44</v>
       </c>
       <c r="B50" s="13" t="s">
-        <v>330</v>
+        <v>291</v>
       </c>
       <c r="C50" s="13" t="s">
-        <v>331</v>
+        <v>671</v>
       </c>
       <c r="D50" s="14" t="s">
-        <v>332</v>
+        <v>292</v>
       </c>
       <c r="E50" s="14" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="F50" s="15" t="s">
         <v>73</v>
       </c>
       <c r="G50" s="16" t="s">
-        <v>333</v>
+        <v>293</v>
       </c>
       <c r="H50" s="16" t="s">
-        <v>334</v>
+        <v>294</v>
       </c>
       <c r="I50" s="17" t="s">
-        <v>335</v>
+        <v>295</v>
       </c>
       <c r="J50" s="17" t="s">
-        <v>670</v>
+        <v>587</v>
       </c>
       <c r="K50" s="23" t="s">
-        <v>94</v>
+        <v>91</v>
       </c>
       <c r="L50" s="23" t="s">
-        <v>336</v>
-      </c>
-      <c r="M50" s="24" t="s">
+        <v>296</v>
+      </c>
+      <c r="M50" s="23" t="s">
+        <v>718</v>
+      </c>
+      <c r="N50" s="24" t="s">
         <v>52</v>
       </c>
-      <c r="N50" s="25" t="s">
-        <v>337</v>
-      </c>
-      <c r="O50" s="26" t="s">
-        <v>338</v>
-      </c>
-    </row>
-    <row r="51" spans="1:15" ht="19.5" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="O50" s="25" t="s">
+        <v>297</v>
+      </c>
+      <c r="P50" s="26" t="s">
+        <v>298</v>
+      </c>
+    </row>
+    <row r="51" spans="1:16" ht="19.5" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A51" s="12">
         <v>45</v>
       </c>
       <c r="B51" s="13" t="s">
-        <v>339</v>
+        <v>299</v>
       </c>
       <c r="C51" s="13" t="s">
-        <v>340</v>
+        <v>672</v>
       </c>
       <c r="D51" s="14" t="s">
-        <v>341</v>
+        <v>300</v>
       </c>
       <c r="E51" s="14" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="F51" s="15" t="s">
         <v>73</v>
       </c>
       <c r="G51" s="16" t="s">
-        <v>333</v>
+        <v>293</v>
       </c>
       <c r="H51" s="16" t="s">
-        <v>342</v>
+        <v>301</v>
       </c>
       <c r="I51" s="17" t="s">
-        <v>343</v>
+        <v>302</v>
       </c>
       <c r="J51" s="17" t="s">
-        <v>671</v>
+        <v>588</v>
       </c>
       <c r="K51" s="18" t="s">
-        <v>94</v>
+        <v>91</v>
       </c>
       <c r="L51" s="18" t="s">
-        <v>116</v>
-      </c>
-      <c r="M51" s="19" t="s">
+        <v>111</v>
+      </c>
+      <c r="M51" s="18" t="s">
+        <v>718</v>
+      </c>
+      <c r="N51" s="19" t="s">
         <v>52</v>
       </c>
-      <c r="N51" s="20" t="s">
-        <v>344</v>
-      </c>
-      <c r="O51" s="21" t="s">
-        <v>338</v>
-      </c>
-    </row>
-    <row r="52" spans="1:15" ht="19.5" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="O51" s="20" t="s">
+        <v>303</v>
+      </c>
+      <c r="P51" s="21" t="s">
+        <v>298</v>
+      </c>
+    </row>
+    <row r="52" spans="1:16" ht="19.5" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A52" s="22">
         <v>46</v>
       </c>
       <c r="B52" s="13" t="s">
-        <v>345</v>
+        <v>304</v>
       </c>
       <c r="C52" s="13" t="s">
-        <v>346</v>
+        <v>673</v>
       </c>
       <c r="D52" s="14" t="s">
-        <v>347</v>
+        <v>305</v>
       </c>
       <c r="E52" s="14" t="s">
-        <v>348</v>
+        <v>306</v>
       </c>
       <c r="F52" s="15" t="s">
         <v>78</v>
       </c>
       <c r="G52" s="16" t="s">
-        <v>349</v>
+        <v>307</v>
       </c>
       <c r="H52" s="16" t="s">
-        <v>350</v>
+        <v>308</v>
       </c>
       <c r="I52" s="17"/>
       <c r="J52" s="17"/>
       <c r="K52" s="23" t="s">
-        <v>351</v>
+        <v>309</v>
       </c>
       <c r="L52" s="23" t="s">
-        <v>352</v>
-      </c>
-      <c r="M52" s="24" t="s">
-        <v>348</v>
-      </c>
-      <c r="N52" s="37"/>
-      <c r="O52" s="26"/>
-    </row>
-    <row r="53" spans="1:15" ht="19.5" customHeight="1" x14ac:dyDescent="0.45">
+        <v>310</v>
+      </c>
+      <c r="M52" s="23" t="s">
+        <v>722</v>
+      </c>
+      <c r="N52" s="24" t="s">
+        <v>306</v>
+      </c>
+      <c r="O52" s="37"/>
+      <c r="P52" s="26"/>
+    </row>
+    <row r="53" spans="1:16" ht="19.5" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A53" s="12">
         <v>47</v>
       </c>
       <c r="B53" s="13" t="s">
-        <v>353</v>
+        <v>311</v>
       </c>
       <c r="C53" s="13" t="s">
-        <v>354</v>
+        <v>674</v>
       </c>
       <c r="D53" s="14" t="s">
-        <v>355</v>
+        <v>312</v>
       </c>
       <c r="E53" s="14" t="s">
-        <v>348</v>
+        <v>306</v>
       </c>
       <c r="F53" s="15" t="s">
         <v>78</v>
       </c>
       <c r="G53" s="16" t="s">
-        <v>356</v>
+        <v>313</v>
       </c>
       <c r="H53" s="16" t="s">
-        <v>357</v>
+        <v>314</v>
       </c>
       <c r="I53" s="17"/>
       <c r="J53" s="17"/>
       <c r="K53" s="18" t="s">
-        <v>351</v>
+        <v>309</v>
       </c>
       <c r="L53" s="18" t="s">
-        <v>352</v>
-      </c>
-      <c r="M53" s="19" t="s">
-        <v>348</v>
-      </c>
-      <c r="N53" s="38"/>
-      <c r="O53" s="21"/>
-    </row>
-    <row r="54" spans="1:15" ht="19.5" customHeight="1" x14ac:dyDescent="0.45">
+        <v>310</v>
+      </c>
+      <c r="M53" s="18" t="s">
+        <v>722</v>
+      </c>
+      <c r="N53" s="19" t="s">
+        <v>306</v>
+      </c>
+      <c r="O53" s="38"/>
+      <c r="P53" s="21"/>
+    </row>
+    <row r="54" spans="1:16" ht="19.5" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A54" s="22">
         <v>48</v>
       </c>
       <c r="B54" s="13" t="s">
-        <v>358</v>
+        <v>315</v>
       </c>
       <c r="C54" s="13" t="s">
-        <v>359</v>
+        <v>675</v>
       </c>
       <c r="D54" s="14" t="s">
-        <v>360</v>
+        <v>316</v>
       </c>
       <c r="E54" s="14" t="s">
-        <v>361</v>
+        <v>317</v>
       </c>
       <c r="F54" s="15" t="s">
         <v>77</v>
       </c>
       <c r="G54" s="16" t="s">
-        <v>362</v>
+        <v>318</v>
       </c>
       <c r="H54" s="16" t="s">
-        <v>176</v>
+        <v>164</v>
       </c>
       <c r="I54" s="17" t="s">
-        <v>363</v>
+        <v>319</v>
       </c>
       <c r="J54" s="17" t="s">
-        <v>672</v>
+        <v>589</v>
       </c>
       <c r="K54" s="23" t="s">
-        <v>107</v>
+        <v>103</v>
       </c>
       <c r="L54" s="23" t="s">
-        <v>364</v>
-      </c>
-      <c r="M54" s="24" t="s">
-        <v>361</v>
-      </c>
-      <c r="N54" s="25" t="s">
-        <v>365</v>
-      </c>
-      <c r="O54" s="26" t="s">
-        <v>366</v>
-      </c>
-    </row>
-    <row r="55" spans="1:15" ht="19.5" customHeight="1" x14ac:dyDescent="0.45">
+        <v>320</v>
+      </c>
+      <c r="M54" s="23" t="s">
+        <v>718</v>
+      </c>
+      <c r="N54" s="24" t="s">
+        <v>317</v>
+      </c>
+      <c r="O54" s="25" t="s">
+        <v>321</v>
+      </c>
+      <c r="P54" s="26" t="s">
+        <v>322</v>
+      </c>
+    </row>
+    <row r="55" spans="1:16" ht="19.5" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A55" s="12">
         <v>49</v>
       </c>
       <c r="B55" s="13" t="s">
-        <v>367</v>
+        <v>323</v>
       </c>
       <c r="C55" s="13" t="s">
-        <v>368</v>
+        <v>676</v>
       </c>
       <c r="D55" s="14" t="s">
-        <v>369</v>
+        <v>324</v>
       </c>
       <c r="E55" s="14" t="s">
-        <v>361</v>
+        <v>317</v>
       </c>
       <c r="F55" s="15" t="s">
         <v>77</v>
       </c>
       <c r="G55" s="16" t="s">
-        <v>370</v>
+        <v>325</v>
       </c>
       <c r="H55" s="16" t="s">
-        <v>371</v>
+        <v>326</v>
       </c>
       <c r="I55" s="17" t="s">
-        <v>372</v>
+        <v>327</v>
       </c>
       <c r="J55" s="17" t="s">
-        <v>673</v>
+        <v>590</v>
       </c>
       <c r="K55" s="18" t="s">
-        <v>107</v>
+        <v>103</v>
       </c>
       <c r="L55" s="18" t="s">
-        <v>373</v>
-      </c>
-      <c r="M55" s="19" t="s">
-        <v>361</v>
-      </c>
-      <c r="N55" s="20" t="s">
-        <v>617</v>
-      </c>
-      <c r="O55" s="21" t="s">
-        <v>284</v>
-      </c>
-    </row>
-    <row r="56" spans="1:15" ht="19.5" customHeight="1" x14ac:dyDescent="0.45">
+        <v>328</v>
+      </c>
+      <c r="M55" s="18" t="s">
+        <v>718</v>
+      </c>
+      <c r="N55" s="19" t="s">
+        <v>317</v>
+      </c>
+      <c r="O55" s="20" t="s">
+        <v>535</v>
+      </c>
+      <c r="P55" s="21" t="s">
+        <v>251</v>
+      </c>
+    </row>
+    <row r="56" spans="1:16" ht="19.5" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A56" s="22">
         <v>50</v>
       </c>
       <c r="B56" s="13" t="s">
-        <v>374</v>
+        <v>329</v>
       </c>
       <c r="C56" s="13" t="s">
-        <v>375</v>
+        <v>677</v>
       </c>
       <c r="D56" s="14" t="s">
-        <v>376</v>
+        <v>330</v>
       </c>
       <c r="E56" s="14" t="s">
-        <v>361</v>
+        <v>317</v>
       </c>
       <c r="F56" s="15" t="s">
         <v>77</v>
       </c>
       <c r="G56" s="16" t="s">
-        <v>370</v>
+        <v>325</v>
       </c>
       <c r="H56" s="16" t="s">
-        <v>371</v>
+        <v>326</v>
       </c>
       <c r="I56" s="17" t="s">
-        <v>377</v>
+        <v>331</v>
       </c>
       <c r="J56" s="17" t="s">
-        <v>674</v>
+        <v>591</v>
       </c>
       <c r="K56" s="23" t="s">
-        <v>107</v>
+        <v>103</v>
       </c>
       <c r="L56" s="23" t="s">
-        <v>378</v>
-      </c>
-      <c r="M56" s="24" t="s">
-        <v>361</v>
-      </c>
-      <c r="N56" s="25" t="s">
-        <v>618</v>
-      </c>
-      <c r="O56" s="26" t="s">
-        <v>379</v>
-      </c>
-    </row>
-    <row r="57" spans="1:15" ht="19.5" customHeight="1" x14ac:dyDescent="0.45">
+        <v>332</v>
+      </c>
+      <c r="M56" s="23" t="s">
+        <v>718</v>
+      </c>
+      <c r="N56" s="24" t="s">
+        <v>317</v>
+      </c>
+      <c r="O56" s="25" t="s">
+        <v>536</v>
+      </c>
+      <c r="P56" s="26" t="s">
+        <v>333</v>
+      </c>
+    </row>
+    <row r="57" spans="1:16" ht="19.5" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A57" s="12">
         <v>51</v>
       </c>
       <c r="B57" s="13" t="s">
-        <v>380</v>
+        <v>334</v>
       </c>
       <c r="C57" s="13" t="s">
-        <v>381</v>
+        <v>678</v>
       </c>
       <c r="D57" s="14" t="s">
-        <v>382</v>
+        <v>335</v>
       </c>
       <c r="E57" s="14" t="s">
-        <v>361</v>
+        <v>317</v>
       </c>
       <c r="F57" s="15" t="s">
         <v>77</v>
       </c>
       <c r="G57" s="16" t="s">
-        <v>383</v>
+        <v>336</v>
       </c>
       <c r="H57" s="16" t="s">
-        <v>371</v>
+        <v>326</v>
       </c>
       <c r="I57" s="17" t="s">
-        <v>384</v>
+        <v>337</v>
       </c>
       <c r="J57" s="17" t="s">
-        <v>675</v>
+        <v>592</v>
       </c>
       <c r="K57" s="18" t="s">
-        <v>107</v>
+        <v>103</v>
       </c>
       <c r="L57" s="18" t="s">
-        <v>222</v>
-      </c>
-      <c r="M57" s="19" t="s">
-        <v>361</v>
-      </c>
-      <c r="N57" s="20" t="s">
-        <v>619</v>
-      </c>
-      <c r="O57" s="21" t="s">
-        <v>284</v>
-      </c>
-    </row>
-    <row r="58" spans="1:15" ht="19.5" customHeight="1" x14ac:dyDescent="0.45">
+        <v>199</v>
+      </c>
+      <c r="M57" s="18" t="s">
+        <v>718</v>
+      </c>
+      <c r="N57" s="19" t="s">
+        <v>317</v>
+      </c>
+      <c r="O57" s="20" t="s">
+        <v>537</v>
+      </c>
+      <c r="P57" s="21" t="s">
+        <v>251</v>
+      </c>
+    </row>
+    <row r="58" spans="1:16" ht="19.5" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A58" s="22">
         <v>52</v>
       </c>
       <c r="B58" s="13" t="s">
-        <v>385</v>
+        <v>338</v>
       </c>
       <c r="C58" s="13" t="s">
-        <v>386</v>
+        <v>679</v>
       </c>
       <c r="D58" s="14" t="s">
-        <v>387</v>
+        <v>339</v>
       </c>
       <c r="E58" s="14" t="s">
-        <v>361</v>
+        <v>317</v>
       </c>
       <c r="F58" s="15" t="s">
         <v>77</v>
       </c>
       <c r="G58" s="16" t="s">
-        <v>383</v>
+        <v>336</v>
       </c>
       <c r="H58" s="16" t="s">
-        <v>371</v>
+        <v>326</v>
       </c>
       <c r="I58" s="17" t="s">
-        <v>388</v>
+        <v>340</v>
       </c>
       <c r="J58" s="17" t="s">
-        <v>676</v>
+        <v>593</v>
       </c>
       <c r="K58" s="23" t="s">
-        <v>107</v>
+        <v>103</v>
       </c>
       <c r="L58" s="23" t="s">
-        <v>222</v>
-      </c>
-      <c r="M58" s="24" t="s">
-        <v>361</v>
-      </c>
-      <c r="N58" s="25" t="s">
-        <v>620</v>
-      </c>
-      <c r="O58" s="26" t="s">
-        <v>284</v>
-      </c>
-    </row>
-    <row r="59" spans="1:15" ht="19.5" customHeight="1" x14ac:dyDescent="0.45">
+        <v>199</v>
+      </c>
+      <c r="M58" s="23" t="s">
+        <v>718</v>
+      </c>
+      <c r="N58" s="24" t="s">
+        <v>317</v>
+      </c>
+      <c r="O58" s="25" t="s">
+        <v>538</v>
+      </c>
+      <c r="P58" s="26" t="s">
+        <v>251</v>
+      </c>
+    </row>
+    <row r="59" spans="1:16" ht="19.5" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A59" s="55">
         <v>53</v>
       </c>
       <c r="B59" s="56" t="s">
-        <v>389</v>
+        <v>341</v>
       </c>
       <c r="C59" s="56" t="s">
-        <v>390</v>
+        <v>680</v>
       </c>
       <c r="D59" s="56" t="s">
-        <v>391</v>
+        <v>342</v>
       </c>
       <c r="E59" s="57" t="s">
-        <v>392</v>
+        <v>343</v>
       </c>
       <c r="F59" s="58" t="s">
         <v>78</v>
       </c>
       <c r="G59" s="57" t="s">
-        <v>393</v>
+        <v>344</v>
       </c>
       <c r="H59" s="57" t="s">
-        <v>394</v>
+        <v>345</v>
       </c>
       <c r="I59" s="56" t="s">
-        <v>395</v>
+        <v>346</v>
       </c>
       <c r="J59" s="56"/>
       <c r="K59" s="58" t="s">
-        <v>94</v>
+        <v>91</v>
       </c>
       <c r="L59" s="58" t="s">
-        <v>116</v>
-      </c>
-      <c r="M59" s="57" t="s">
-        <v>392</v>
-      </c>
-      <c r="N59" s="59" t="s">
-        <v>626</v>
-      </c>
-      <c r="O59" s="60" t="s">
-        <v>396</v>
-      </c>
-    </row>
-    <row r="60" spans="1:15" ht="19.5" customHeight="1" x14ac:dyDescent="0.45">
+        <v>111</v>
+      </c>
+      <c r="M59" s="58" t="s">
+        <v>722</v>
+      </c>
+      <c r="N59" s="57" t="s">
+        <v>343</v>
+      </c>
+      <c r="O59" s="59" t="s">
+        <v>544</v>
+      </c>
+      <c r="P59" s="60" t="s">
+        <v>347</v>
+      </c>
+    </row>
+    <row r="60" spans="1:16" ht="19.5" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A60" s="55">
         <v>54</v>
       </c>
       <c r="B60" s="56" t="s">
-        <v>397</v>
+        <v>348</v>
       </c>
       <c r="C60" s="56" t="s">
-        <v>398</v>
+        <v>681</v>
       </c>
       <c r="D60" s="57" t="s">
-        <v>399</v>
+        <v>349</v>
       </c>
       <c r="E60" s="57" t="s">
-        <v>392</v>
+        <v>343</v>
       </c>
       <c r="F60" s="58" t="s">
         <v>78</v>
       </c>
       <c r="G60" s="57" t="s">
-        <v>393</v>
+        <v>344</v>
       </c>
       <c r="H60" s="57" t="s">
-        <v>394</v>
+        <v>345</v>
       </c>
       <c r="I60" s="56" t="s">
-        <v>400</v>
+        <v>350</v>
       </c>
       <c r="J60" s="56"/>
       <c r="K60" s="58" t="s">
-        <v>94</v>
+        <v>91</v>
       </c>
       <c r="L60" s="58" t="s">
-        <v>116</v>
-      </c>
-      <c r="M60" s="57" t="s">
-        <v>392</v>
-      </c>
-      <c r="N60" s="59" t="s">
-        <v>626</v>
-      </c>
-      <c r="O60" s="60"/>
-    </row>
-    <row r="61" spans="1:15" ht="19.5" customHeight="1" x14ac:dyDescent="0.45">
+        <v>111</v>
+      </c>
+      <c r="M60" s="58" t="s">
+        <v>722</v>
+      </c>
+      <c r="N60" s="57" t="s">
+        <v>343</v>
+      </c>
+      <c r="O60" s="59" t="s">
+        <v>544</v>
+      </c>
+      <c r="P60" s="60"/>
+    </row>
+    <row r="61" spans="1:16" ht="19.5" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A61" s="55">
         <v>55</v>
       </c>
       <c r="B61" s="56" t="s">
-        <v>401</v>
+        <v>351</v>
       </c>
       <c r="C61" s="56" t="s">
-        <v>402</v>
+        <v>682</v>
       </c>
       <c r="D61" s="57" t="s">
-        <v>403</v>
+        <v>352</v>
       </c>
       <c r="E61" s="57" t="s">
-        <v>392</v>
+        <v>343</v>
       </c>
       <c r="F61" s="58" t="s">
         <v>78</v>
       </c>
       <c r="G61" s="57" t="s">
-        <v>404</v>
+        <v>353</v>
       </c>
       <c r="H61" s="57" t="s">
-        <v>405</v>
+        <v>354</v>
       </c>
       <c r="I61" s="56" t="s">
-        <v>406</v>
+        <v>355</v>
       </c>
       <c r="J61" s="56"/>
       <c r="K61" s="58" t="s">
-        <v>133</v>
+        <v>126</v>
       </c>
       <c r="L61" s="58" t="s">
-        <v>116</v>
-      </c>
-      <c r="M61" s="57" t="s">
-        <v>392</v>
-      </c>
-      <c r="N61" s="59" t="s">
-        <v>626</v>
-      </c>
-      <c r="O61" s="60" t="s">
-        <v>407</v>
-      </c>
-    </row>
-    <row r="62" spans="1:15" ht="19.5" customHeight="1" x14ac:dyDescent="0.45">
+        <v>111</v>
+      </c>
+      <c r="M61" s="58" t="s">
+        <v>719</v>
+      </c>
+      <c r="N61" s="57" t="s">
+        <v>343</v>
+      </c>
+      <c r="O61" s="59" t="s">
+        <v>544</v>
+      </c>
+      <c r="P61" s="60" t="s">
+        <v>356</v>
+      </c>
+    </row>
+    <row r="62" spans="1:16" ht="19.5" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A62" s="55">
         <v>56</v>
       </c>
       <c r="B62" s="56" t="s">
-        <v>408</v>
+        <v>357</v>
       </c>
       <c r="C62" s="56" t="s">
-        <v>409</v>
+        <v>683</v>
       </c>
       <c r="D62" s="57" t="s">
-        <v>410</v>
+        <v>358</v>
       </c>
       <c r="E62" s="57" t="s">
-        <v>392</v>
+        <v>343</v>
       </c>
       <c r="F62" s="58" t="s">
         <v>78</v>
       </c>
       <c r="G62" s="57" t="s">
-        <v>404</v>
+        <v>353</v>
       </c>
       <c r="H62" s="57" t="s">
-        <v>405</v>
+        <v>354</v>
       </c>
       <c r="I62" s="56" t="s">
-        <v>411</v>
+        <v>359</v>
       </c>
       <c r="J62" s="56"/>
       <c r="K62" s="58" t="s">
-        <v>133</v>
+        <v>126</v>
       </c>
       <c r="L62" s="58" t="s">
-        <v>116</v>
-      </c>
-      <c r="M62" s="57" t="s">
-        <v>392</v>
-      </c>
-      <c r="N62" s="59" t="s">
-        <v>626</v>
-      </c>
-      <c r="O62" s="60" t="s">
-        <v>412</v>
-      </c>
-    </row>
-    <row r="63" spans="1:15" ht="19.5" customHeight="1" x14ac:dyDescent="0.45">
+        <v>111</v>
+      </c>
+      <c r="M62" s="58" t="s">
+        <v>719</v>
+      </c>
+      <c r="N62" s="57" t="s">
+        <v>343</v>
+      </c>
+      <c r="O62" s="59" t="s">
+        <v>544</v>
+      </c>
+      <c r="P62" s="60" t="s">
+        <v>360</v>
+      </c>
+    </row>
+    <row r="63" spans="1:16" ht="19.5" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A63" s="12">
         <v>57</v>
       </c>
       <c r="B63" s="13" t="s">
-        <v>413</v>
+        <v>361</v>
       </c>
       <c r="C63" s="13" t="s">
-        <v>414</v>
+        <v>684</v>
       </c>
       <c r="D63" s="14"/>
       <c r="E63" s="14" t="s">
-        <v>415</v>
+        <v>362</v>
       </c>
       <c r="F63" s="15" t="s">
         <v>77</v>
       </c>
       <c r="G63" s="16" t="s">
-        <v>416</v>
+        <v>363</v>
       </c>
       <c r="H63" s="16" t="s">
-        <v>123</v>
+        <v>117</v>
       </c>
       <c r="I63" s="17"/>
       <c r="J63" s="17"/>
       <c r="K63" s="18" t="s">
-        <v>107</v>
+        <v>103</v>
       </c>
       <c r="L63" s="18" t="s">
-        <v>188</v>
-      </c>
-      <c r="M63" s="19" t="s">
-        <v>417</v>
-      </c>
-      <c r="N63" s="38"/>
-      <c r="O63" s="21"/>
-    </row>
-    <row r="64" spans="1:15" ht="127.15" customHeight="1" x14ac:dyDescent="0.45">
+        <v>174</v>
+      </c>
+      <c r="M63" s="18" t="s">
+        <v>718</v>
+      </c>
+      <c r="N63" s="19" t="s">
+        <v>364</v>
+      </c>
+      <c r="O63" s="38"/>
+      <c r="P63" s="21"/>
+    </row>
+    <row r="64" spans="1:16" ht="127.15" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A64" s="22">
         <v>58</v>
       </c>
       <c r="B64" s="13" t="s">
-        <v>418</v>
+        <v>365</v>
       </c>
       <c r="C64" s="13" t="s">
-        <v>419</v>
+        <v>685</v>
       </c>
       <c r="D64" s="14" t="s">
-        <v>420</v>
+        <v>366</v>
       </c>
       <c r="E64" s="14" t="s">
-        <v>415</v>
+        <v>362</v>
       </c>
       <c r="F64" s="15" t="s">
         <v>77</v>
       </c>
       <c r="G64" s="16" t="s">
-        <v>421</v>
+        <v>367</v>
       </c>
       <c r="H64" s="16" t="s">
-        <v>154</v>
+        <v>144</v>
       </c>
       <c r="I64" s="17" t="s">
-        <v>422</v>
+        <v>368</v>
       </c>
       <c r="J64" s="17" t="s">
-        <v>677</v>
+        <v>594</v>
       </c>
       <c r="K64" s="23" t="s">
-        <v>133</v>
+        <v>126</v>
       </c>
       <c r="L64" s="23" t="s">
-        <v>423</v>
-      </c>
-      <c r="M64" s="24" t="s">
-        <v>417</v>
-      </c>
-      <c r="N64" s="25" t="s">
-        <v>621</v>
-      </c>
-      <c r="O64" s="26" t="s">
-        <v>622</v>
-      </c>
-    </row>
-    <row r="65" spans="1:15" ht="19.5" customHeight="1" x14ac:dyDescent="0.45">
+        <v>369</v>
+      </c>
+      <c r="M64" s="23" t="s">
+        <v>718</v>
+      </c>
+      <c r="N64" s="24" t="s">
+        <v>364</v>
+      </c>
+      <c r="O64" s="25" t="s">
+        <v>539</v>
+      </c>
+      <c r="P64" s="26" t="s">
+        <v>540</v>
+      </c>
+    </row>
+    <row r="65" spans="1:16" ht="19.5" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A65" s="12">
         <v>59</v>
       </c>
       <c r="B65" s="13" t="s">
-        <v>424</v>
+        <v>370</v>
       </c>
       <c r="C65" s="13" t="s">
-        <v>425</v>
+        <v>686</v>
       </c>
       <c r="D65" s="14" t="s">
-        <v>426</v>
+        <v>371</v>
       </c>
       <c r="E65" s="14" t="s">
-        <v>415</v>
+        <v>362</v>
       </c>
       <c r="F65" s="15" t="s">
         <v>77</v>
       </c>
       <c r="G65" s="16" t="s">
-        <v>421</v>
+        <v>367</v>
       </c>
       <c r="H65" s="16" t="s">
-        <v>154</v>
+        <v>144</v>
       </c>
       <c r="I65" s="17" t="s">
-        <v>427</v>
+        <v>372</v>
       </c>
       <c r="J65" s="17" t="s">
-        <v>677</v>
+        <v>594</v>
       </c>
       <c r="K65" s="18" t="s">
-        <v>133</v>
+        <v>126</v>
       </c>
       <c r="L65" s="18" t="s">
-        <v>423</v>
-      </c>
-      <c r="M65" s="19" t="s">
-        <v>417</v>
-      </c>
-      <c r="N65" s="20" t="s">
-        <v>623</v>
-      </c>
-      <c r="O65" s="21" t="s">
-        <v>624</v>
-      </c>
-    </row>
-    <row r="66" spans="1:15" s="49" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.45">
+        <v>369</v>
+      </c>
+      <c r="M65" s="18" t="s">
+        <v>718</v>
+      </c>
+      <c r="N65" s="19" t="s">
+        <v>364</v>
+      </c>
+      <c r="O65" s="20" t="s">
+        <v>541</v>
+      </c>
+      <c r="P65" s="21" t="s">
+        <v>542</v>
+      </c>
+    </row>
+    <row r="66" spans="1:16" s="49" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A66" s="50">
         <v>60</v>
       </c>
       <c r="B66" s="40" t="s">
-        <v>428</v>
+        <v>373</v>
       </c>
       <c r="C66" s="40" t="s">
-        <v>429</v>
+        <v>687</v>
       </c>
       <c r="D66" s="41" t="s">
-        <v>430</v>
+        <v>374</v>
       </c>
       <c r="E66" s="41" t="s">
-        <v>431</v>
+        <v>375</v>
       </c>
       <c r="F66" s="42" t="s">
         <v>78</v>
       </c>
       <c r="G66" s="43" t="s">
-        <v>432</v>
+        <v>376</v>
       </c>
       <c r="H66" s="43" t="s">
-        <v>328</v>
+        <v>289</v>
       </c>
       <c r="I66" s="44" t="s">
-        <v>433</v>
+        <v>377</v>
       </c>
       <c r="J66" s="44" t="s">
-        <v>678</v>
+        <v>595</v>
       </c>
       <c r="K66" s="51" t="s">
-        <v>94</v>
+        <v>91</v>
       </c>
       <c r="L66" s="51" t="s">
-        <v>434</v>
-      </c>
-      <c r="M66" s="52" t="s">
-        <v>435</v>
-      </c>
-      <c r="N66" s="53" t="s">
-        <v>436</v>
-      </c>
-      <c r="O66" s="54" t="s">
-        <v>437</v>
-      </c>
-    </row>
-    <row r="67" spans="1:15" ht="19.5" customHeight="1" x14ac:dyDescent="0.45">
+        <v>378</v>
+      </c>
+      <c r="M66" s="51" t="s">
+        <v>718</v>
+      </c>
+      <c r="N66" s="52" t="s">
+        <v>379</v>
+      </c>
+      <c r="O66" s="53" t="s">
+        <v>380</v>
+      </c>
+      <c r="P66" s="54" t="s">
+        <v>381</v>
+      </c>
+    </row>
+    <row r="67" spans="1:16" ht="19.5" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A67" s="12">
         <v>61</v>
       </c>
       <c r="B67" s="13" t="s">
-        <v>438</v>
+        <v>382</v>
       </c>
       <c r="C67" s="13" t="s">
-        <v>439</v>
+        <v>688</v>
       </c>
       <c r="D67" s="14" t="s">
-        <v>440</v>
+        <v>383</v>
       </c>
       <c r="E67" s="14" t="s">
-        <v>441</v>
+        <v>384</v>
       </c>
       <c r="F67" s="15" t="s">
         <v>78</v>
       </c>
       <c r="G67" s="16" t="s">
-        <v>442</v>
+        <v>385</v>
       </c>
       <c r="H67" s="16" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="I67" s="17"/>
       <c r="J67" s="17" t="s">
-        <v>679</v>
+        <v>596</v>
       </c>
       <c r="K67" s="18"/>
       <c r="L67" s="18"/>
-      <c r="M67" s="19" t="s">
-        <v>443</v>
-      </c>
-      <c r="N67" s="38"/>
-      <c r="O67" s="21"/>
-    </row>
-    <row r="68" spans="1:15" ht="19.5" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="M67" s="18" t="s">
+        <v>718</v>
+      </c>
+      <c r="N67" s="19" t="s">
+        <v>386</v>
+      </c>
+      <c r="O67" s="38"/>
+      <c r="P67" s="21"/>
+    </row>
+    <row r="68" spans="1:16" ht="19.5" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A68" s="22">
         <v>62</v>
       </c>
       <c r="B68" s="13" t="s">
-        <v>444</v>
+        <v>387</v>
       </c>
       <c r="C68" s="13" t="s">
-        <v>445</v>
+        <v>689</v>
       </c>
       <c r="D68" s="14" t="s">
-        <v>446</v>
+        <v>388</v>
       </c>
       <c r="E68" s="14" t="s">
-        <v>447</v>
+        <v>389</v>
       </c>
       <c r="F68" s="15" t="s">
         <v>78</v>
       </c>
       <c r="G68" s="16" t="s">
-        <v>448</v>
+        <v>390</v>
       </c>
       <c r="H68" s="16" t="s">
-        <v>405</v>
+        <v>354</v>
       </c>
       <c r="I68" s="17" t="s">
-        <v>449</v>
+        <v>391</v>
       </c>
       <c r="J68" s="17" t="s">
-        <v>680</v>
+        <v>597</v>
       </c>
       <c r="K68" s="23" t="s">
-        <v>133</v>
+        <v>126</v>
       </c>
       <c r="L68" s="23" t="s">
-        <v>116</v>
-      </c>
-      <c r="M68" s="24" t="s">
-        <v>450</v>
-      </c>
-      <c r="N68" s="25" t="s">
-        <v>625</v>
-      </c>
-      <c r="O68" s="26" t="s">
-        <v>451</v>
-      </c>
-    </row>
-    <row r="69" spans="1:15" ht="19.5" customHeight="1" x14ac:dyDescent="0.45">
+        <v>111</v>
+      </c>
+      <c r="M68" s="23" t="s">
+        <v>719</v>
+      </c>
+      <c r="N68" s="24" t="s">
+        <v>392</v>
+      </c>
+      <c r="O68" s="25" t="s">
+        <v>543</v>
+      </c>
+      <c r="P68" s="26" t="s">
+        <v>393</v>
+      </c>
+    </row>
+    <row r="69" spans="1:16" ht="19.5" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A69" s="12">
         <v>63</v>
       </c>
       <c r="B69" s="13" t="s">
-        <v>452</v>
+        <v>394</v>
       </c>
       <c r="C69" s="13" t="s">
-        <v>453</v>
+        <v>690</v>
       </c>
       <c r="D69" s="14" t="s">
-        <v>454</v>
+        <v>395</v>
       </c>
       <c r="E69" s="14" t="s">
-        <v>447</v>
+        <v>389</v>
       </c>
       <c r="F69" s="15" t="s">
         <v>78</v>
       </c>
       <c r="G69" s="16" t="s">
-        <v>448</v>
+        <v>390</v>
       </c>
       <c r="H69" s="16" t="s">
-        <v>405</v>
+        <v>354</v>
       </c>
       <c r="I69" s="17" t="s">
-        <v>455</v>
+        <v>396</v>
       </c>
       <c r="J69" s="17" t="s">
-        <v>681</v>
+        <v>598</v>
       </c>
       <c r="K69" s="18" t="s">
-        <v>133</v>
+        <v>126</v>
       </c>
       <c r="L69" s="18" t="s">
-        <v>116</v>
-      </c>
-      <c r="M69" s="19" t="s">
-        <v>450</v>
-      </c>
-      <c r="N69" s="20" t="s">
-        <v>625</v>
-      </c>
-      <c r="O69" s="21" t="s">
-        <v>451</v>
-      </c>
-    </row>
-    <row r="70" spans="1:15" ht="19.5" customHeight="1" x14ac:dyDescent="0.45">
+        <v>111</v>
+      </c>
+      <c r="M69" s="18" t="s">
+        <v>719</v>
+      </c>
+      <c r="N69" s="19" t="s">
+        <v>392</v>
+      </c>
+      <c r="O69" s="20" t="s">
+        <v>543</v>
+      </c>
+      <c r="P69" s="21" t="s">
+        <v>393</v>
+      </c>
+    </row>
+    <row r="70" spans="1:16" ht="19.5" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A70" s="22">
         <v>64</v>
       </c>
       <c r="B70" s="13" t="s">
-        <v>456</v>
+        <v>397</v>
       </c>
       <c r="C70" s="13" t="s">
-        <v>457</v>
+        <v>691</v>
       </c>
       <c r="D70" s="14" t="s">
-        <v>458</v>
+        <v>398</v>
       </c>
       <c r="E70" s="14" t="s">
-        <v>447</v>
+        <v>389</v>
       </c>
       <c r="F70" s="15" t="s">
         <v>78</v>
       </c>
       <c r="G70" s="16" t="s">
-        <v>459</v>
+        <v>399</v>
       </c>
       <c r="H70" s="16" t="s">
-        <v>405</v>
+        <v>354</v>
       </c>
       <c r="I70" s="17" t="s">
-        <v>460</v>
+        <v>400</v>
       </c>
       <c r="J70" s="17" t="s">
-        <v>681</v>
+        <v>598</v>
       </c>
       <c r="K70" s="23" t="s">
-        <v>133</v>
+        <v>126</v>
       </c>
       <c r="L70" s="23" t="s">
-        <v>116</v>
-      </c>
-      <c r="M70" s="24" t="s">
-        <v>450</v>
-      </c>
-      <c r="N70" s="25" t="s">
-        <v>461</v>
-      </c>
-      <c r="O70" s="26" t="s">
-        <v>451</v>
-      </c>
-    </row>
-    <row r="71" spans="1:15" ht="19.5" customHeight="1" x14ac:dyDescent="0.45">
+        <v>111</v>
+      </c>
+      <c r="M70" s="23" t="s">
+        <v>719</v>
+      </c>
+      <c r="N70" s="24" t="s">
+        <v>392</v>
+      </c>
+      <c r="O70" s="25" t="s">
+        <v>401</v>
+      </c>
+      <c r="P70" s="26" t="s">
+        <v>393</v>
+      </c>
+    </row>
+    <row r="71" spans="1:16" ht="19.5" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A71" s="12">
         <v>65</v>
       </c>
       <c r="B71" s="13" t="s">
-        <v>462</v>
+        <v>402</v>
       </c>
       <c r="C71" s="13" t="s">
-        <v>463</v>
+        <v>692</v>
       </c>
       <c r="D71" s="14" t="s">
-        <v>464</v>
+        <v>403</v>
       </c>
       <c r="E71" s="14" t="s">
-        <v>447</v>
+        <v>389</v>
       </c>
       <c r="F71" s="15" t="s">
         <v>78</v>
       </c>
       <c r="G71" s="16" t="s">
-        <v>465</v>
+        <v>404</v>
       </c>
       <c r="H71" s="16" t="s">
-        <v>154</v>
+        <v>144</v>
       </c>
       <c r="I71" s="17" t="s">
-        <v>466</v>
+        <v>405</v>
       </c>
       <c r="J71" s="17" t="s">
-        <v>682</v>
+        <v>599</v>
       </c>
       <c r="K71" s="18" t="s">
-        <v>94</v>
+        <v>91</v>
       </c>
       <c r="L71" s="18" t="s">
-        <v>116</v>
-      </c>
-      <c r="M71" s="19" t="s">
-        <v>450</v>
-      </c>
-      <c r="N71" s="20" t="s">
-        <v>467</v>
-      </c>
-      <c r="O71" s="21" t="s">
-        <v>468</v>
-      </c>
-    </row>
-    <row r="72" spans="1:15" ht="19.5" customHeight="1" x14ac:dyDescent="0.45">
+        <v>111</v>
+      </c>
+      <c r="M71" s="18" t="s">
+        <v>718</v>
+      </c>
+      <c r="N71" s="19" t="s">
+        <v>392</v>
+      </c>
+      <c r="O71" s="20" t="s">
+        <v>406</v>
+      </c>
+      <c r="P71" s="21" t="s">
+        <v>407</v>
+      </c>
+    </row>
+    <row r="72" spans="1:16" ht="19.5" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A72" s="22">
         <v>66</v>
       </c>
       <c r="B72" s="13" t="s">
-        <v>469</v>
+        <v>408</v>
       </c>
       <c r="C72" s="13" t="s">
-        <v>470</v>
+        <v>693</v>
       </c>
       <c r="D72" s="14" t="s">
-        <v>471</v>
+        <v>409</v>
       </c>
       <c r="E72" s="14" t="s">
-        <v>447</v>
+        <v>389</v>
       </c>
       <c r="F72" s="15" t="s">
         <v>78</v>
       </c>
       <c r="G72" s="16" t="s">
-        <v>472</v>
+        <v>410</v>
       </c>
       <c r="H72" s="16" t="s">
-        <v>328</v>
+        <v>289</v>
       </c>
       <c r="I72" s="17" t="s">
-        <v>473</v>
+        <v>411</v>
       </c>
       <c r="J72" s="17" t="s">
-        <v>683</v>
+        <v>600</v>
       </c>
       <c r="K72" s="23" t="s">
-        <v>94</v>
+        <v>91</v>
       </c>
       <c r="L72" s="23" t="s">
-        <v>236</v>
-      </c>
-      <c r="M72" s="24" t="s">
-        <v>450</v>
-      </c>
-      <c r="N72" s="63" t="s">
-        <v>474</v>
-      </c>
-      <c r="O72" s="26"/>
-    </row>
-    <row r="73" spans="1:15" ht="19.5" customHeight="1" x14ac:dyDescent="0.45">
+        <v>209</v>
+      </c>
+      <c r="M72" s="23" t="s">
+        <v>718</v>
+      </c>
+      <c r="N72" s="24" t="s">
+        <v>392</v>
+      </c>
+      <c r="O72" s="63" t="s">
+        <v>412</v>
+      </c>
+      <c r="P72" s="26"/>
+    </row>
+    <row r="73" spans="1:16" ht="19.5" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A73" s="12">
         <v>67</v>
       </c>
       <c r="B73" s="13" t="s">
-        <v>475</v>
+        <v>413</v>
       </c>
       <c r="C73" s="13" t="s">
-        <v>476</v>
+        <v>694</v>
       </c>
       <c r="D73" s="14" t="s">
-        <v>477</v>
+        <v>414</v>
       </c>
       <c r="E73" s="14" t="s">
-        <v>447</v>
+        <v>389</v>
       </c>
       <c r="F73" s="15" t="s">
         <v>78</v>
       </c>
       <c r="G73" s="16" t="s">
-        <v>478</v>
+        <v>415</v>
       </c>
       <c r="H73" s="16" t="s">
-        <v>123</v>
+        <v>117</v>
       </c>
       <c r="I73" s="17" t="s">
-        <v>479</v>
+        <v>416</v>
       </c>
       <c r="J73" s="17" t="s">
-        <v>684</v>
+        <v>601</v>
       </c>
       <c r="K73" s="18" t="s">
-        <v>94</v>
+        <v>91</v>
       </c>
       <c r="L73" s="18" t="s">
-        <v>116</v>
-      </c>
-      <c r="M73" s="19" t="s">
-        <v>450</v>
-      </c>
-      <c r="N73" s="20" t="s">
-        <v>627</v>
-      </c>
-      <c r="O73" s="21" t="s">
-        <v>628</v>
-      </c>
-    </row>
-    <row r="74" spans="1:15" ht="19.5" customHeight="1" x14ac:dyDescent="0.45">
+        <v>111</v>
+      </c>
+      <c r="M73" s="18" t="s">
+        <v>718</v>
+      </c>
+      <c r="N73" s="19" t="s">
+        <v>392</v>
+      </c>
+      <c r="O73" s="20" t="s">
+        <v>545</v>
+      </c>
+      <c r="P73" s="21" t="s">
+        <v>546</v>
+      </c>
+    </row>
+    <row r="74" spans="1:16" ht="19.5" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A74" s="22">
         <v>68</v>
       </c>
       <c r="B74" s="13" t="s">
-        <v>480</v>
+        <v>417</v>
       </c>
       <c r="C74" s="13" t="s">
-        <v>481</v>
+        <v>695</v>
       </c>
       <c r="D74" s="14" t="s">
-        <v>482</v>
+        <v>418</v>
       </c>
       <c r="E74" s="14" t="s">
-        <v>447</v>
+        <v>389</v>
       </c>
       <c r="F74" s="15" t="s">
         <v>78</v>
       </c>
       <c r="G74" s="16" t="s">
-        <v>483</v>
+        <v>419</v>
       </c>
       <c r="H74" s="16" t="s">
-        <v>371</v>
+        <v>326</v>
       </c>
       <c r="I74" s="17" t="s">
-        <v>484</v>
+        <v>420</v>
       </c>
       <c r="J74" s="17" t="s">
-        <v>685</v>
+        <v>602</v>
       </c>
       <c r="K74" s="23" t="s">
-        <v>94</v>
+        <v>91</v>
       </c>
       <c r="L74" s="23" t="s">
-        <v>116</v>
-      </c>
-      <c r="M74" s="24" t="s">
-        <v>450</v>
-      </c>
-      <c r="N74" s="25" t="s">
-        <v>629</v>
-      </c>
-      <c r="O74" s="26" t="s">
-        <v>485</v>
-      </c>
-    </row>
-    <row r="75" spans="1:15" ht="19.5" customHeight="1" x14ac:dyDescent="0.45">
+        <v>111</v>
+      </c>
+      <c r="M74" s="23" t="s">
+        <v>718</v>
+      </c>
+      <c r="N74" s="24" t="s">
+        <v>392</v>
+      </c>
+      <c r="O74" s="25" t="s">
+        <v>547</v>
+      </c>
+      <c r="P74" s="26" t="s">
+        <v>421</v>
+      </c>
+    </row>
+    <row r="75" spans="1:16" ht="19.5" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A75" s="12">
         <v>69</v>
       </c>
       <c r="B75" s="13" t="s">
-        <v>486</v>
+        <v>422</v>
       </c>
       <c r="C75" s="13" t="s">
-        <v>487</v>
+        <v>696</v>
       </c>
       <c r="D75" s="14" t="s">
-        <v>488</v>
+        <v>423</v>
       </c>
       <c r="E75" s="14" t="s">
-        <v>447</v>
+        <v>389</v>
       </c>
       <c r="F75" s="15" t="s">
         <v>78</v>
       </c>
       <c r="G75" s="16" t="s">
-        <v>489</v>
+        <v>424</v>
       </c>
       <c r="H75" s="16" t="s">
-        <v>123</v>
+        <v>117</v>
       </c>
       <c r="I75" s="17" t="s">
-        <v>490</v>
+        <v>425</v>
       </c>
       <c r="J75" s="17" t="s">
-        <v>686</v>
+        <v>603</v>
       </c>
       <c r="K75" s="18" t="s">
-        <v>133</v>
+        <v>126</v>
       </c>
       <c r="L75" s="18" t="s">
-        <v>116</v>
-      </c>
-      <c r="M75" s="19" t="s">
-        <v>450</v>
-      </c>
-      <c r="N75" s="20" t="s">
-        <v>630</v>
-      </c>
-      <c r="O75" s="21" t="s">
-        <v>407</v>
-      </c>
-    </row>
-    <row r="76" spans="1:15" ht="98.25" customHeight="1" x14ac:dyDescent="0.45">
+        <v>111</v>
+      </c>
+      <c r="M75" s="18" t="s">
+        <v>718</v>
+      </c>
+      <c r="N75" s="19" t="s">
+        <v>392</v>
+      </c>
+      <c r="O75" s="20" t="s">
+        <v>548</v>
+      </c>
+      <c r="P75" s="21" t="s">
+        <v>356</v>
+      </c>
+    </row>
+    <row r="76" spans="1:16" ht="98.25" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A76" s="22">
         <v>70</v>
       </c>
       <c r="B76" s="13" t="s">
-        <v>491</v>
+        <v>426</v>
       </c>
       <c r="C76" s="13" t="s">
-        <v>492</v>
+        <v>697</v>
       </c>
       <c r="D76" s="14" t="s">
-        <v>493</v>
+        <v>427</v>
       </c>
       <c r="E76" s="14" t="s">
-        <v>447</v>
+        <v>389</v>
       </c>
       <c r="F76" s="15" t="s">
         <v>78</v>
       </c>
       <c r="G76" s="16" t="s">
-        <v>489</v>
+        <v>424</v>
       </c>
       <c r="H76" s="16" t="s">
-        <v>123</v>
+        <v>117</v>
       </c>
       <c r="I76" s="17" t="s">
-        <v>494</v>
+        <v>428</v>
       </c>
       <c r="J76" s="17" t="s">
-        <v>687</v>
+        <v>604</v>
       </c>
       <c r="K76" s="23" t="s">
-        <v>133</v>
+        <v>126</v>
       </c>
       <c r="L76" s="23" t="s">
-        <v>116</v>
-      </c>
-      <c r="M76" s="24" t="s">
-        <v>450</v>
-      </c>
-      <c r="N76" s="25" t="s">
-        <v>631</v>
-      </c>
-      <c r="O76" s="26" t="s">
-        <v>407</v>
-      </c>
-    </row>
-    <row r="77" spans="1:15" ht="77.75" customHeight="1" x14ac:dyDescent="0.45">
+        <v>111</v>
+      </c>
+      <c r="M76" s="23" t="s">
+        <v>718</v>
+      </c>
+      <c r="N76" s="24" t="s">
+        <v>392</v>
+      </c>
+      <c r="O76" s="25" t="s">
+        <v>549</v>
+      </c>
+      <c r="P76" s="26" t="s">
+        <v>356</v>
+      </c>
+    </row>
+    <row r="77" spans="1:16" ht="77.75" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A77" s="12">
         <v>71</v>
       </c>
       <c r="B77" s="13" t="s">
-        <v>495</v>
+        <v>429</v>
       </c>
       <c r="C77" s="13" t="s">
-        <v>496</v>
+        <v>698</v>
       </c>
       <c r="D77" s="14" t="s">
-        <v>497</v>
+        <v>430</v>
       </c>
       <c r="E77" s="14" t="s">
-        <v>447</v>
+        <v>389</v>
       </c>
       <c r="F77" s="15" t="s">
         <v>78</v>
       </c>
       <c r="G77" s="16" t="s">
-        <v>498</v>
+        <v>431</v>
       </c>
       <c r="H77" s="16" t="s">
-        <v>123</v>
+        <v>117</v>
       </c>
       <c r="I77" s="17" t="s">
-        <v>499</v>
+        <v>432</v>
       </c>
       <c r="J77" s="17" t="s">
-        <v>688</v>
+        <v>605</v>
       </c>
       <c r="K77" s="18" t="s">
-        <v>133</v>
+        <v>126</v>
       </c>
       <c r="L77" s="18" t="s">
-        <v>116</v>
-      </c>
-      <c r="M77" s="19" t="s">
-        <v>450</v>
-      </c>
-      <c r="N77" s="20" t="s">
-        <v>500</v>
-      </c>
-      <c r="O77" s="21" t="s">
-        <v>407</v>
-      </c>
-    </row>
-    <row r="78" spans="1:15" ht="77.75" customHeight="1" x14ac:dyDescent="0.45">
+        <v>111</v>
+      </c>
+      <c r="M77" s="18" t="s">
+        <v>718</v>
+      </c>
+      <c r="N77" s="19" t="s">
+        <v>392</v>
+      </c>
+      <c r="O77" s="20" t="s">
+        <v>433</v>
+      </c>
+      <c r="P77" s="21" t="s">
+        <v>356</v>
+      </c>
+    </row>
+    <row r="78" spans="1:16" ht="77.75" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A78" s="22">
         <v>72</v>
       </c>
       <c r="B78" s="13" t="s">
-        <v>501</v>
+        <v>434</v>
       </c>
       <c r="C78" s="13" t="s">
-        <v>502</v>
+        <v>699</v>
       </c>
       <c r="D78" s="14" t="s">
-        <v>503</v>
+        <v>435</v>
       </c>
       <c r="E78" s="14" t="s">
-        <v>447</v>
+        <v>389</v>
       </c>
       <c r="F78" s="15" t="s">
         <v>78</v>
       </c>
       <c r="G78" s="16" t="s">
-        <v>504</v>
+        <v>436</v>
       </c>
       <c r="H78" s="16" t="s">
-        <v>123</v>
+        <v>117</v>
       </c>
       <c r="I78" s="17" t="s">
-        <v>505</v>
+        <v>437</v>
       </c>
       <c r="J78" s="17" t="s">
-        <v>689</v>
+        <v>606</v>
       </c>
       <c r="K78" s="23" t="s">
-        <v>133</v>
+        <v>126</v>
       </c>
       <c r="L78" s="23" t="s">
-        <v>116</v>
-      </c>
-      <c r="M78" s="24" t="s">
-        <v>450</v>
-      </c>
-      <c r="N78" s="25" t="s">
-        <v>506</v>
-      </c>
-      <c r="O78" s="26" t="s">
-        <v>407</v>
-      </c>
-    </row>
-    <row r="79" spans="1:15" ht="19.5" customHeight="1" x14ac:dyDescent="0.45">
+        <v>111</v>
+      </c>
+      <c r="M78" s="23" t="s">
+        <v>718</v>
+      </c>
+      <c r="N78" s="24" t="s">
+        <v>392</v>
+      </c>
+      <c r="O78" s="25" t="s">
+        <v>438</v>
+      </c>
+      <c r="P78" s="26" t="s">
+        <v>356</v>
+      </c>
+    </row>
+    <row r="79" spans="1:16" ht="19.5" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A79" s="12">
         <v>73</v>
       </c>
       <c r="B79" s="13" t="s">
-        <v>507</v>
+        <v>439</v>
       </c>
       <c r="C79" s="13" t="s">
-        <v>508</v>
+        <v>700</v>
       </c>
       <c r="D79" s="14" t="s">
-        <v>509</v>
+        <v>440</v>
       </c>
       <c r="E79" s="14" t="s">
-        <v>447</v>
+        <v>389</v>
       </c>
       <c r="F79" s="15" t="s">
         <v>78</v>
       </c>
       <c r="G79" s="16" t="s">
-        <v>510</v>
+        <v>441</v>
       </c>
       <c r="H79" s="16" t="s">
-        <v>371</v>
+        <v>326</v>
       </c>
       <c r="I79" s="17" t="s">
-        <v>511</v>
+        <v>442</v>
       </c>
       <c r="J79" s="17" t="s">
-        <v>690</v>
+        <v>607</v>
       </c>
       <c r="K79" s="18" t="s">
-        <v>94</v>
+        <v>91</v>
       </c>
       <c r="L79" s="18" t="s">
-        <v>116</v>
-      </c>
-      <c r="M79" s="19" t="s">
-        <v>450</v>
-      </c>
-      <c r="N79" s="20" t="s">
-        <v>632</v>
-      </c>
-      <c r="O79" s="21"/>
-    </row>
-    <row r="80" spans="1:15" ht="19.5" customHeight="1" x14ac:dyDescent="0.45">
+        <v>111</v>
+      </c>
+      <c r="M79" s="18" t="s">
+        <v>718</v>
+      </c>
+      <c r="N79" s="19" t="s">
+        <v>392</v>
+      </c>
+      <c r="O79" s="20" t="s">
+        <v>550</v>
+      </c>
+      <c r="P79" s="21"/>
+    </row>
+    <row r="80" spans="1:16" ht="19.5" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A80" s="22">
         <v>74</v>
       </c>
       <c r="B80" s="13" t="s">
-        <v>512</v>
+        <v>443</v>
       </c>
       <c r="C80" s="13" t="s">
-        <v>513</v>
+        <v>701</v>
       </c>
       <c r="D80" s="14" t="s">
-        <v>514</v>
+        <v>444</v>
       </c>
       <c r="E80" s="14" t="s">
-        <v>447</v>
+        <v>389</v>
       </c>
       <c r="F80" s="15" t="s">
         <v>78</v>
       </c>
       <c r="G80" s="16" t="s">
-        <v>515</v>
+        <v>445</v>
       </c>
       <c r="H80" s="16" t="s">
-        <v>154</v>
+        <v>144</v>
       </c>
       <c r="I80" s="17" t="s">
-        <v>516</v>
+        <v>446</v>
       </c>
       <c r="J80" s="17" t="s">
-        <v>691</v>
+        <v>608</v>
       </c>
       <c r="K80" s="23" t="s">
-        <v>94</v>
+        <v>91</v>
       </c>
       <c r="L80" s="23" t="s">
-        <v>116</v>
-      </c>
-      <c r="M80" s="24" t="s">
-        <v>450</v>
-      </c>
-      <c r="N80" s="25" t="s">
-        <v>517</v>
-      </c>
-      <c r="O80" s="26"/>
-    </row>
-    <row r="81" spans="1:15" ht="19.5" customHeight="1" x14ac:dyDescent="0.45">
+        <v>111</v>
+      </c>
+      <c r="M80" s="23" t="s">
+        <v>718</v>
+      </c>
+      <c r="N80" s="24" t="s">
+        <v>392</v>
+      </c>
+      <c r="O80" s="25" t="s">
+        <v>447</v>
+      </c>
+      <c r="P80" s="26"/>
+    </row>
+    <row r="81" spans="1:16" ht="19.5" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A81" s="12">
         <v>75</v>
       </c>
       <c r="B81" s="13" t="s">
-        <v>518</v>
+        <v>448</v>
       </c>
       <c r="C81" s="13" t="s">
-        <v>519</v>
+        <v>702</v>
       </c>
       <c r="D81" s="14" t="s">
-        <v>520</v>
+        <v>449</v>
       </c>
       <c r="E81" s="14" t="s">
-        <v>447</v>
+        <v>389</v>
       </c>
       <c r="F81" s="15" t="s">
         <v>78</v>
       </c>
       <c r="G81" s="16" t="s">
-        <v>521</v>
+        <v>450</v>
       </c>
       <c r="H81" s="16" t="s">
-        <v>328</v>
+        <v>289</v>
       </c>
       <c r="I81" s="17" t="s">
-        <v>633</v>
+        <v>551</v>
       </c>
       <c r="J81" s="17" t="s">
-        <v>692</v>
+        <v>609</v>
       </c>
       <c r="K81" s="18" t="s">
-        <v>94</v>
+        <v>91</v>
       </c>
       <c r="L81" s="18">
         <v>5</v>
       </c>
-      <c r="M81" s="19" t="s">
-        <v>450</v>
-      </c>
-      <c r="N81" s="20" t="s">
-        <v>522</v>
-      </c>
-      <c r="O81" s="21"/>
-    </row>
-    <row r="82" spans="1:15" ht="45.4" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="M81" s="18" t="s">
+        <v>718</v>
+      </c>
+      <c r="N81" s="19" t="s">
+        <v>392</v>
+      </c>
+      <c r="O81" s="20" t="s">
+        <v>451</v>
+      </c>
+      <c r="P81" s="21"/>
+    </row>
+    <row r="82" spans="1:16" ht="45.4" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A82" s="22">
         <v>76</v>
       </c>
       <c r="B82" s="13" t="s">
-        <v>523</v>
+        <v>452</v>
       </c>
       <c r="C82" s="13" t="s">
-        <v>524</v>
+        <v>703</v>
       </c>
       <c r="D82" s="14" t="s">
-        <v>525</v>
+        <v>453</v>
       </c>
       <c r="E82" s="14" t="s">
-        <v>447</v>
+        <v>389</v>
       </c>
       <c r="F82" s="15" t="s">
         <v>78</v>
       </c>
       <c r="G82" s="16" t="s">
-        <v>521</v>
+        <v>450</v>
       </c>
       <c r="H82" s="16" t="s">
-        <v>526</v>
+        <v>454</v>
       </c>
       <c r="I82" s="17" t="s">
-        <v>527</v>
+        <v>455</v>
       </c>
       <c r="J82" s="17" t="s">
-        <v>693</v>
+        <v>610</v>
       </c>
       <c r="K82" s="23" t="s">
-        <v>94</v>
+        <v>91</v>
       </c>
       <c r="L82" s="23" t="s">
-        <v>528</v>
-      </c>
-      <c r="M82" s="24" t="s">
-        <v>256</v>
-      </c>
-      <c r="N82" s="63" t="s">
-        <v>529</v>
-      </c>
-      <c r="O82" s="26"/>
-    </row>
-    <row r="83" spans="1:15" ht="19.5" customHeight="1" x14ac:dyDescent="0.45">
+        <v>456</v>
+      </c>
+      <c r="M82" s="23" t="s">
+        <v>718</v>
+      </c>
+      <c r="N82" s="24" t="s">
+        <v>226</v>
+      </c>
+      <c r="O82" s="63" t="s">
+        <v>457</v>
+      </c>
+      <c r="P82" s="26"/>
+    </row>
+    <row r="83" spans="1:16" ht="19.5" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A83" s="12">
         <v>77</v>
       </c>
       <c r="B83" s="13" t="s">
-        <v>530</v>
+        <v>458</v>
       </c>
       <c r="C83" s="13" t="s">
-        <v>531</v>
+        <v>704</v>
       </c>
       <c r="D83" s="14" t="s">
-        <v>532</v>
+        <v>459</v>
       </c>
       <c r="E83" s="14" t="s">
-        <v>251</v>
+        <v>221</v>
       </c>
       <c r="F83" s="15" t="s">
         <v>75</v>
       </c>
       <c r="G83" s="16" t="s">
-        <v>533</v>
+        <v>460</v>
       </c>
       <c r="H83" s="16" t="s">
-        <v>534</v>
+        <v>461</v>
       </c>
       <c r="I83" s="17" t="s">
-        <v>535</v>
+        <v>462</v>
       </c>
       <c r="J83" s="17" t="s">
-        <v>694</v>
+        <v>611</v>
       </c>
       <c r="K83" s="18" t="s">
-        <v>255</v>
+        <v>225</v>
       </c>
       <c r="L83" s="18" t="s">
-        <v>116</v>
-      </c>
-      <c r="M83" s="19" t="s">
-        <v>256</v>
-      </c>
-      <c r="N83" s="20" t="s">
-        <v>634</v>
-      </c>
-      <c r="O83" s="21" t="s">
-        <v>270</v>
-      </c>
-    </row>
-    <row r="84" spans="1:15" ht="19.5" customHeight="1" x14ac:dyDescent="0.45">
+        <v>111</v>
+      </c>
+      <c r="M83" s="18" t="s">
+        <v>718</v>
+      </c>
+      <c r="N83" s="19" t="s">
+        <v>226</v>
+      </c>
+      <c r="O83" s="20" t="s">
+        <v>552</v>
+      </c>
+      <c r="P83" s="21" t="s">
+        <v>238</v>
+      </c>
+    </row>
+    <row r="84" spans="1:16" ht="19.5" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A84" s="22">
         <v>78</v>
       </c>
       <c r="B84" s="13" t="s">
-        <v>536</v>
+        <v>463</v>
       </c>
       <c r="C84" s="13" t="s">
-        <v>537</v>
+        <v>705</v>
       </c>
       <c r="D84" s="14" t="s">
-        <v>538</v>
+        <v>464</v>
       </c>
       <c r="E84" s="14" t="s">
-        <v>251</v>
+        <v>221</v>
       </c>
       <c r="F84" s="15" t="s">
         <v>75</v>
       </c>
       <c r="G84" s="16" t="s">
-        <v>539</v>
+        <v>465</v>
       </c>
       <c r="H84" s="16" t="s">
-        <v>534</v>
+        <v>461</v>
       </c>
       <c r="I84" s="17" t="s">
-        <v>540</v>
+        <v>466</v>
       </c>
       <c r="J84" s="17" t="s">
-        <v>695</v>
+        <v>612</v>
       </c>
       <c r="K84" s="23" t="s">
-        <v>255</v>
+        <v>225</v>
       </c>
       <c r="L84" s="23" t="s">
-        <v>116</v>
-      </c>
-      <c r="M84" s="24" t="s">
-        <v>256</v>
-      </c>
-      <c r="N84" s="25" t="s">
-        <v>614</v>
-      </c>
-      <c r="O84" s="26" t="s">
-        <v>270</v>
-      </c>
-    </row>
-    <row r="85" spans="1:15" ht="19.5" customHeight="1" x14ac:dyDescent="0.45">
+        <v>111</v>
+      </c>
+      <c r="M84" s="23" t="s">
+        <v>718</v>
+      </c>
+      <c r="N84" s="24" t="s">
+        <v>226</v>
+      </c>
+      <c r="O84" s="25" t="s">
+        <v>532</v>
+      </c>
+      <c r="P84" s="26" t="s">
+        <v>238</v>
+      </c>
+    </row>
+    <row r="85" spans="1:16" ht="19.5" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A85" s="12">
         <v>79</v>
       </c>
       <c r="B85" s="13" t="s">
-        <v>541</v>
+        <v>467</v>
       </c>
       <c r="C85" s="13" t="s">
-        <v>542</v>
+        <v>706</v>
       </c>
       <c r="D85" s="14" t="s">
-        <v>543</v>
+        <v>468</v>
       </c>
       <c r="E85" s="14" t="s">
-        <v>251</v>
+        <v>221</v>
       </c>
       <c r="F85" s="15" t="s">
         <v>75</v>
       </c>
       <c r="G85" s="16" t="s">
-        <v>261</v>
+        <v>230</v>
       </c>
       <c r="H85" s="16" t="s">
-        <v>534</v>
+        <v>461</v>
       </c>
       <c r="I85" s="17" t="s">
-        <v>544</v>
+        <v>469</v>
       </c>
       <c r="J85" s="17" t="s">
-        <v>696</v>
+        <v>613</v>
       </c>
       <c r="K85" s="18" t="s">
-        <v>263</v>
+        <v>232</v>
       </c>
       <c r="L85" s="18" t="s">
-        <v>116</v>
-      </c>
-      <c r="M85" s="19" t="s">
-        <v>256</v>
-      </c>
-      <c r="N85" s="20" t="s">
-        <v>635</v>
-      </c>
-      <c r="O85" s="21" t="s">
-        <v>545</v>
-      </c>
-    </row>
-    <row r="86" spans="1:15" ht="19.5" customHeight="1" x14ac:dyDescent="0.45">
+        <v>111</v>
+      </c>
+      <c r="M85" s="18" t="s">
+        <v>718</v>
+      </c>
+      <c r="N85" s="19" t="s">
+        <v>226</v>
+      </c>
+      <c r="O85" s="20" t="s">
+        <v>553</v>
+      </c>
+      <c r="P85" s="21" t="s">
+        <v>470</v>
+      </c>
+    </row>
+    <row r="86" spans="1:16" ht="19.5" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A86" s="22">
         <v>80</v>
       </c>
       <c r="B86" s="13" t="s">
-        <v>546</v>
+        <v>471</v>
       </c>
       <c r="C86" s="13" t="s">
-        <v>547</v>
+        <v>707</v>
       </c>
       <c r="D86" s="14" t="s">
-        <v>548</v>
+        <v>472</v>
       </c>
       <c r="E86" s="14" t="s">
-        <v>251</v>
+        <v>221</v>
       </c>
       <c r="F86" s="15" t="s">
         <v>75</v>
       </c>
       <c r="G86" s="16" t="s">
-        <v>549</v>
+        <v>473</v>
       </c>
       <c r="H86" s="16" t="s">
-        <v>534</v>
+        <v>461</v>
       </c>
       <c r="I86" s="17" t="s">
-        <v>550</v>
+        <v>474</v>
       </c>
       <c r="J86" s="17" t="s">
-        <v>697</v>
+        <v>614</v>
       </c>
       <c r="K86" s="23" t="s">
-        <v>551</v>
+        <v>475</v>
       </c>
       <c r="L86" s="23" t="s">
-        <v>116</v>
-      </c>
-      <c r="M86" s="24" t="s">
-        <v>256</v>
-      </c>
-      <c r="N86" s="25" t="s">
-        <v>636</v>
-      </c>
-      <c r="O86" s="26" t="s">
-        <v>552</v>
-      </c>
-    </row>
-    <row r="87" spans="1:15" ht="19.5" customHeight="1" x14ac:dyDescent="0.45">
+        <v>111</v>
+      </c>
+      <c r="M86" s="23" t="s">
+        <v>718</v>
+      </c>
+      <c r="N86" s="24" t="s">
+        <v>226</v>
+      </c>
+      <c r="O86" s="25" t="s">
+        <v>554</v>
+      </c>
+      <c r="P86" s="26" t="s">
+        <v>476</v>
+      </c>
+    </row>
+    <row r="87" spans="1:16" ht="19.5" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A87" s="12">
         <v>81</v>
       </c>
       <c r="B87" s="13" t="s">
-        <v>553</v>
+        <v>477</v>
       </c>
       <c r="C87" s="13" t="s">
-        <v>554</v>
+        <v>708</v>
       </c>
       <c r="D87" s="14" t="s">
-        <v>555</v>
+        <v>478</v>
       </c>
       <c r="E87" s="14" t="s">
-        <v>251</v>
+        <v>221</v>
       </c>
       <c r="F87" s="15" t="s">
         <v>75</v>
       </c>
       <c r="G87" s="16" t="s">
-        <v>556</v>
+        <v>479</v>
       </c>
       <c r="H87" s="16" t="s">
-        <v>334</v>
+        <v>294</v>
       </c>
       <c r="I87" s="17" t="s">
-        <v>557</v>
+        <v>480</v>
       </c>
       <c r="J87" s="17" t="s">
-        <v>698</v>
+        <v>615</v>
       </c>
       <c r="K87" s="18" t="s">
-        <v>255</v>
+        <v>225</v>
       </c>
       <c r="L87" s="18" t="s">
-        <v>116</v>
-      </c>
-      <c r="M87" s="19" t="s">
-        <v>256</v>
-      </c>
-      <c r="N87" s="20" t="s">
-        <v>634</v>
-      </c>
-      <c r="O87" s="21" t="s">
-        <v>270</v>
-      </c>
-    </row>
-    <row r="88" spans="1:15" ht="19.5" customHeight="1" x14ac:dyDescent="0.45">
+        <v>111</v>
+      </c>
+      <c r="M87" s="18" t="s">
+        <v>718</v>
+      </c>
+      <c r="N87" s="19" t="s">
+        <v>226</v>
+      </c>
+      <c r="O87" s="20" t="s">
+        <v>552</v>
+      </c>
+      <c r="P87" s="21" t="s">
+        <v>238</v>
+      </c>
+    </row>
+    <row r="88" spans="1:16" ht="19.5" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A88" s="22">
         <v>82</v>
       </c>
       <c r="B88" s="13" t="s">
-        <v>558</v>
-      </c>
-      <c r="C88" s="13"/>
+        <v>481</v>
+      </c>
+      <c r="C88" s="13" t="s">
+        <v>709</v>
+      </c>
       <c r="D88" s="14" t="s">
-        <v>559</v>
+        <v>482</v>
       </c>
       <c r="E88" s="14" t="s">
-        <v>560</v>
+        <v>483</v>
       </c>
       <c r="F88" s="15" t="s">
         <v>78</v>
       </c>
       <c r="G88" s="16" t="s">
-        <v>561</v>
+        <v>484</v>
       </c>
       <c r="H88" s="16" t="s">
-        <v>328</v>
+        <v>289</v>
       </c>
       <c r="I88" s="17"/>
       <c r="J88" s="17" t="s">
-        <v>699</v>
+        <v>616</v>
       </c>
       <c r="K88" s="23" t="s">
-        <v>94</v>
+        <v>91</v>
       </c>
       <c r="L88" s="23" t="s">
-        <v>434</v>
-      </c>
-      <c r="M88" s="24" t="s">
-        <v>560</v>
-      </c>
-      <c r="N88" s="37"/>
-      <c r="O88" s="26"/>
-    </row>
-    <row r="89" spans="1:15" ht="19.5" customHeight="1" x14ac:dyDescent="0.45">
+        <v>378</v>
+      </c>
+      <c r="M88" s="23" t="s">
+        <v>718</v>
+      </c>
+      <c r="N88" s="24" t="s">
+        <v>483</v>
+      </c>
+      <c r="O88" s="37"/>
+      <c r="P88" s="26"/>
+    </row>
+    <row r="89" spans="1:16" ht="19.5" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A89" s="12">
         <v>83</v>
       </c>
       <c r="B89" s="13" t="s">
-        <v>562</v>
+        <v>485</v>
       </c>
       <c r="C89" s="13" t="s">
-        <v>563</v>
+        <v>710</v>
       </c>
       <c r="D89" s="14" t="s">
-        <v>564</v>
+        <v>486</v>
       </c>
       <c r="E89" s="14" t="s">
-        <v>565</v>
+        <v>487</v>
       </c>
       <c r="F89" s="15" t="s">
         <v>77</v>
       </c>
       <c r="G89" s="16" t="s">
-        <v>566</v>
+        <v>488</v>
       </c>
       <c r="H89" s="16" t="s">
-        <v>235</v>
+        <v>208</v>
       </c>
       <c r="I89" s="17"/>
       <c r="J89" s="17"/>
       <c r="K89" s="18" t="s">
-        <v>94</v>
+        <v>91</v>
       </c>
       <c r="L89" s="18" t="s">
-        <v>567</v>
-      </c>
-      <c r="M89" s="19" t="s">
-        <v>565</v>
-      </c>
-      <c r="N89" s="38"/>
-      <c r="O89" s="21"/>
-    </row>
-    <row r="90" spans="1:15" ht="19.5" customHeight="1" x14ac:dyDescent="0.45">
+        <v>489</v>
+      </c>
+      <c r="M89" s="18" t="s">
+        <v>718</v>
+      </c>
+      <c r="N89" s="19" t="s">
+        <v>487</v>
+      </c>
+      <c r="O89" s="38"/>
+      <c r="P89" s="21"/>
+    </row>
+    <row r="90" spans="1:16" ht="19.5" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A90" s="22">
         <v>84</v>
       </c>
       <c r="B90" s="13" t="s">
-        <v>568</v>
+        <v>490</v>
       </c>
       <c r="C90" s="13" t="s">
-        <v>569</v>
+        <v>711</v>
       </c>
       <c r="D90" s="14" t="s">
-        <v>570</v>
+        <v>491</v>
       </c>
       <c r="E90" s="14" t="s">
-        <v>565</v>
+        <v>487</v>
       </c>
       <c r="F90" s="15" t="s">
         <v>77</v>
       </c>
       <c r="G90" s="16" t="s">
-        <v>566</v>
+        <v>488</v>
       </c>
       <c r="H90" s="16" t="s">
-        <v>328</v>
+        <v>289</v>
       </c>
       <c r="I90" s="17"/>
       <c r="J90" s="17"/>
       <c r="K90" s="23" t="s">
-        <v>94</v>
+        <v>91</v>
       </c>
       <c r="L90" s="23" t="s">
-        <v>571</v>
-      </c>
-      <c r="M90" s="24" t="s">
-        <v>565</v>
-      </c>
-      <c r="N90" s="37"/>
-      <c r="O90" s="26"/>
-    </row>
-    <row r="91" spans="1:15" ht="19.5" customHeight="1" x14ac:dyDescent="0.45">
+        <v>492</v>
+      </c>
+      <c r="M90" s="23" t="s">
+        <v>718</v>
+      </c>
+      <c r="N90" s="24" t="s">
+        <v>487</v>
+      </c>
+      <c r="O90" s="37"/>
+      <c r="P90" s="26"/>
+    </row>
+    <row r="91" spans="1:16" ht="19.5" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A91" s="12">
         <v>85</v>
       </c>
       <c r="B91" s="13" t="s">
-        <v>572</v>
+        <v>493</v>
       </c>
       <c r="C91" s="13" t="s">
-        <v>573</v>
+        <v>712</v>
       </c>
       <c r="D91" s="14" t="s">
-        <v>574</v>
+        <v>494</v>
       </c>
       <c r="E91" s="14" t="s">
-        <v>565</v>
+        <v>487</v>
       </c>
       <c r="F91" s="15" t="s">
         <v>77</v>
       </c>
       <c r="G91" s="16" t="s">
-        <v>566</v>
+        <v>488</v>
       </c>
       <c r="H91" s="16" t="s">
-        <v>328</v>
+        <v>289</v>
       </c>
       <c r="I91" s="17"/>
       <c r="J91" s="17"/>
       <c r="K91" s="18" t="s">
-        <v>94</v>
+        <v>91</v>
       </c>
       <c r="L91" s="18" t="s">
-        <v>571</v>
-      </c>
-      <c r="M91" s="19" t="s">
-        <v>565</v>
-      </c>
-      <c r="N91" s="38"/>
-      <c r="O91" s="21"/>
-    </row>
-    <row r="92" spans="1:15" ht="19.5" customHeight="1" x14ac:dyDescent="0.45">
+        <v>492</v>
+      </c>
+      <c r="M91" s="18" t="s">
+        <v>718</v>
+      </c>
+      <c r="N91" s="19" t="s">
+        <v>487</v>
+      </c>
+      <c r="O91" s="38"/>
+      <c r="P91" s="21"/>
+    </row>
+    <row r="92" spans="1:16" ht="19.5" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A92" s="22">
         <v>86</v>
       </c>
       <c r="B92" s="13" t="s">
-        <v>575</v>
+        <v>495</v>
       </c>
       <c r="C92" s="13" t="s">
-        <v>576</v>
+        <v>713</v>
       </c>
       <c r="D92" s="14"/>
       <c r="E92" s="14" t="s">
-        <v>565</v>
+        <v>487</v>
       </c>
       <c r="F92" s="15" t="s">
         <v>77</v>
       </c>
       <c r="G92" s="16" t="s">
-        <v>566</v>
+        <v>488</v>
       </c>
       <c r="H92" s="16" t="s">
-        <v>328</v>
+        <v>289</v>
       </c>
       <c r="I92" s="17"/>
       <c r="J92" s="17"/>
       <c r="K92" s="23" t="s">
-        <v>94</v>
+        <v>91</v>
       </c>
       <c r="L92" s="23" t="s">
-        <v>571</v>
-      </c>
-      <c r="M92" s="24" t="s">
-        <v>565</v>
-      </c>
-      <c r="N92" s="37"/>
-      <c r="O92" s="26"/>
-    </row>
-    <row r="93" spans="1:15" s="49" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.45">
+        <v>492</v>
+      </c>
+      <c r="M92" s="23" t="s">
+        <v>718</v>
+      </c>
+      <c r="N92" s="24" t="s">
+        <v>487</v>
+      </c>
+      <c r="O92" s="37"/>
+      <c r="P92" s="26"/>
+    </row>
+    <row r="93" spans="1:16" s="49" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A93" s="39">
         <v>87</v>
       </c>
       <c r="B93" s="40" t="s">
-        <v>577</v>
+        <v>496</v>
       </c>
       <c r="C93" s="40" t="s">
-        <v>578</v>
+        <v>714</v>
       </c>
       <c r="D93" s="41"/>
       <c r="E93" s="41" t="s">
-        <v>565</v>
+        <v>487</v>
       </c>
       <c r="F93" s="42" t="s">
         <v>78</v>
       </c>
       <c r="G93" s="43" t="s">
-        <v>579</v>
+        <v>497</v>
       </c>
       <c r="H93" s="43" t="s">
-        <v>580</v>
+        <v>498</v>
       </c>
       <c r="I93" s="44" t="s">
-        <v>581</v>
+        <v>499</v>
       </c>
       <c r="J93" s="44"/>
       <c r="K93" s="45" t="s">
-        <v>582</v>
+        <v>500</v>
       </c>
       <c r="L93" s="45" t="s">
-        <v>583</v>
-      </c>
-      <c r="M93" s="46" t="s">
-        <v>565</v>
-      </c>
-      <c r="N93" s="47" t="s">
-        <v>584</v>
-      </c>
-      <c r="O93" s="48"/>
-    </row>
-    <row r="94" spans="1:15" ht="19.5" customHeight="1" x14ac:dyDescent="0.45">
+        <v>501</v>
+      </c>
+      <c r="M93" s="45" t="s">
+        <v>718</v>
+      </c>
+      <c r="N93" s="46" t="s">
+        <v>487</v>
+      </c>
+      <c r="O93" s="47" t="s">
+        <v>502</v>
+      </c>
+      <c r="P93" s="48"/>
+    </row>
+    <row r="94" spans="1:16" ht="19.5" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A94" s="22">
         <v>88</v>
       </c>
       <c r="B94" s="13" t="s">
-        <v>562</v>
+        <v>485</v>
       </c>
       <c r="C94" s="13" t="s">
-        <v>563</v>
+        <v>710</v>
       </c>
       <c r="D94" s="14"/>
       <c r="E94" s="14" t="s">
-        <v>565</v>
+        <v>487</v>
       </c>
       <c r="F94" s="15" t="s">
         <v>77</v>
       </c>
       <c r="G94" s="16" t="s">
-        <v>566</v>
+        <v>488</v>
       </c>
       <c r="H94" s="16" t="s">
-        <v>235</v>
+        <v>208</v>
       </c>
       <c r="I94" s="17"/>
       <c r="J94" s="17"/>
       <c r="K94" s="23" t="s">
-        <v>94</v>
+        <v>91</v>
       </c>
       <c r="L94" s="23" t="s">
-        <v>567</v>
-      </c>
-      <c r="M94" s="24" t="s">
-        <v>565</v>
-      </c>
-      <c r="N94" s="37"/>
-      <c r="O94" s="26"/>
-    </row>
-    <row r="95" spans="1:15" ht="19.5" customHeight="1" x14ac:dyDescent="0.45">
+        <v>489</v>
+      </c>
+      <c r="M94" s="23" t="s">
+        <v>718</v>
+      </c>
+      <c r="N94" s="24" t="s">
+        <v>487</v>
+      </c>
+      <c r="O94" s="37"/>
+      <c r="P94" s="26"/>
+    </row>
+    <row r="95" spans="1:16" ht="19.5" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A95" s="12">
         <v>89</v>
       </c>
       <c r="B95" s="13" t="s">
-        <v>568</v>
+        <v>490</v>
       </c>
       <c r="C95" s="13" t="s">
-        <v>569</v>
+        <v>715</v>
       </c>
       <c r="D95" s="14"/>
       <c r="E95" s="14" t="s">
-        <v>565</v>
+        <v>487</v>
       </c>
       <c r="F95" s="15" t="s">
         <v>77</v>
       </c>
       <c r="G95" s="16" t="s">
-        <v>566</v>
+        <v>488</v>
       </c>
       <c r="H95" s="16" t="s">
-        <v>580</v>
+        <v>498</v>
       </c>
       <c r="I95" s="17"/>
       <c r="J95" s="17"/>
       <c r="K95" s="18" t="s">
-        <v>94</v>
+        <v>91</v>
       </c>
       <c r="L95" s="18" t="s">
-        <v>585</v>
-      </c>
-      <c r="M95" s="19" t="s">
-        <v>565</v>
-      </c>
-      <c r="N95" s="38"/>
-      <c r="O95" s="21"/>
-    </row>
-    <row r="96" spans="1:15" ht="19.5" customHeight="1" x14ac:dyDescent="0.45">
+        <v>503</v>
+      </c>
+      <c r="M95" s="18" t="s">
+        <v>718</v>
+      </c>
+      <c r="N95" s="19" t="s">
+        <v>487</v>
+      </c>
+      <c r="O95" s="38"/>
+      <c r="P95" s="21"/>
+    </row>
+    <row r="96" spans="1:16" ht="19.5" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A96" s="22">
         <v>90</v>
       </c>
       <c r="B96" s="13" t="s">
-        <v>586</v>
+        <v>504</v>
       </c>
       <c r="C96" s="13" t="s">
-        <v>587</v>
+        <v>505</v>
       </c>
       <c r="D96" s="14" t="s">
-        <v>588</v>
+        <v>506</v>
       </c>
       <c r="E96" s="14" t="s">
-        <v>589</v>
+        <v>507</v>
       </c>
       <c r="F96" s="15" t="s">
         <v>78</v>
       </c>
       <c r="G96" s="16" t="s">
-        <v>590</v>
+        <v>508</v>
       </c>
       <c r="H96" s="16" t="s">
-        <v>591</v>
+        <v>509</v>
       </c>
       <c r="I96" s="17" t="s">
-        <v>592</v>
+        <v>510</v>
       </c>
       <c r="J96" s="17"/>
       <c r="K96" s="23" t="s">
-        <v>94</v>
+        <v>91</v>
       </c>
       <c r="L96" s="23" t="s">
-        <v>116</v>
-      </c>
-      <c r="M96" s="24" t="s">
-        <v>589</v>
-      </c>
-      <c r="N96" s="25" t="s">
-        <v>593</v>
-      </c>
-      <c r="O96" s="26"/>
-    </row>
-    <row r="97" spans="1:15" ht="19.5" customHeight="1" x14ac:dyDescent="0.45">
+        <v>111</v>
+      </c>
+      <c r="M96" s="23" t="s">
+        <v>718</v>
+      </c>
+      <c r="N96" s="24" t="s">
+        <v>507</v>
+      </c>
+      <c r="O96" s="25" t="s">
+        <v>511</v>
+      </c>
+      <c r="P96" s="26"/>
+    </row>
+    <row r="97" spans="1:16" ht="19.5" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A97" s="22">
         <v>91</v>
       </c>
       <c r="B97" s="13" t="s">
-        <v>705</v>
+        <v>621</v>
       </c>
       <c r="C97" s="13" t="s">
-        <v>700</v>
+        <v>716</v>
       </c>
       <c r="D97" s="14" t="s">
-        <v>701</v>
+        <v>617</v>
       </c>
       <c r="E97" s="14" t="s">
-        <v>702</v>
+        <v>618</v>
       </c>
       <c r="F97" s="15" t="s">
         <v>77</v>
       </c>
       <c r="G97" s="16"/>
       <c r="H97" s="16" t="s">
-        <v>704</v>
+        <v>620</v>
       </c>
       <c r="I97" s="17"/>
       <c r="J97" s="17" t="s">
-        <v>703</v>
+        <v>619</v>
       </c>
       <c r="K97" s="23" t="s">
-        <v>94</v>
+        <v>91</v>
       </c>
       <c r="L97" s="23" t="s">
-        <v>364</v>
-      </c>
-      <c r="M97" s="24" t="s">
-        <v>361</v>
-      </c>
-      <c r="N97" s="25" t="s">
-        <v>706</v>
-      </c>
-      <c r="O97" s="26"/>
-    </row>
-    <row r="98" spans="1:15" ht="19.5" customHeight="1" x14ac:dyDescent="0.45">
+        <v>320</v>
+      </c>
+      <c r="M97" s="23" t="s">
+        <v>723</v>
+      </c>
+      <c r="N97" s="24" t="s">
+        <v>317</v>
+      </c>
+      <c r="O97" s="25" t="s">
+        <v>622</v>
+      </c>
+      <c r="P97" s="26"/>
+    </row>
+    <row r="98" spans="1:16" ht="19.5" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A98" s="22">
         <v>92</v>
       </c>
       <c r="B98" s="13" t="s">
-        <v>707</v>
+        <v>623</v>
       </c>
       <c r="C98" s="13" t="s">
-        <v>708</v>
+        <v>623</v>
       </c>
       <c r="D98" s="14" t="s">
-        <v>709</v>
+        <v>624</v>
       </c>
       <c r="E98" s="14" t="s">
-        <v>361</v>
+        <v>317</v>
       </c>
       <c r="F98" s="15" t="s">
         <v>77</v>
       </c>
       <c r="G98" s="16"/>
       <c r="H98" s="16" t="s">
-        <v>710</v>
+        <v>625</v>
       </c>
       <c r="I98" s="17"/>
       <c r="J98" s="17" t="s">
-        <v>712</v>
+        <v>627</v>
       </c>
       <c r="K98" s="23" t="s">
-        <v>107</v>
+        <v>103</v>
       </c>
       <c r="L98" s="23" t="s">
-        <v>711</v>
-      </c>
-      <c r="M98" s="24" t="s">
-        <v>361</v>
-      </c>
-      <c r="N98" s="25" t="s">
-        <v>713</v>
-      </c>
-      <c r="O98" s="26"/>
-    </row>
-    <row r="99" spans="1:15" ht="19.5" customHeight="1" x14ac:dyDescent="0.45">
+        <v>626</v>
+      </c>
+      <c r="M98" s="23" t="s">
+        <v>721</v>
+      </c>
+      <c r="N98" s="24" t="s">
+        <v>317</v>
+      </c>
+      <c r="O98" s="25" t="s">
+        <v>628</v>
+      </c>
+      <c r="P98" s="26"/>
+    </row>
+    <row r="99" spans="1:16" ht="19.5" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A99" s="12">
         <v>93</v>
       </c>
       <c r="B99" s="13" t="s">
-        <v>594</v>
+        <v>512</v>
       </c>
       <c r="C99" s="13" t="s">
-        <v>595</v>
+        <v>513</v>
       </c>
       <c r="D99" s="14" t="s">
-        <v>596</v>
+        <v>514</v>
       </c>
       <c r="E99" s="14" t="s">
-        <v>597</v>
+        <v>515</v>
       </c>
       <c r="F99" s="15" t="s">
         <v>77</v>
       </c>
       <c r="G99" s="16" t="s">
-        <v>598</v>
+        <v>516</v>
       </c>
       <c r="H99" s="16" t="s">
-        <v>599</v>
+        <v>517</v>
       </c>
       <c r="I99" s="17" t="s">
-        <v>600</v>
+        <v>518</v>
       </c>
       <c r="J99" s="17" t="s">
-        <v>714</v>
+        <v>629</v>
       </c>
       <c r="K99" s="18" t="s">
-        <v>133</v>
+        <v>126</v>
       </c>
       <c r="L99" s="18" t="s">
-        <v>601</v>
-      </c>
-      <c r="M99" s="19" t="s">
-        <v>597</v>
-      </c>
-      <c r="N99" s="20" t="s">
-        <v>602</v>
-      </c>
-      <c r="O99" s="21" t="s">
-        <v>603</v>
-      </c>
-    </row>
-    <row r="100" spans="1:15" ht="187.25" customHeight="1" x14ac:dyDescent="0.45">
+        <v>519</v>
+      </c>
+      <c r="M99" s="18" t="s">
+        <v>724</v>
+      </c>
+      <c r="N99" s="19" t="s">
+        <v>515</v>
+      </c>
+      <c r="O99" s="20" t="s">
+        <v>520</v>
+      </c>
+      <c r="P99" s="21" t="s">
+        <v>521</v>
+      </c>
+    </row>
+    <row r="100" spans="1:16" ht="187.25" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A100" s="22">
         <v>94</v>
       </c>
       <c r="B100" s="13" t="s">
-        <v>604</v>
+        <v>522</v>
       </c>
       <c r="C100" s="13" t="s">
-        <v>605</v>
+        <v>523</v>
       </c>
       <c r="D100" s="14"/>
       <c r="E100" s="14" t="s">
-        <v>597</v>
+        <v>515</v>
       </c>
       <c r="F100" s="15"/>
       <c r="G100" s="16"/>
       <c r="H100" s="16" t="s">
-        <v>599</v>
+        <v>517</v>
       </c>
       <c r="I100" s="17"/>
       <c r="J100" s="17" t="s">
-        <v>715</v>
+        <v>630</v>
       </c>
       <c r="K100" s="23"/>
       <c r="L100" s="23"/>
-      <c r="M100" s="24"/>
-      <c r="N100" s="25" t="s">
-        <v>606</v>
-      </c>
-      <c r="O100" s="26"/>
-    </row>
-    <row r="101" spans="1:15" ht="88.9" customHeight="1" thickBot="1" x14ac:dyDescent="0.5">
+      <c r="M100" s="23" t="s">
+        <v>724</v>
+      </c>
+      <c r="N100" s="24"/>
+      <c r="O100" s="25" t="s">
+        <v>524</v>
+      </c>
+      <c r="P100" s="26"/>
+    </row>
+    <row r="101" spans="1:16" ht="88.9" customHeight="1" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A101" s="12">
         <v>95</v>
       </c>
       <c r="B101" s="13" t="s">
-        <v>607</v>
+        <v>525</v>
       </c>
       <c r="C101" s="13" t="s">
-        <v>608</v>
+        <v>526</v>
       </c>
       <c r="D101" s="14"/>
       <c r="E101" s="14" t="s">
-        <v>609</v>
+        <v>527</v>
       </c>
       <c r="F101" s="15" t="s">
         <v>77</v>
       </c>
       <c r="G101" s="16" t="s">
-        <v>610</v>
+        <v>528</v>
       </c>
       <c r="H101" s="16" t="s">
-        <v>599</v>
+        <v>517</v>
       </c>
       <c r="I101" s="17"/>
       <c r="J101" s="17" t="s">
-        <v>716</v>
+        <v>631</v>
       </c>
       <c r="K101" s="18" t="s">
-        <v>133</v>
+        <v>126</v>
       </c>
       <c r="L101" s="18" t="s">
-        <v>601</v>
-      </c>
-      <c r="M101" s="19" t="s">
-        <v>597</v>
-      </c>
-      <c r="N101" s="38"/>
-      <c r="O101" s="21"/>
-    </row>
-    <row r="102" spans="1:15" ht="21.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="A102" s="66" t="s">
+        <v>519</v>
+      </c>
+      <c r="M101" s="18" t="s">
+        <v>724</v>
+      </c>
+      <c r="N101" s="19" t="s">
+        <v>515</v>
+      </c>
+      <c r="O101" s="38"/>
+      <c r="P101" s="21"/>
+    </row>
+    <row r="102" spans="1:16" ht="21.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.5">
+      <c r="A102" s="67" t="s">
         <v>35</v>
       </c>
-      <c r="B102" s="66"/>
+      <c r="B102" s="67"/>
       <c r="C102" s="27"/>
       <c r="D102" s="28"/>
       <c r="E102" s="28"/>
@@ -7788,42 +8108,43 @@
       <c r="M102" s="28"/>
       <c r="N102" s="28"/>
       <c r="O102" s="28"/>
+      <c r="P102" s="28"/>
     </row>
   </sheetData>
   <mergeCells count="6">
     <mergeCell ref="A102:B102"/>
-    <mergeCell ref="A2:O2"/>
+    <mergeCell ref="A2:P2"/>
     <mergeCell ref="B4:E4"/>
     <mergeCell ref="F4:I4"/>
     <mergeCell ref="K4:L4"/>
-    <mergeCell ref="N4:O4"/>
+    <mergeCell ref="O4:P4"/>
   </mergeCells>
-  <dataValidations count="1">
+  <dataValidations disablePrompts="1" count="1">
     <dataValidation type="list" allowBlank="1" sqref="F7:F101" xr:uid="{B8BA07F0-5CBC-7246-81AB-410FD646B5A0}">
       <formula1>"PCR &amp; Moleküler Biyoloji,Hücre Kültürü,Pipetleme,Sterilizasyon,Su Arıtma,Genomik &amp; Sekanslama,Biyokimya,Genel Sarf"</formula1>
       <formula2>0</formula2>
     </dataValidation>
   </dataValidations>
   <hyperlinks>
-    <hyperlink ref="N7" r:id="rId1" xr:uid="{FDA6277D-8475-4C83-9C6E-35569D8354D9}"/>
-    <hyperlink ref="N8" r:id="rId2" xr:uid="{04AC5826-5818-48CD-9DD4-18AB01976770}"/>
-    <hyperlink ref="N9" r:id="rId3" xr:uid="{EFF9AA3D-0150-497F-BBD5-8CBBC6EE6C4E}"/>
-    <hyperlink ref="N10" r:id="rId4" xr:uid="{9145BF72-CF0A-48B8-B4CA-49DC975175EC}"/>
-    <hyperlink ref="N11" r:id="rId5" xr:uid="{F58A0592-019C-488B-9C66-8B0F2314952E}"/>
-    <hyperlink ref="N12" r:id="rId6" xr:uid="{7EC34FE7-F386-48D9-B8AC-B099FE88CC40}"/>
-    <hyperlink ref="N13" r:id="rId7" xr:uid="{FD973873-E9F1-400E-ABA8-DC8D4BF2F4C2}"/>
-    <hyperlink ref="N14" r:id="rId8" xr:uid="{66149693-A9F0-4597-A524-6101242D3698}"/>
-    <hyperlink ref="N15" r:id="rId9" xr:uid="{64A35D5B-977F-414B-9F81-E0D0CBE77ECD}"/>
-    <hyperlink ref="N16" r:id="rId10" xr:uid="{7C6EF88E-64B0-4CF8-8485-51E6E6B3E383}"/>
-    <hyperlink ref="N17" r:id="rId11" xr:uid="{8C57653B-2299-4183-995F-A6BD11D8E5CE}"/>
-    <hyperlink ref="N18" r:id="rId12" xr:uid="{9750664B-66BA-4573-8C57-704400686884}"/>
-    <hyperlink ref="N44" r:id="rId13" xr:uid="{4DF39448-B653-432A-8C6C-585C1D93B7F3}"/>
-    <hyperlink ref="N45" r:id="rId14" xr:uid="{1AA6145A-C0A2-4147-9B3A-76DC3D67E88C}"/>
-    <hyperlink ref="N46" r:id="rId15" xr:uid="{4A56879B-7FF9-466D-B6B5-78C2886FDE4E}"/>
-    <hyperlink ref="N97" r:id="rId16" xr:uid="{ED808F01-6CDC-4E88-B155-7E5D0AB08340}"/>
-    <hyperlink ref="N98" r:id="rId17" xr:uid="{E5222A7C-8F0C-422E-A945-517E0B9977DF}"/>
-    <hyperlink ref="N82" r:id="rId18" xr:uid="{5BC976E8-AB27-482D-BDC0-CD507D47AC2E}"/>
-    <hyperlink ref="N72" r:id="rId19" xr:uid="{67C65B40-5C7F-432E-805E-29F235451CE5}"/>
+    <hyperlink ref="O7" r:id="rId1" xr:uid="{FDA6277D-8475-4C83-9C6E-35569D8354D9}"/>
+    <hyperlink ref="O8" r:id="rId2" xr:uid="{04AC5826-5818-48CD-9DD4-18AB01976770}"/>
+    <hyperlink ref="O9" r:id="rId3" xr:uid="{EFF9AA3D-0150-497F-BBD5-8CBBC6EE6C4E}"/>
+    <hyperlink ref="O10" r:id="rId4" xr:uid="{9145BF72-CF0A-48B8-B4CA-49DC975175EC}"/>
+    <hyperlink ref="O11" r:id="rId5" xr:uid="{F58A0592-019C-488B-9C66-8B0F2314952E}"/>
+    <hyperlink ref="O12" r:id="rId6" xr:uid="{7EC34FE7-F386-48D9-B8AC-B099FE88CC40}"/>
+    <hyperlink ref="O13" r:id="rId7" xr:uid="{FD973873-E9F1-400E-ABA8-DC8D4BF2F4C2}"/>
+    <hyperlink ref="O14" r:id="rId8" xr:uid="{66149693-A9F0-4597-A524-6101242D3698}"/>
+    <hyperlink ref="O15" r:id="rId9" xr:uid="{64A35D5B-977F-414B-9F81-E0D0CBE77ECD}"/>
+    <hyperlink ref="O16" r:id="rId10" xr:uid="{7C6EF88E-64B0-4CF8-8485-51E6E6B3E383}"/>
+    <hyperlink ref="O17" r:id="rId11" xr:uid="{8C57653B-2299-4183-995F-A6BD11D8E5CE}"/>
+    <hyperlink ref="O18" r:id="rId12" xr:uid="{9750664B-66BA-4573-8C57-704400686884}"/>
+    <hyperlink ref="O44" r:id="rId13" xr:uid="{4DF39448-B653-432A-8C6C-585C1D93B7F3}"/>
+    <hyperlink ref="O45" r:id="rId14" xr:uid="{1AA6145A-C0A2-4147-9B3A-76DC3D67E88C}"/>
+    <hyperlink ref="O46" r:id="rId15" xr:uid="{4A56879B-7FF9-466D-B6B5-78C2886FDE4E}"/>
+    <hyperlink ref="O97" r:id="rId16" xr:uid="{ED808F01-6CDC-4E88-B155-7E5D0AB08340}"/>
+    <hyperlink ref="O98" r:id="rId17" xr:uid="{E5222A7C-8F0C-422E-A945-517E0B9977DF}"/>
+    <hyperlink ref="O82" r:id="rId18" xr:uid="{5BC976E8-AB27-482D-BDC0-CD507D47AC2E}"/>
+    <hyperlink ref="O72" r:id="rId19" xr:uid="{67C65B40-5C7F-432E-805E-29F235451CE5}"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
@@ -7842,12 +8163,12 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:4" ht="30" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A1" s="72" t="s">
+      <c r="A1" s="73" t="s">
         <v>36</v>
       </c>
-      <c r="B1" s="72"/>
-      <c r="C1" s="72"/>
-      <c r="D1" s="72"/>
+      <c r="B1" s="73"/>
+      <c r="C1" s="73"/>
+      <c r="D1" s="73"/>
     </row>
     <row r="2" spans="1:4" ht="19.5" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A2" s="29" t="s">
@@ -8060,12 +8381,12 @@
       </c>
     </row>
     <row r="19" spans="1:4" ht="19.5" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A19" s="73" t="s">
+      <c r="A19" s="74" t="s">
         <v>71</v>
       </c>
-      <c r="B19" s="73"/>
-      <c r="C19" s="73"/>
-      <c r="D19" s="73"/>
+      <c r="B19" s="74"/>
+      <c r="C19" s="74"/>
+      <c r="D19" s="74"/>
     </row>
     <row r="20" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A20" s="35" t="s">
